--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9173181A-B7D8-4FBF-BAEB-BFA102C7B0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DDBFB2-8AA5-4923-B8CD-FB6E86860846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7650" yWindow="555" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
     <sheet name="2" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="135">
   <si>
     <t>VALOR UNITARIO</t>
   </si>
@@ -498,18 +498,12 @@
     <t>CANTIDAD CAJONES</t>
   </si>
   <si>
-    <t>VALOR DE CARGA (PAGO AL PROVEEDOR)</t>
-  </si>
-  <si>
     <t>RESUMEN DE COTIZACIÓN</t>
   </si>
   <si>
     <t>MONTO TOTAL</t>
   </si>
   <si>
-    <t>SERVICIO DE IMPORTACIÓN  (ORIGEN -FLETE - DESTINO)</t>
-  </si>
-  <si>
     <t>CALCULO DE TRIBUTOS</t>
   </si>
   <si>
@@ -580,6 +574,42 @@
   </si>
   <si>
     <t xml:space="preserve">         RUC: 20612452432</t>
+  </si>
+  <si>
+    <t>COSTOS FOB</t>
+  </si>
+  <si>
+    <t>ISC</t>
+  </si>
+  <si>
+    <t>CALCULO DE SERVICIO DE IMPORTACIÓN</t>
+  </si>
+  <si>
+    <t>Gravado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLETE INTERNACIONAL </t>
+  </si>
+  <si>
+    <t>No gravado</t>
+  </si>
+  <si>
+    <t>COSTOS EN DESTINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECARGOS OPERATIVOS ( QTY PROVEEDORES Y/O ITEMS) </t>
+  </si>
+  <si>
+    <t>DESCUENTO APLICABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVICIO DE IMPORTACIÓN  </t>
+  </si>
+  <si>
+    <t>RECARGO LOGISTICOS ( MONTACARGAS)</t>
+  </si>
+  <si>
+    <t>RECARGO DE DESPACHO (ALMACEN - AGENCIAS)</t>
   </si>
 </sst>
 </file>
@@ -601,7 +631,7 @@
     <numFmt numFmtId="174" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-[$$-80A]* #,##0.000_-;\-[$$-80A]* #,##0.000_-;_-[$$-80A]* &quot;-&quot;???_-;_-@_-"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,8 +835,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,8 +959,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FF009999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1021,6 +1131,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1055,7 +1195,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1256,83 +1396,71 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="36" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1344,9 +1472,96 @@
     <xf numFmtId="14" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1363,6 +1578,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1444,7 +1671,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>511628</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>10885</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1209675" cy="1190625"/>
@@ -1483,13 +1710,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>696686</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>107313</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>500744</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>174173</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1800,7 +2027,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -1812,141 +2039,142 @@
     <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="0.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" style="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="105"/>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
+      <c r="A1" s="124"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
     </row>
     <row r="3" spans="1:12" ht="26.25">
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="E3" s="112" t="s">
+      <c r="B3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="E3" s="129" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+    </row>
+    <row r="4" spans="1:12" ht="26.25">
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="E4" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-    </row>
-    <row r="4" spans="1:12" ht="26.25">
-      <c r="B4" s="92"/>
-      <c r="C4" s="92"/>
-      <c r="E4" s="113" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
       <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="92"/>
-      <c r="C5" s="92"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
       <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="92"/>
-      <c r="C6" s="92"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="92"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
+      <c r="A7" s="120"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
       <c r="E7" s="121" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F7" s="121"/>
       <c r="G7" s="121"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D8" s="87"/>
       <c r="E8" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="125" t="s">
+      <c r="F8" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="126"/>
+      <c r="G8" s="127"/>
       <c r="H8" s="86"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="117">
+      <c r="J8" s="140">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="117"/>
-      <c r="L8" s="117"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
         <v>81</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" s="87"/>
       <c r="E9" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F9" s="122">
         <f ca="1">+TODAY()</f>
-        <v>45943</v>
+        <v>46125</v>
       </c>
       <c r="G9" s="123"/>
       <c r="H9" s="86"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="120">
+      <c r="J9" s="119">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
@@ -1959,19 +2187,19 @@
       <c r="E10" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="105" t="s">
+      <c r="F10" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="124"/>
+      <c r="G10" s="125"/>
       <c r="H10" s="86"/>
       <c r="I10" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J10" s="118">
+        <v>119</v>
+      </c>
+      <c r="J10" s="141">
         <v>0</v>
       </c>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
@@ -1984,44 +2212,44 @@
       <c r="E11" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="119"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="144"/>
       <c r="H11" s="86"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="100">
+      <c r="J11" s="152">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
+      <c r="K11" s="152"/>
+      <c r="L11" s="152"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="109" t="s">
+      <c r="B13" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
       <c r="K13" s="32" t="s">
         <v>34</v>
       </c>
@@ -2030,17 +2258,17 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="146"/>
+      <c r="I14" s="146"/>
+      <c r="J14" s="146"/>
       <c r="K14" s="37">
         <f>'2'!F13</f>
         <v>944.03</v>
@@ -2050,59 +2278,64 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="110" t="s">
+      <c r="A15" s="92"/>
+      <c r="B15" s="154" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="38">
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="38">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
       </c>
-      <c r="L15" s="34" t="s">
+      <c r="L16" s="34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="B16" s="106" t="s">
+    <row r="17" spans="1:29">
+      <c r="B17" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="37">
-        <f>SUM(K14:K15)</f>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="147"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="37">
+        <f>SUM(K14:K16)</f>
         <v>1243.51</v>
       </c>
-      <c r="L16" s="31" t="s">
+      <c r="L17" s="31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-    </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="1:29">
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
       <c r="D18" s="29"/>
@@ -2115,14 +2348,14 @@
       <c r="K18" s="29"/>
       <c r="L18" s="29"/>
     </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
+    <row r="19" spans="1:29">
+      <c r="B19" s="153" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
@@ -2136,17 +2369,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="93" t="s">
+    <row r="20" spans="1:29">
+      <c r="B20" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="149"/>
       <c r="J20" s="47">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
@@ -2159,1134 +2392,1506 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="93"/>
+    <row r="21" spans="1:29">
+      <c r="B21" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
       <c r="J21" s="47">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="K21" s="37">
-        <f>'2'!F28</f>
-        <v>204.32327611622512</v>
+        <v>0</v>
       </c>
       <c r="L21" s="31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
+    <row r="22" spans="1:29">
+      <c r="B22" s="149" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="149"/>
       <c r="J22" s="47">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="K22" s="37">
         <f>'2'!F29</f>
-        <v>25.54040951452814</v>
+        <v>204.32327611622512</v>
       </c>
       <c r="L22" s="31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="106" t="s">
+    <row r="23" spans="1:29">
+      <c r="B23" s="143" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="47">
+        <v>0.02</v>
+      </c>
+      <c r="K23" s="37">
+        <f>'2'!F30</f>
+        <v>25.54040951452814</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="B24" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="76">
-        <f>SUM(K20:K22)</f>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="147"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="76">
+        <f>SUM(K20:K23)</f>
         <v>263.37416135716029</v>
       </c>
-      <c r="L23" s="75" t="s">
+      <c r="L24" s="75" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="93"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="31"/>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="107" t="s">
+    <row r="25" spans="1:29">
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="149"/>
+      <c r="I25" s="149"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="31"/>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="B26" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="48" t="s">
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="K25" s="38">
-        <f>'2'!F30</f>
+      <c r="K26" s="38">
+        <f>'2'!F31</f>
         <v>52.74094564750061</v>
       </c>
-      <c r="L25" s="34" t="s">
+      <c r="L26" s="34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
-      <c r="B26" s="106" t="s">
+    <row r="27" spans="1:29">
+      <c r="B27" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="K26" s="37">
-        <f>K23+K25</f>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="147"/>
+      <c r="I27" s="147"/>
+      <c r="K27" s="37">
+        <f>K24+K26</f>
         <v>316.1151070046609</v>
       </c>
-      <c r="L26" s="31" t="s">
+      <c r="L27" s="31" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="2:12">
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-    </row>
-    <row r="28" spans="2:12" ht="15.75">
-      <c r="B28" s="128" t="s">
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+      <c r="U27"/>
+      <c r="V27"/>
+      <c r="W27"/>
+      <c r="X27"/>
+      <c r="Y27"/>
+      <c r="Z27"/>
+      <c r="AA27"/>
+      <c r="AB27"/>
+      <c r="AC27"/>
+    </row>
+    <row r="28" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B28" s="124"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="124"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+      <c r="S28"/>
+      <c r="T28"/>
+      <c r="U28"/>
+      <c r="V28"/>
+      <c r="W28"/>
+      <c r="X28"/>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+    </row>
+    <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A29" s="93"/>
+      <c r="B29" s="157" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="158"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" s="96" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="M29" s="110"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="111"/>
+      <c r="S29" s="111"/>
+      <c r="T29" s="111"/>
+      <c r="W29" s="111"/>
+      <c r="X29" s="111"/>
+      <c r="AA29" s="111"/>
+      <c r="AB29" s="111"/>
+    </row>
+    <row r="30" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A30" s="93"/>
+      <c r="B30" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="97"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30" s="99"/>
+      <c r="L30" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="110"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="S30" s="112"/>
+      <c r="T30" s="112"/>
+      <c r="W30" s="112"/>
+      <c r="X30" s="112"/>
+      <c r="AA30" s="112"/>
+      <c r="AB30" s="112"/>
+    </row>
+    <row r="31" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A31" s="93"/>
+      <c r="B31" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="97"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="K31" s="99"/>
+      <c r="L31" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="M31" s="110"/>
+      <c r="N31" s="100"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="113"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="112"/>
+      <c r="U31" s="112"/>
+      <c r="W31" s="112"/>
+      <c r="X31" s="112"/>
+      <c r="Y31" s="112"/>
+      <c r="AA31" s="112"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+    </row>
+    <row r="32" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A32" s="93"/>
+      <c r="B32" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="103" t="s">
+        <v>126</v>
+      </c>
+      <c r="K32" s="104"/>
+      <c r="L32" s="105" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="110"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="S32" s="112"/>
+      <c r="T32" s="112"/>
+      <c r="W32" s="112"/>
+      <c r="X32" s="112"/>
+      <c r="AA32" s="112"/>
+      <c r="AB32" s="112"/>
+    </row>
+    <row r="33" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A33" s="93"/>
+      <c r="B33" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="97"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="107"/>
+      <c r="K33" s="99">
+        <f>SUM(K30:K32)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="110"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="S33" s="112"/>
+      <c r="T33" s="114"/>
+      <c r="W33" s="112"/>
+      <c r="AA33" s="112"/>
+      <c r="AB33" s="115"/>
+    </row>
+    <row r="34" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A34" s="93"/>
+      <c r="B34" s="106"/>
+      <c r="C34" s="97"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="97"/>
+      <c r="I34" s="97"/>
+      <c r="J34" s="107"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="110"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="S34" s="112"/>
+      <c r="T34" s="112"/>
+      <c r="W34" s="112"/>
+      <c r="X34" s="112"/>
+      <c r="AA34" s="112"/>
+      <c r="AB34" s="112"/>
+    </row>
+    <row r="35" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A35" s="93"/>
+      <c r="B35" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="97"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="107"/>
+      <c r="K35" s="99">
+        <v>0</v>
+      </c>
+      <c r="L35" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="M35" s="110"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="S35" s="112"/>
+      <c r="T35" s="112"/>
+      <c r="W35" s="112"/>
+      <c r="X35" s="112"/>
+      <c r="AA35" s="112"/>
+      <c r="AB35" s="112"/>
+    </row>
+    <row r="36" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A36" s="93"/>
+      <c r="B36" s="101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="102"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="108">
+        <v>0</v>
+      </c>
+      <c r="L36" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="M36" s="110"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="S36" s="112"/>
+      <c r="T36" s="112"/>
+      <c r="W36" s="112"/>
+      <c r="X36" s="112"/>
+      <c r="AA36" s="112"/>
+      <c r="AB36" s="112"/>
+    </row>
+    <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A37" s="93"/>
+      <c r="B37" s="174" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="175"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="175"/>
+      <c r="F37" s="175"/>
+      <c r="G37" s="175"/>
+      <c r="H37" s="175"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="171">
+        <f>SUM(K33+K35)-K36</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="172" t="s">
+        <v>35</v>
+      </c>
+      <c r="M37" s="110"/>
+    </row>
+    <row r="38" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A38" s="93"/>
+      <c r="B38" s="168"/>
+      <c r="C38" s="169"/>
+      <c r="D38" s="169"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="169"/>
+      <c r="J38" s="170"/>
+      <c r="K38" s="171"/>
+      <c r="L38" s="172"/>
+      <c r="M38" s="110"/>
+    </row>
+    <row r="39" spans="1:29" ht="15.75">
+      <c r="B39" s="163" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="163"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="163"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="163"/>
+      <c r="H39" s="163"/>
+      <c r="I39" s="163"/>
+      <c r="J39" s="163"/>
+      <c r="K39" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="M39" s="173"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+    </row>
+    <row r="40" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B40" s="149" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="149"/>
+      <c r="D40" s="149"/>
+      <c r="E40" s="149"/>
+      <c r="F40" s="149"/>
+      <c r="G40" s="149"/>
+      <c r="H40" s="149"/>
+      <c r="I40" s="149"/>
+      <c r="J40" s="149"/>
+      <c r="K40" s="37">
+        <f>K37</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40"/>
+      <c r="Z40"/>
+      <c r="AA40"/>
+      <c r="AB40"/>
+      <c r="AC40"/>
+    </row>
+    <row r="41" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B41" s="149" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="149"/>
+      <c r="D41" s="149"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
+      <c r="I41" s="149"/>
+      <c r="J41" s="149"/>
+      <c r="K41" s="37">
+        <f>K27</f>
+        <v>316.1151070046609</v>
+      </c>
+      <c r="L41" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="B42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K42" s="37">
+        <v>0</v>
+      </c>
+      <c r="L42" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="B43" s="159" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="159"/>
+      <c r="D43" s="159"/>
+      <c r="E43" s="159"/>
+      <c r="F43" s="159"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="159"/>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="37">
+        <v>0</v>
+      </c>
+      <c r="L43" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B44" s="147" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="60" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="37">
-        <f>K14</f>
-        <v>944.03</v>
-      </c>
-      <c r="L29" s="31" t="s">
+      <c r="C44" s="147"/>
+      <c r="D44" s="147"/>
+      <c r="E44" s="147"/>
+      <c r="F44" s="147"/>
+      <c r="G44" s="147"/>
+      <c r="H44" s="147"/>
+      <c r="I44" s="147"/>
+      <c r="J44" s="147"/>
+      <c r="K44" s="76">
+        <f>SUM(K40:K43)</f>
+        <v>316.1151070046609</v>
+      </c>
+      <c r="L44" s="75" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
-      <c r="B30" s="93" t="s">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B45" s="162"/>
+      <c r="C45" s="162"/>
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="162"/>
+      <c r="L45" s="162"/>
+    </row>
+    <row r="46" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B46" s="137" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="93"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="37">
-        <f>+'2'!K22</f>
-        <v>415.79999999999995</v>
-      </c>
-      <c r="L30" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12">
-      <c r="B31" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="107"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="38">
-        <f>K26</f>
-        <v>316.1151070046609</v>
-      </c>
-      <c r="L31" s="34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12">
-      <c r="B32" s="106" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="106"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="37">
-        <f>SUM(K29:K31)</f>
-        <v>1675.9451070046607</v>
-      </c>
-      <c r="L32" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-    </row>
-    <row r="34" spans="2:13">
-      <c r="B34" s="114" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="115"/>
-      <c r="J34" s="115"/>
-      <c r="K34" s="115"/>
-      <c r="L34" s="116"/>
-    </row>
-    <row r="35" spans="2:13">
-      <c r="B35" s="46" t="s">
+      <c r="C46" s="138"/>
+      <c r="D46" s="138"/>
+      <c r="E46" s="138"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="138"/>
+      <c r="I46" s="138"/>
+      <c r="J46" s="138"/>
+      <c r="K46" s="138"/>
+      <c r="L46" s="139"/>
+    </row>
+    <row r="47" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B47" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="95" t="s">
+      <c r="C47" s="132" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="7" t="s">
+      <c r="D47" s="133"/>
+      <c r="E47" s="134"/>
+      <c r="F47" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G35" s="95" t="s">
+      <c r="G47" s="132" t="s">
         <v>80</v>
       </c>
-      <c r="H35" s="97"/>
-      <c r="I35" s="5" t="s">
+      <c r="H47" s="134"/>
+      <c r="I47" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J35" s="54" t="s">
+      <c r="J47" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="104" t="s">
+      <c r="K47" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="L35" s="104"/>
-    </row>
-    <row r="36" spans="2:13">
-      <c r="B36" s="46">
+      <c r="L47" s="161"/>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="B48" s="46">
         <v>1</v>
       </c>
-      <c r="C36" s="95" t="str">
+      <c r="C48" s="132" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D36" s="96"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="7">
-        <f>+'2'!$C$45</f>
+      <c r="D48" s="133"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="7">
+        <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G36" s="98">
+      <c r="G48" s="135">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H36" s="99"/>
-      <c r="I36" s="55">
-        <f>+'2'!$C$46</f>
+      <c r="H48" s="136"/>
+      <c r="I48" s="55">
+        <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
       </c>
-      <c r="J36" s="55">
-        <f t="shared" ref="J36" si="0">+F36*I36</f>
+      <c r="J48" s="55">
+        <f t="shared" ref="J48" si="0">+F48*I48</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K36" s="104">
-        <f t="shared" ref="K36" si="1">I36*3.7</f>
+      <c r="K48" s="131">
+        <f t="shared" ref="K48" si="1">I48*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L36" s="104"/>
-    </row>
-    <row r="37" spans="2:13" ht="15.75">
-      <c r="B37" s="49" t="s">
+      <c r="L48" s="131"/>
+    </row>
+    <row r="49" spans="2:13" ht="15.75">
+      <c r="B49" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="36">
-        <f>+SUM(F36:F36)</f>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="36">
+        <f>+SUM(F48:F48)</f>
         <v>100</v>
       </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="J37" s="56">
-        <f>+SUM(J36:J36)</f>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="J49" s="56">
+        <f>+SUM(J48:J48)</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K37" s="77"/>
-      <c r="L37" s="78"/>
-    </row>
-    <row r="38" spans="2:13" ht="15.75">
-      <c r="B38" s="49"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="78"/>
-    </row>
-    <row r="39" spans="2:13">
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="80"/>
-    </row>
-    <row r="40" spans="2:13" ht="18.75">
-      <c r="B40" s="61" t="s">
+      <c r="K49" s="77"/>
+      <c r="L49" s="78"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.75">
+      <c r="B50" s="49"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="78"/>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="79"/>
+      <c r="L51" s="80"/>
+    </row>
+    <row r="52" spans="2:13" ht="18.75">
+      <c r="B52" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-    </row>
-    <row r="41" spans="2:13" ht="18.75">
-      <c r="B41" s="94" t="s">
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+    </row>
+    <row r="53" spans="2:13" ht="18.75">
+      <c r="B53" s="142" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-    </row>
-    <row r="42" spans="2:13" ht="18.75">
-      <c r="B42" s="94" t="s">
+      <c r="C53" s="142"/>
+      <c r="D53" s="142"/>
+      <c r="E53" s="142"/>
+      <c r="F53" s="142"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="142"/>
+      <c r="I53" s="142"/>
+      <c r="J53" s="142"/>
+      <c r="K53" s="142"/>
+      <c r="L53" s="142"/>
+    </row>
+    <row r="54" spans="2:13" ht="18.75">
+      <c r="B54" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="94"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="94"/>
-      <c r="J42" s="94"/>
-      <c r="K42" s="94"/>
-      <c r="L42" s="94"/>
-    </row>
-    <row r="43" spans="2:13" ht="18.75">
-      <c r="B43" s="94" t="s">
+      <c r="C54" s="142"/>
+      <c r="D54" s="142"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="142"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="142"/>
+      <c r="I54" s="142"/>
+      <c r="J54" s="142"/>
+      <c r="K54" s="142"/>
+      <c r="L54" s="142"/>
+    </row>
+    <row r="55" spans="2:13" ht="18.75">
+      <c r="B55" s="142" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="94"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="94"/>
-      <c r="F43" s="94"/>
-      <c r="G43" s="94"/>
-      <c r="H43" s="94"/>
-      <c r="I43" s="94"/>
-      <c r="J43" s="94"/>
-      <c r="K43" s="94"/>
-      <c r="L43" s="94"/>
-    </row>
-    <row r="44" spans="2:13" ht="18.75">
-      <c r="B44" s="94" t="s">
+      <c r="C55" s="142"/>
+      <c r="D55" s="142"/>
+      <c r="E55" s="142"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="142"/>
+      <c r="I55" s="142"/>
+      <c r="J55" s="142"/>
+      <c r="K55" s="142"/>
+      <c r="L55" s="142"/>
+    </row>
+    <row r="56" spans="2:13" ht="18.75">
+      <c r="B56" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
-      <c r="F44" s="94"/>
-      <c r="G44" s="94"/>
-      <c r="H44" s="94"/>
-      <c r="I44" s="94"/>
-      <c r="J44" s="94"/>
-      <c r="K44" s="94"/>
-      <c r="L44" s="94"/>
-    </row>
-    <row r="45" spans="2:13" ht="18.75">
-      <c r="B45" s="94" t="s">
+      <c r="C56" s="142"/>
+      <c r="D56" s="142"/>
+      <c r="E56" s="142"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="142"/>
+      <c r="H56" s="142"/>
+      <c r="I56" s="142"/>
+      <c r="J56" s="142"/>
+      <c r="K56" s="142"/>
+      <c r="L56" s="142"/>
+    </row>
+    <row r="57" spans="2:13" ht="18.75">
+      <c r="B57" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="94"/>
-      <c r="G45" s="94"/>
-      <c r="H45" s="94"/>
-      <c r="I45" s="94"/>
-      <c r="J45" s="94"/>
-      <c r="K45" s="94"/>
-      <c r="L45" s="94"/>
-    </row>
-    <row r="46" spans="2:13">
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-    </row>
-    <row r="47" spans="2:13" ht="9" customHeight="1">
-      <c r="B47" s="92"/>
-      <c r="C47" s="92"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="92"/>
-      <c r="G47" s="92"/>
-      <c r="H47" s="92"/>
-      <c r="I47" s="92"/>
-      <c r="J47" s="92"/>
-      <c r="K47" s="92"/>
-      <c r="L47" s="92"/>
-      <c r="M47" s="92"/>
-    </row>
-    <row r="48" spans="2:13" ht="31.9" customHeight="1">
-      <c r="B48" s="92"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="108" t="s">
-        <v>122</v>
-      </c>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="108"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="108"/>
-      <c r="K48" s="108"/>
-      <c r="L48" s="108"/>
-      <c r="M48" s="108"/>
-    </row>
-    <row r="49" spans="2:12" ht="21" customHeight="1">
-      <c r="B49" s="92"/>
-      <c r="C49" s="92"/>
-      <c r="D49" s="111" t="s">
-        <v>123</v>
-      </c>
-      <c r="E49" s="111"/>
-      <c r="F49" s="111"/>
-      <c r="G49" s="111"/>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-    </row>
-    <row r="50" spans="2:12">
-      <c r="B50" s="92"/>
-      <c r="C50" s="92"/>
-    </row>
-    <row r="51" spans="2:12">
-      <c r="B51" s="92"/>
-      <c r="C51" s="92"/>
-    </row>
-    <row r="52" spans="2:12" ht="21">
-      <c r="B52" s="103" t="s">
+      <c r="C57" s="142"/>
+      <c r="D57" s="142"/>
+      <c r="E57" s="142"/>
+      <c r="F57" s="142"/>
+      <c r="G57" s="142"/>
+      <c r="H57" s="142"/>
+      <c r="I57" s="142"/>
+      <c r="J57" s="142"/>
+      <c r="K57" s="142"/>
+      <c r="L57" s="142"/>
+    </row>
+    <row r="58" spans="2:13">
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+    </row>
+    <row r="59" spans="2:13" ht="9" customHeight="1">
+      <c r="B59" s="120"/>
+      <c r="C59" s="120"/>
+      <c r="E59" s="120"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="120"/>
+      <c r="H59" s="120"/>
+      <c r="I59" s="120"/>
+      <c r="J59" s="120"/>
+      <c r="K59" s="120"/>
+      <c r="L59" s="120"/>
+      <c r="M59" s="120"/>
+    </row>
+    <row r="60" spans="2:13" ht="31.9" customHeight="1">
+      <c r="B60" s="120"/>
+      <c r="C60" s="120"/>
+      <c r="D60" s="156" t="s">
+        <v>120</v>
+      </c>
+      <c r="E60" s="156"/>
+      <c r="F60" s="156"/>
+      <c r="G60" s="156"/>
+      <c r="H60" s="156"/>
+      <c r="I60" s="156"/>
+      <c r="J60" s="156"/>
+      <c r="K60" s="156"/>
+      <c r="L60" s="156"/>
+      <c r="M60" s="156"/>
+    </row>
+    <row r="61" spans="2:13" ht="21" customHeight="1">
+      <c r="B61" s="120"/>
+      <c r="C61" s="120"/>
+      <c r="D61" s="128" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="128"/>
+      <c r="F61" s="128"/>
+      <c r="G61" s="128"/>
+      <c r="H61" s="128"/>
+      <c r="I61" s="128"/>
+    </row>
+    <row r="62" spans="2:13">
+      <c r="B62" s="120"/>
+      <c r="C62" s="120"/>
+    </row>
+    <row r="63" spans="2:13">
+      <c r="B63" s="120"/>
+      <c r="C63" s="120"/>
+    </row>
+    <row r="64" spans="2:13" ht="21">
+      <c r="B64" s="155" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="103"/>
-      <c r="D52" s="103"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="103"/>
-      <c r="G52" s="103"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="103"/>
-      <c r="K52" s="103"/>
-      <c r="L52" s="103"/>
-    </row>
-    <row r="54" spans="2:12">
-      <c r="B54" s="91" t="s">
+      <c r="C64" s="155"/>
+      <c r="D64" s="155"/>
+      <c r="E64" s="155"/>
+      <c r="F64" s="155"/>
+      <c r="G64" s="155"/>
+      <c r="H64" s="155"/>
+      <c r="I64" s="155"/>
+      <c r="J64" s="155"/>
+      <c r="K64" s="155"/>
+      <c r="L64" s="155"/>
+    </row>
+    <row r="66" spans="2:12">
+      <c r="B66" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="91"/>
-      <c r="D54" s="91"/>
-      <c r="E54" s="91"/>
-      <c r="F54" s="91"/>
-      <c r="G54" s="91"/>
-      <c r="H54" s="91"/>
-      <c r="I54" s="91"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-    </row>
-    <row r="55" spans="2:12">
-      <c r="B55" s="91" t="s">
+      <c r="C66" s="150"/>
+      <c r="D66" s="150"/>
+      <c r="E66" s="150"/>
+      <c r="F66" s="150"/>
+      <c r="G66" s="150"/>
+      <c r="H66" s="150"/>
+      <c r="I66" s="150"/>
+      <c r="J66" s="150"/>
+      <c r="K66" s="150"/>
+      <c r="L66" s="150"/>
+    </row>
+    <row r="67" spans="2:12">
+      <c r="B67" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="91"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="91"/>
-      <c r="F55" s="91"/>
-      <c r="G55" s="91"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="91"/>
-      <c r="J55" s="91"/>
-      <c r="K55" s="91"/>
-      <c r="L55" s="91"/>
-    </row>
-    <row r="56" spans="2:12">
-      <c r="B56" s="93" t="s">
+      <c r="C67" s="150"/>
+      <c r="D67" s="150"/>
+      <c r="E67" s="150"/>
+      <c r="F67" s="150"/>
+      <c r="G67" s="150"/>
+      <c r="H67" s="150"/>
+      <c r="I67" s="150"/>
+      <c r="J67" s="150"/>
+      <c r="K67" s="150"/>
+      <c r="L67" s="150"/>
+    </row>
+    <row r="68" spans="2:12">
+      <c r="B68" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="93"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="93"/>
-      <c r="K56" s="93"/>
-      <c r="L56" s="93"/>
-    </row>
-    <row r="57" spans="2:12">
-      <c r="B57" s="91" t="s">
+      <c r="C68" s="149"/>
+      <c r="D68" s="149"/>
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="149"/>
+      <c r="H68" s="149"/>
+      <c r="I68" s="149"/>
+      <c r="J68" s="149"/>
+      <c r="K68" s="149"/>
+      <c r="L68" s="149"/>
+    </row>
+    <row r="69" spans="2:12">
+      <c r="B69" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="91"/>
-      <c r="D57" s="91"/>
-      <c r="E57" s="91"/>
-      <c r="F57" s="91"/>
-      <c r="G57" s="91"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="91"/>
-      <c r="J57" s="91"/>
-      <c r="K57" s="91"/>
-      <c r="L57" s="91"/>
-    </row>
-    <row r="58" spans="2:12">
-      <c r="B58" s="91" t="s">
+      <c r="C69" s="150"/>
+      <c r="D69" s="150"/>
+      <c r="E69" s="150"/>
+      <c r="F69" s="150"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="150"/>
+      <c r="I69" s="150"/>
+      <c r="J69" s="150"/>
+      <c r="K69" s="150"/>
+      <c r="L69" s="150"/>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="B70" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="91"/>
-      <c r="D58" s="91"/>
-      <c r="E58" s="91"/>
-      <c r="F58" s="91"/>
-      <c r="G58" s="91"/>
-      <c r="H58" s="91"/>
-      <c r="I58" s="91"/>
-      <c r="J58" s="91"/>
-      <c r="K58" s="91"/>
-      <c r="L58" s="91"/>
-    </row>
-    <row r="59" spans="2:12">
-      <c r="B59" s="93" t="s">
+      <c r="C70" s="150"/>
+      <c r="D70" s="150"/>
+      <c r="E70" s="150"/>
+      <c r="F70" s="150"/>
+      <c r="G70" s="150"/>
+      <c r="H70" s="150"/>
+      <c r="I70" s="150"/>
+      <c r="J70" s="150"/>
+      <c r="K70" s="150"/>
+      <c r="L70" s="150"/>
+    </row>
+    <row r="71" spans="2:12">
+      <c r="B71" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="C59" s="93"/>
-      <c r="D59" s="93"/>
-      <c r="E59" s="93"/>
-      <c r="F59" s="93"/>
-      <c r="G59" s="93"/>
-      <c r="H59" s="93"/>
-      <c r="I59" s="93"/>
-      <c r="J59" s="93"/>
-      <c r="K59" s="93"/>
-      <c r="L59" s="93"/>
-    </row>
-    <row r="60" spans="2:12">
-      <c r="B60" s="91" t="s">
+      <c r="C71" s="149"/>
+      <c r="D71" s="149"/>
+      <c r="E71" s="149"/>
+      <c r="F71" s="149"/>
+      <c r="G71" s="149"/>
+      <c r="H71" s="149"/>
+      <c r="I71" s="149"/>
+      <c r="J71" s="149"/>
+      <c r="K71" s="149"/>
+      <c r="L71" s="149"/>
+    </row>
+    <row r="72" spans="2:12">
+      <c r="B72" s="150" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="91"/>
-      <c r="D60" s="91"/>
-      <c r="E60" s="91"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="91"/>
-      <c r="H60" s="91"/>
-      <c r="I60" s="91"/>
-      <c r="J60" s="91"/>
-      <c r="K60" s="91"/>
-      <c r="L60" s="91"/>
-    </row>
-    <row r="61" spans="2:12">
-      <c r="B61" s="91" t="s">
+      <c r="C72" s="150"/>
+      <c r="D72" s="150"/>
+      <c r="E72" s="150"/>
+      <c r="F72" s="150"/>
+      <c r="G72" s="150"/>
+      <c r="H72" s="150"/>
+      <c r="I72" s="150"/>
+      <c r="J72" s="150"/>
+      <c r="K72" s="150"/>
+      <c r="L72" s="150"/>
+    </row>
+    <row r="73" spans="2:12">
+      <c r="B73" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="91"/>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
-      <c r="F61" s="91"/>
-      <c r="G61" s="91"/>
-      <c r="H61" s="91"/>
-      <c r="I61" s="91"/>
-      <c r="J61" s="91"/>
-      <c r="K61" s="91"/>
-      <c r="L61" s="91"/>
-    </row>
-    <row r="62" spans="2:12">
-      <c r="B62" s="91" t="s">
+      <c r="C73" s="150"/>
+      <c r="D73" s="150"/>
+      <c r="E73" s="150"/>
+      <c r="F73" s="150"/>
+      <c r="G73" s="150"/>
+      <c r="H73" s="150"/>
+      <c r="I73" s="150"/>
+      <c r="J73" s="150"/>
+      <c r="K73" s="150"/>
+      <c r="L73" s="150"/>
+    </row>
+    <row r="74" spans="2:12">
+      <c r="B74" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="C62" s="91"/>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="91"/>
-      <c r="G62" s="91"/>
-      <c r="H62" s="91"/>
-      <c r="I62" s="91"/>
-      <c r="J62" s="91"/>
-      <c r="K62" s="91"/>
-      <c r="L62" s="91"/>
-    </row>
-    <row r="63" spans="2:12">
-      <c r="B63" s="91" t="s">
+      <c r="C74" s="150"/>
+      <c r="D74" s="150"/>
+      <c r="E74" s="150"/>
+      <c r="F74" s="150"/>
+      <c r="G74" s="150"/>
+      <c r="H74" s="150"/>
+      <c r="I74" s="150"/>
+      <c r="J74" s="150"/>
+      <c r="K74" s="150"/>
+      <c r="L74" s="150"/>
+    </row>
+    <row r="75" spans="2:12">
+      <c r="B75" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="91"/>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="91"/>
-      <c r="G63" s="91"/>
-      <c r="H63" s="91"/>
-      <c r="I63" s="91"/>
-      <c r="J63" s="91"/>
-      <c r="K63" s="91"/>
-      <c r="L63" s="91"/>
-    </row>
-    <row r="64" spans="2:12">
-      <c r="B64" s="91" t="s">
+      <c r="C75" s="150"/>
+      <c r="D75" s="150"/>
+      <c r="E75" s="150"/>
+      <c r="F75" s="150"/>
+      <c r="G75" s="150"/>
+      <c r="H75" s="150"/>
+      <c r="I75" s="150"/>
+      <c r="J75" s="150"/>
+      <c r="K75" s="150"/>
+      <c r="L75" s="150"/>
+    </row>
+    <row r="76" spans="2:12">
+      <c r="B76" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="91"/>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="91"/>
-      <c r="G64" s="91"/>
-      <c r="H64" s="91"/>
-      <c r="I64" s="91"/>
-      <c r="J64" s="91"/>
-      <c r="K64" s="91"/>
-      <c r="L64" s="91"/>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="B65" s="91" t="s">
+      <c r="C76" s="150"/>
+      <c r="D76" s="150"/>
+      <c r="E76" s="150"/>
+      <c r="F76" s="150"/>
+      <c r="G76" s="150"/>
+      <c r="H76" s="150"/>
+      <c r="I76" s="150"/>
+      <c r="J76" s="150"/>
+      <c r="K76" s="150"/>
+      <c r="L76" s="150"/>
+    </row>
+    <row r="77" spans="2:12">
+      <c r="B77" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="C65" s="91"/>
-      <c r="D65" s="91"/>
-      <c r="E65" s="91"/>
-      <c r="F65" s="91"/>
-      <c r="G65" s="91"/>
-      <c r="H65" s="91"/>
-      <c r="I65" s="91"/>
-      <c r="J65" s="91"/>
-      <c r="K65" s="91"/>
-      <c r="L65" s="91"/>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="B66" s="91" t="s">
+      <c r="C77" s="150"/>
+      <c r="D77" s="150"/>
+      <c r="E77" s="150"/>
+      <c r="F77" s="150"/>
+      <c r="G77" s="150"/>
+      <c r="H77" s="150"/>
+      <c r="I77" s="150"/>
+      <c r="J77" s="150"/>
+      <c r="K77" s="150"/>
+      <c r="L77" s="150"/>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="C66" s="91"/>
-      <c r="D66" s="91"/>
-      <c r="E66" s="91"/>
-      <c r="F66" s="91"/>
-      <c r="G66" s="91"/>
-      <c r="H66" s="91"/>
-      <c r="I66" s="91"/>
-      <c r="J66" s="91"/>
-      <c r="K66" s="91"/>
-      <c r="L66" s="91"/>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="B67" s="91" t="s">
+      <c r="C78" s="150"/>
+      <c r="D78" s="150"/>
+      <c r="E78" s="150"/>
+      <c r="F78" s="150"/>
+      <c r="G78" s="150"/>
+      <c r="H78" s="150"/>
+      <c r="I78" s="150"/>
+      <c r="J78" s="150"/>
+      <c r="K78" s="150"/>
+      <c r="L78" s="150"/>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79" s="150" t="s">
         <v>63</v>
       </c>
-      <c r="C67" s="91"/>
-      <c r="D67" s="91"/>
-      <c r="E67" s="91"/>
-      <c r="F67" s="91"/>
-      <c r="G67" s="91"/>
-      <c r="H67" s="91"/>
-      <c r="I67" s="91"/>
-      <c r="J67" s="91"/>
-      <c r="K67" s="91"/>
-      <c r="L67" s="91"/>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="B68" s="91" t="s">
+      <c r="C79" s="150"/>
+      <c r="D79" s="150"/>
+      <c r="E79" s="150"/>
+      <c r="F79" s="150"/>
+      <c r="G79" s="150"/>
+      <c r="H79" s="150"/>
+      <c r="I79" s="150"/>
+      <c r="J79" s="150"/>
+      <c r="K79" s="150"/>
+      <c r="L79" s="150"/>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="B80" s="150" t="s">
         <v>64</v>
       </c>
-      <c r="C68" s="91"/>
-      <c r="D68" s="91"/>
-      <c r="E68" s="91"/>
-      <c r="F68" s="91"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="91"/>
-      <c r="I68" s="91"/>
-      <c r="J68" s="91"/>
-      <c r="K68" s="91"/>
-      <c r="L68" s="91"/>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="B69" s="91" t="s">
+      <c r="C80" s="150"/>
+      <c r="D80" s="150"/>
+      <c r="E80" s="150"/>
+      <c r="F80" s="150"/>
+      <c r="G80" s="150"/>
+      <c r="H80" s="150"/>
+      <c r="I80" s="150"/>
+      <c r="J80" s="150"/>
+      <c r="K80" s="150"/>
+      <c r="L80" s="150"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="B81" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="C69" s="91"/>
-      <c r="D69" s="91"/>
-      <c r="E69" s="91"/>
-      <c r="F69" s="91"/>
-      <c r="G69" s="91"/>
-      <c r="H69" s="91"/>
-      <c r="I69" s="91"/>
-      <c r="J69" s="91"/>
-      <c r="K69" s="91"/>
-      <c r="L69" s="91"/>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="B70" s="91" t="s">
+      <c r="C81" s="150"/>
+      <c r="D81" s="150"/>
+      <c r="E81" s="150"/>
+      <c r="F81" s="150"/>
+      <c r="G81" s="150"/>
+      <c r="H81" s="150"/>
+      <c r="I81" s="150"/>
+      <c r="J81" s="150"/>
+      <c r="K81" s="150"/>
+      <c r="L81" s="150"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="B82" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="C70" s="91"/>
-      <c r="D70" s="91"/>
-      <c r="E70" s="91"/>
-      <c r="F70" s="91"/>
-      <c r="G70" s="91"/>
-      <c r="H70" s="91"/>
-      <c r="I70" s="91"/>
-      <c r="J70" s="91"/>
-      <c r="K70" s="91"/>
-      <c r="L70" s="91"/>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="B71" s="90" t="s">
+      <c r="C82" s="150"/>
+      <c r="D82" s="150"/>
+      <c r="E82" s="150"/>
+      <c r="F82" s="150"/>
+      <c r="G82" s="150"/>
+      <c r="H82" s="150"/>
+      <c r="I82" s="150"/>
+      <c r="J82" s="150"/>
+      <c r="K82" s="150"/>
+      <c r="L82" s="150"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="B83" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="90"/>
-      <c r="D71" s="90"/>
-      <c r="E71" s="90"/>
-      <c r="F71" s="90"/>
-      <c r="G71" s="90"/>
-      <c r="H71" s="90"/>
-      <c r="I71" s="90"/>
-      <c r="J71" s="90"/>
-      <c r="K71" s="90"/>
-      <c r="L71" s="90"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="B72" s="91" t="s">
+      <c r="C83" s="146"/>
+      <c r="D83" s="146"/>
+      <c r="E83" s="146"/>
+      <c r="F83" s="146"/>
+      <c r="G83" s="146"/>
+      <c r="H83" s="146"/>
+      <c r="I83" s="146"/>
+      <c r="J83" s="146"/>
+      <c r="K83" s="146"/>
+      <c r="L83" s="146"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="B84" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="C72" s="91"/>
-      <c r="D72" s="91"/>
-      <c r="E72" s="91"/>
-      <c r="F72" s="91"/>
-      <c r="G72" s="91"/>
-      <c r="H72" s="91"/>
-      <c r="I72" s="91"/>
-      <c r="J72" s="91"/>
-      <c r="K72" s="91"/>
-      <c r="L72" s="91"/>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="B73" s="90" t="s">
+      <c r="C84" s="150"/>
+      <c r="D84" s="150"/>
+      <c r="E84" s="150"/>
+      <c r="F84" s="150"/>
+      <c r="G84" s="150"/>
+      <c r="H84" s="150"/>
+      <c r="I84" s="150"/>
+      <c r="J84" s="150"/>
+      <c r="K84" s="150"/>
+      <c r="L84" s="150"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="B85" s="146" t="s">
         <v>51</v>
       </c>
-      <c r="C73" s="90"/>
-      <c r="D73" s="90"/>
-      <c r="E73" s="90"/>
-      <c r="F73" s="90"/>
-      <c r="G73" s="90"/>
-      <c r="H73" s="90"/>
-      <c r="I73" s="90"/>
-      <c r="J73" s="90"/>
-      <c r="K73" s="90"/>
-      <c r="L73" s="90"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="B74" s="91" t="s">
+      <c r="C85" s="146"/>
+      <c r="D85" s="146"/>
+      <c r="E85" s="146"/>
+      <c r="F85" s="146"/>
+      <c r="G85" s="146"/>
+      <c r="H85" s="146"/>
+      <c r="I85" s="146"/>
+      <c r="J85" s="146"/>
+      <c r="K85" s="146"/>
+      <c r="L85" s="146"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="B86" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="91"/>
-      <c r="D74" s="91"/>
-      <c r="E74" s="91"/>
-      <c r="F74" s="91"/>
-      <c r="G74" s="91"/>
-      <c r="H74" s="91"/>
-      <c r="I74" s="91"/>
-      <c r="J74" s="91"/>
-      <c r="K74" s="91"/>
-      <c r="L74" s="91"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="B75" s="91" t="s">
+      <c r="C86" s="150"/>
+      <c r="D86" s="150"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="150"/>
+      <c r="G86" s="150"/>
+      <c r="H86" s="150"/>
+      <c r="I86" s="150"/>
+      <c r="J86" s="150"/>
+      <c r="K86" s="150"/>
+      <c r="L86" s="150"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="B87" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="91"/>
-      <c r="D75" s="91"/>
-      <c r="E75" s="91"/>
-      <c r="F75" s="91"/>
-      <c r="G75" s="91"/>
-      <c r="H75" s="91"/>
-      <c r="I75" s="91"/>
-      <c r="J75" s="91"/>
-      <c r="K75" s="91"/>
-      <c r="L75" s="91"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="B76" s="91" t="s">
+      <c r="C87" s="150"/>
+      <c r="D87" s="150"/>
+      <c r="E87" s="150"/>
+      <c r="F87" s="150"/>
+      <c r="G87" s="150"/>
+      <c r="H87" s="150"/>
+      <c r="I87" s="150"/>
+      <c r="J87" s="150"/>
+      <c r="K87" s="150"/>
+      <c r="L87" s="150"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="B88" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="91"/>
-      <c r="D76" s="91"/>
-      <c r="E76" s="91"/>
-      <c r="F76" s="91"/>
-      <c r="G76" s="91"/>
-      <c r="H76" s="91"/>
-      <c r="I76" s="91"/>
-      <c r="J76" s="91"/>
-      <c r="K76" s="91"/>
-      <c r="L76" s="91"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="B77" s="91" t="s">
+      <c r="C88" s="150"/>
+      <c r="D88" s="150"/>
+      <c r="E88" s="150"/>
+      <c r="F88" s="150"/>
+      <c r="G88" s="150"/>
+      <c r="H88" s="150"/>
+      <c r="I88" s="150"/>
+      <c r="J88" s="150"/>
+      <c r="K88" s="150"/>
+      <c r="L88" s="150"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="B89" s="150" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="91"/>
-      <c r="D77" s="91"/>
-      <c r="E77" s="91"/>
-      <c r="F77" s="91"/>
-      <c r="G77" s="91"/>
-      <c r="H77" s="91"/>
-      <c r="I77" s="91"/>
-      <c r="J77" s="91"/>
-      <c r="K77" s="91"/>
-      <c r="L77" s="91"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="B78" s="91" t="s">
+      <c r="C89" s="150"/>
+      <c r="D89" s="150"/>
+      <c r="E89" s="150"/>
+      <c r="F89" s="150"/>
+      <c r="G89" s="150"/>
+      <c r="H89" s="150"/>
+      <c r="I89" s="150"/>
+      <c r="J89" s="150"/>
+      <c r="K89" s="150"/>
+      <c r="L89" s="150"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="C78" s="91"/>
-      <c r="D78" s="91"/>
-      <c r="E78" s="91"/>
-      <c r="F78" s="91"/>
-      <c r="G78" s="91"/>
-      <c r="H78" s="91"/>
-      <c r="I78" s="91"/>
-      <c r="J78" s="91"/>
-      <c r="K78" s="91"/>
-      <c r="L78" s="91"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" s="85"/>
-      <c r="B79" s="101" t="s">
+      <c r="C90" s="150"/>
+      <c r="D90" s="150"/>
+      <c r="E90" s="150"/>
+      <c r="F90" s="150"/>
+      <c r="G90" s="150"/>
+      <c r="H90" s="150"/>
+      <c r="I90" s="150"/>
+      <c r="J90" s="150"/>
+      <c r="K90" s="150"/>
+      <c r="L90" s="150"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="85"/>
+      <c r="B91" s="151" t="s">
         <v>84</v>
       </c>
-      <c r="C79" s="101"/>
-      <c r="D79" s="101"/>
-      <c r="E79" s="101"/>
-      <c r="F79" s="101"/>
-      <c r="G79" s="101"/>
-      <c r="H79" s="101"/>
-      <c r="I79" s="101"/>
-      <c r="J79" s="101"/>
-      <c r="K79" s="101"/>
-      <c r="L79" s="101"/>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" s="85"/>
-      <c r="B80" s="91" t="s">
+      <c r="C91" s="151"/>
+      <c r="D91" s="151"/>
+      <c r="E91" s="151"/>
+      <c r="F91" s="151"/>
+      <c r="G91" s="151"/>
+      <c r="H91" s="151"/>
+      <c r="I91" s="151"/>
+      <c r="J91" s="151"/>
+      <c r="K91" s="151"/>
+      <c r="L91" s="151"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="85"/>
+      <c r="B92" s="150" t="s">
         <v>85</v>
       </c>
-      <c r="C80" s="91"/>
-      <c r="D80" s="91"/>
-      <c r="E80" s="91"/>
-      <c r="F80" s="91"/>
-      <c r="G80" s="91"/>
-      <c r="H80" s="91"/>
-      <c r="I80" s="91"/>
-      <c r="J80" s="91"/>
-      <c r="K80" s="91"/>
-      <c r="L80" s="91"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" s="85"/>
-      <c r="B81" s="101" t="s">
+      <c r="C92" s="150"/>
+      <c r="D92" s="150"/>
+      <c r="E92" s="150"/>
+      <c r="F92" s="150"/>
+      <c r="G92" s="150"/>
+      <c r="H92" s="150"/>
+      <c r="I92" s="150"/>
+      <c r="J92" s="150"/>
+      <c r="K92" s="150"/>
+      <c r="L92" s="150"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="85"/>
+      <c r="B93" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="C81" s="101"/>
-      <c r="D81" s="101"/>
-      <c r="E81" s="101"/>
-      <c r="F81" s="101"/>
-      <c r="G81" s="101"/>
-      <c r="H81" s="101"/>
-      <c r="I81" s="101"/>
-      <c r="J81" s="101"/>
-      <c r="K81" s="101"/>
-      <c r="L81" s="101"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="C83" s="92"/>
-      <c r="D83" s="92"/>
-      <c r="E83" s="92"/>
-      <c r="F83" s="92"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
-      <c r="I83" s="92"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="C84" s="92"/>
-      <c r="D84" s="92"/>
-      <c r="E84" s="92"/>
-      <c r="F84" s="92"/>
-      <c r="G84" s="92"/>
-      <c r="H84" s="92"/>
-      <c r="I84" s="92"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="C85" s="92"/>
-      <c r="D85" s="92"/>
-      <c r="E85" s="92"/>
-      <c r="F85" s="92"/>
-      <c r="G85" s="92"/>
-      <c r="H85" s="92"/>
-      <c r="I85" s="92"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="C86" s="92"/>
-      <c r="D86" s="92"/>
-      <c r="E86" s="92"/>
-      <c r="F86" s="92"/>
-      <c r="G86" s="92"/>
-      <c r="H86" s="92"/>
-      <c r="I86" s="92"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="C87" s="92"/>
-      <c r="D87" s="92"/>
-      <c r="E87" s="92"/>
-      <c r="F87" s="92"/>
-      <c r="G87" s="92"/>
-      <c r="H87" s="92"/>
-      <c r="I87" s="92"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="C88" s="92"/>
-      <c r="D88" s="92"/>
-      <c r="E88" s="92"/>
-      <c r="F88" s="92"/>
-      <c r="G88" s="92"/>
-      <c r="H88" s="92"/>
-      <c r="I88" s="92"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="C89" s="92"/>
-      <c r="D89" s="92"/>
-      <c r="E89" s="92"/>
-      <c r="F89" s="92"/>
-      <c r="G89" s="92"/>
-      <c r="H89" s="92"/>
-      <c r="I89" s="92"/>
-    </row>
-    <row r="90" spans="1:12" ht="15.6" customHeight="1">
-      <c r="C90" s="92"/>
-      <c r="D90" s="92"/>
-      <c r="E90" s="92"/>
-      <c r="F90" s="92"/>
-      <c r="G90" s="92"/>
-      <c r="H90" s="92"/>
-      <c r="I90" s="92"/>
-    </row>
-    <row r="91" spans="1:12" ht="15.6" customHeight="1">
-      <c r="C91" s="92"/>
-      <c r="D91" s="92"/>
-      <c r="E91" s="92"/>
-      <c r="F91" s="92"/>
-      <c r="G91" s="92"/>
-      <c r="H91" s="92"/>
-      <c r="I91" s="92"/>
-    </row>
-    <row r="92" spans="1:12">
-      <c r="C92" s="92"/>
-      <c r="D92" s="92"/>
-      <c r="E92" s="92"/>
-      <c r="F92" s="92"/>
-      <c r="G92" s="92"/>
-      <c r="H92" s="92"/>
-      <c r="I92" s="92"/>
-    </row>
-    <row r="98" ht="15.6" customHeight="1"/>
+      <c r="C93" s="151"/>
+      <c r="D93" s="151"/>
+      <c r="E93" s="151"/>
+      <c r="F93" s="151"/>
+      <c r="G93" s="151"/>
+      <c r="H93" s="151"/>
+      <c r="I93" s="151"/>
+      <c r="J93" s="151"/>
+      <c r="K93" s="151"/>
+      <c r="L93" s="151"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="C95" s="120"/>
+      <c r="D95" s="120"/>
+      <c r="E95" s="120"/>
+      <c r="F95" s="120"/>
+      <c r="G95" s="120"/>
+      <c r="H95" s="120"/>
+      <c r="I95" s="120"/>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="C96" s="120"/>
+      <c r="D96" s="120"/>
+      <c r="E96" s="120"/>
+      <c r="F96" s="120"/>
+      <c r="G96" s="120"/>
+      <c r="H96" s="120"/>
+      <c r="I96" s="120"/>
+    </row>
+    <row r="97" spans="3:9">
+      <c r="C97" s="120"/>
+      <c r="D97" s="120"/>
+      <c r="E97" s="120"/>
+      <c r="F97" s="120"/>
+      <c r="G97" s="120"/>
+      <c r="H97" s="120"/>
+      <c r="I97" s="120"/>
+    </row>
+    <row r="98" spans="3:9">
+      <c r="C98" s="120"/>
+      <c r="D98" s="120"/>
+      <c r="E98" s="120"/>
+      <c r="F98" s="120"/>
+      <c r="G98" s="120"/>
+      <c r="H98" s="120"/>
+      <c r="I98" s="120"/>
+    </row>
+    <row r="99" spans="3:9">
+      <c r="C99" s="120"/>
+      <c r="D99" s="120"/>
+      <c r="E99" s="120"/>
+      <c r="F99" s="120"/>
+      <c r="G99" s="120"/>
+      <c r="H99" s="120"/>
+      <c r="I99" s="120"/>
+    </row>
+    <row r="100" spans="3:9">
+      <c r="C100" s="120"/>
+      <c r="D100" s="120"/>
+      <c r="E100" s="120"/>
+      <c r="F100" s="120"/>
+      <c r="G100" s="120"/>
+      <c r="H100" s="120"/>
+      <c r="I100" s="120"/>
+    </row>
+    <row r="101" spans="3:9">
+      <c r="C101" s="120"/>
+      <c r="D101" s="120"/>
+      <c r="E101" s="120"/>
+      <c r="F101" s="120"/>
+      <c r="G101" s="120"/>
+      <c r="H101" s="120"/>
+      <c r="I101" s="120"/>
+    </row>
+    <row r="102" spans="3:9" ht="15.6" customHeight="1">
+      <c r="C102" s="120"/>
+      <c r="D102" s="120"/>
+      <c r="E102" s="120"/>
+      <c r="F102" s="120"/>
+      <c r="G102" s="120"/>
+      <c r="H102" s="120"/>
+      <c r="I102" s="120"/>
+    </row>
+    <row r="103" spans="3:9" ht="15.6" customHeight="1">
+      <c r="C103" s="120"/>
+      <c r="D103" s="120"/>
+      <c r="E103" s="120"/>
+      <c r="F103" s="120"/>
+      <c r="G103" s="120"/>
+      <c r="H103" s="120"/>
+      <c r="I103" s="120"/>
+    </row>
+    <row r="104" spans="3:9">
+      <c r="C104" s="120"/>
+      <c r="D104" s="120"/>
+      <c r="E104" s="120"/>
+      <c r="F104" s="120"/>
+      <c r="G104" s="120"/>
+      <c r="H104" s="120"/>
+      <c r="I104" s="120"/>
+    </row>
+    <row r="110" spans="3:9" ht="15.6" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="83">
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
+  <mergeCells count="86">
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B84:L84"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="E59:M59"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="B59:C63"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="D60:J60"/>
+    <mergeCell ref="K60:M60"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B45:L45"/>
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B66:L66"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="B93:L93"/>
+    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B92:L92"/>
+    <mergeCell ref="B91:L91"/>
+    <mergeCell ref="B90:L90"/>
+    <mergeCell ref="B85:L85"/>
+    <mergeCell ref="B86:L86"/>
+    <mergeCell ref="B87:L87"/>
+    <mergeCell ref="B88:L88"/>
+    <mergeCell ref="B89:L89"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="C95:I104"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B2:C6"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="C83:I92"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D49:I49"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="B52:L52"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="E47:M47"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="B78:L78"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B74:L74"/>
-    <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B76:L76"/>
-    <mergeCell ref="B77:L77"/>
-    <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B64:L64"/>
-    <mergeCell ref="B65:L65"/>
-    <mergeCell ref="B66:L66"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B59:L59"/>
-    <mergeCell ref="B60:L60"/>
-    <mergeCell ref="B61:L61"/>
-    <mergeCell ref="B62:L62"/>
-    <mergeCell ref="B63:L63"/>
-    <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B72:L72"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="I7:L7"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="B45:L45"/>
-    <mergeCell ref="B41:L41"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="B47:C51"/>
-    <mergeCell ref="B19:F19"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="VERIFICAR NÚMERO DE TELEFONO" error="Verifica que tenga 9 digitos sin espacio" sqref="J8:L8" xr:uid="{CC0405B2-A74A-4E8F-BF03-C34BEE695B67}">
       <formula1>(LEN(C11)=9)</formula1>
     </dataValidation>
@@ -3301,13 +3906,13 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="71" fitToWidth="2" fitToHeight="2" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="46" max="12" man="1"/>
+    <brk id="58" max="12" man="1"/>
   </rowBreaks>
   <cellWatches>
-    <cellWatch r="K16"/>
+    <cellWatch r="K17"/>
   </cellWatches>
   <ignoredErrors>
-    <ignoredError sqref="J25" numberStoredAsText="1"/>
+    <ignoredError sqref="J26" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -3316,7 +3921,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A3:AG49"/>
+  <dimension ref="A3:AG50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
@@ -3331,27 +3936,27 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
       <c r="B6" s="70" t="s">
         <v>88</v>
       </c>
       <c r="C6" s="70" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="70" t="s">
         <v>104</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>106</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>8</v>
@@ -3388,14 +3993,14 @@
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="129" t="s">
+      <c r="J8" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="129"/>
-      <c r="M8" s="129" t="s">
-        <v>109</v>
-      </c>
-      <c r="N8" s="129"/>
+      <c r="K8" s="164"/>
+      <c r="M8" s="164" t="s">
+        <v>107</v>
+      </c>
+      <c r="N8" s="164"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
@@ -3451,13 +4056,13 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K10" s="72">
         <v>250</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N10" s="72">
         <v>250</v>
@@ -3517,13 +4122,13 @@
       </c>
       <c r="G12" s="1"/>
       <c r="J12" s="58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K12" s="72">
         <v>350</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N12" s="72">
         <v>325</v>
@@ -3559,13 +4164,13 @@
       </c>
       <c r="G13" s="1"/>
       <c r="J13" s="58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K13" s="72">
         <v>350</v>
       </c>
       <c r="M13" s="58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N13" s="72">
         <v>325</v>
@@ -3638,13 +4243,13 @@
       </c>
       <c r="G15" s="28"/>
       <c r="J15" s="58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K15" s="72">
         <v>325</v>
       </c>
       <c r="M15" s="58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N15" s="72">
         <v>300</v>
@@ -3680,13 +4285,13 @@
       </c>
       <c r="G16" s="59"/>
       <c r="J16" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K16" s="72">
         <v>300</v>
       </c>
       <c r="M16" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N16" s="72">
         <v>275</v>
@@ -3722,13 +4327,13 @@
       </c>
       <c r="G17" s="1"/>
       <c r="J17" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K17" s="72">
         <v>280</v>
       </c>
       <c r="M17" s="58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N17" s="72">
         <v>250</v>
@@ -3829,7 +4434,7 @@
         <v>89</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Y20"/>
       <c r="Z20"/>
@@ -3868,21 +4473,21 @@
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -3935,56 +4540,41 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:33">
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="116" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="117">
+        <v>0</v>
+      </c>
+      <c r="D28" s="118">
+        <f>ROUND((MAX(D17:D18)+D26)*D27,10)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="10">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:33">
+      <c r="B29" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C29" s="13">
         <f>((MAX(C20:C21))+C27)*16%</f>
         <v>139.40357902185312</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D29" s="13">
         <f>((MAX(D20:D21))+D27)*16%</f>
         <v>1.6923844030380388</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E29" s="13">
         <f>((MAX(E20:E21))+E27)*16%</f>
         <v>63.227312691333957</v>
       </c>
-      <c r="F28" s="10">
-        <f>SUM(C28:E28)</f>
-        <v>204.32327611622512</v>
-      </c>
-      <c r="G28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28"/>
-      <c r="AB28"/>
-      <c r="AC28"/>
-      <c r="AD28"/>
-      <c r="AE28"/>
-      <c r="AF28"/>
-    </row>
-    <row r="29" spans="1:33">
-      <c r="B29" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="15">
-        <f>((MAX(C20:C21))+C27)*2%</f>
-        <v>17.42544737773164</v>
-      </c>
-      <c r="D29" s="15">
-        <f>((MAX(D20:D21))+D27)*2%</f>
-        <v>0.21154805037975485</v>
-      </c>
-      <c r="E29" s="15">
-        <f>((MAX(E20:E21))+E27)*2%</f>
-        <v>7.9034140864167446</v>
-      </c>
       <c r="F29" s="10">
         <f>SUM(C29:E29)</f>
-        <v>25.54040951452814</v>
+        <v>204.32327611622512</v>
       </c>
       <c r="G29" s="12"/>
       <c r="J29" s="12"/>
@@ -3998,76 +4588,64 @@
       <c r="AE29"/>
       <c r="AF29"/>
     </row>
-    <row r="30" spans="1:33" s="14" customFormat="1">
-      <c r="A30" s="12"/>
+    <row r="30" spans="1:33">
       <c r="B30" s="16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C30" s="15">
-        <f>(C20+C27+C28+C29)*3.5%</f>
-        <v>35.983548835015839</v>
+        <f>((MAX(C20:C21))+C27)*2%</f>
+        <v>17.42544737773164</v>
       </c>
       <c r="D30" s="15">
-        <f>(D20+D27+D28+D29)*3.5%</f>
-        <v>0.43684672403419378</v>
+        <f>((MAX(D20:D21))+D27)*2%</f>
+        <v>0.21154805037975485</v>
       </c>
       <c r="E30" s="15">
-        <f>(E20+E27+E28+E29)*3.5%</f>
-        <v>16.320550088450577</v>
+        <f>((MAX(E20:E21))+E27)*2%</f>
+        <v>7.9034140864167446</v>
       </c>
       <c r="F30" s="10">
         <f>SUM(C30:E30)</f>
-        <v>52.74094564750061</v>
+        <v>25.54040951452814</v>
       </c>
       <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
+      <c r="Y30"/>
+      <c r="Z30"/>
+      <c r="AA30"/>
+      <c r="AB30"/>
+      <c r="AC30"/>
+      <c r="AD30"/>
+      <c r="AE30"/>
+      <c r="AF30"/>
     </row>
     <row r="31" spans="1:33" s="14" customFormat="1">
       <c r="A31" s="12"/>
-      <c r="B31" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="20">
-        <f t="shared" ref="C31:E31" si="5">SUM(C27:C30)</f>
-        <v>226.3230509610076</v>
-      </c>
-      <c r="D31" s="20">
-        <f t="shared" si="5"/>
-        <v>2.3407791774519877</v>
-      </c>
-      <c r="E31" s="20">
-        <f t="shared" si="5"/>
-        <v>87.451276866201269</v>
-      </c>
-      <c r="F31" s="18">
+      <c r="B31" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="15">
+        <f>(C20+C27+C29+C30)*3.5%</f>
+        <v>35.983548835015839</v>
+      </c>
+      <c r="D31" s="15">
+        <f>(D20+D27+D29+D30)*3.5%</f>
+        <v>0.43684672403419378</v>
+      </c>
+      <c r="E31" s="15">
+        <f>(E20+E27+E29+E30)*3.5%</f>
+        <v>16.320550088450577</v>
+      </c>
+      <c r="F31" s="10">
         <f>SUM(C31:E31)</f>
-        <v>316.11510700466084</v>
-      </c>
-      <c r="G31" s="1"/>
+        <v>52.74094564750061</v>
+      </c>
+      <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="K31" s="5">
-        <v>3.7</v>
-      </c>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
@@ -4084,16 +4662,34 @@
     </row>
     <row r="32" spans="1:33" s="14" customFormat="1">
       <c r="A32" s="12"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="B32" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="20">
+        <f t="shared" ref="C32:E32" si="5">SUM(C27:C31)</f>
+        <v>226.3230509610076</v>
+      </c>
+      <c r="D32" s="20">
+        <f t="shared" si="5"/>
+        <v>2.3407791774519877</v>
+      </c>
+      <c r="E32" s="20">
+        <f t="shared" si="5"/>
+        <v>87.451276866201269</v>
+      </c>
+      <c r="F32" s="18">
+        <f>SUM(C32:E32)</f>
+        <v>316.11510700466084</v>
+      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="J32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="5">
+        <v>3.7</v>
+      </c>
       <c r="L32" s="12"/>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
@@ -4108,87 +4704,103 @@
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="1:32">
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
+    <row r="33" spans="1:32" s="14" customFormat="1">
+      <c r="A33" s="12"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
     </row>
     <row r="34" spans="1:32">
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+      <c r="AB34"/>
+      <c r="AC34"/>
       <c r="AD34"/>
       <c r="AE34"/>
       <c r="AF34"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="B35" s="132" t="s">
+      <c r="AD35"/>
+      <c r="AE35"/>
+      <c r="AF35"/>
+    </row>
+    <row r="36" spans="1:32">
+      <c r="B36" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-    </row>
-    <row r="37" spans="1:32">
-      <c r="C37" s="21">
+      <c r="C36" s="167"/>
+      <c r="D36" s="167"/>
+      <c r="E36" s="167"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="167"/>
+    </row>
+    <row r="38" spans="1:32">
+      <c r="C38" s="21">
         <f>+C15</f>
         <v>0.67370740336641843</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D38" s="21">
         <f>+D15</f>
         <v>8.5060856116860682E-3</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E38" s="21">
         <f>+E15</f>
         <v>0.31778651102189548</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:32">
-      <c r="B38" s="26" t="s">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:32">
+      <c r="B39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="23">
-        <f>$F$38*C37</f>
+      <c r="C39" s="23">
+        <f>$F$39*C38</f>
         <v>112.0510153279027</v>
       </c>
-      <c r="D38" s="23">
-        <f>$F$38*D37</f>
+      <c r="D39" s="23">
+        <f>$F$39*D38</f>
         <v>1.4147321589356268</v>
       </c>
-      <c r="E38" s="23">
-        <f>$F$38*E37</f>
+      <c r="E39" s="23">
+        <f>$F$39*E38</f>
         <v>52.854252513161654</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F39" s="27">
         <f>+K25</f>
         <v>166.32</v>
       </c>
-      <c r="G38" s="59"/>
-    </row>
-    <row r="39" spans="1:32">
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39"/>
-      <c r="AB39"/>
-      <c r="AC39"/>
-      <c r="AD39"/>
-      <c r="AE39"/>
-      <c r="AF39"/>
+      <c r="G39" s="59"/>
     </row>
     <row r="40" spans="1:32">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
       <c r="Y40"/>
       <c r="Z40"/>
       <c r="AA40"/>
@@ -4198,97 +4810,81 @@
       <c r="AE40"/>
       <c r="AF40"/>
     </row>
-    <row r="41" spans="1:32" s="1" customFormat="1">
-      <c r="B41" s="71" t="s">
+    <row r="41" spans="1:32">
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41"/>
+      <c r="AF41"/>
+    </row>
+    <row r="42" spans="1:32" s="1" customFormat="1">
+      <c r="B42" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-    </row>
-    <row r="43" spans="1:32">
-      <c r="B43" s="25" t="s">
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+    </row>
+    <row r="44" spans="1:32">
+      <c r="B44" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="7" t="str">
+      <c r="C44" s="7" t="str">
         <f>C6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D43" s="7" t="str">
+      <c r="D44" s="7" t="str">
         <f>D6</f>
         <v>Car Headrest</v>
       </c>
-      <c r="E43" s="7" t="str">
+      <c r="E44" s="7" t="str">
         <f>E6</f>
         <v>Bluetooth sleep mask</v>
       </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:32">
-      <c r="B44" s="26" t="s">
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:32">
+      <c r="B45" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="23">
-        <f>C17+C31+C38</f>
+      <c r="C45" s="23">
+        <f>C17+C32+C39</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="D44" s="23">
-        <f t="shared" ref="D44:E44" si="6">D17+D31+D38</f>
+      <c r="D45" s="23">
+        <f t="shared" ref="D45:E45" si="6">D17+D32+D39</f>
         <v>13.907609574791055</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E45" s="23">
         <f t="shared" si="6"/>
         <v>519.5869081491054</v>
       </c>
-      <c r="F44" s="23">
-        <f>SUM(C44:E44)</f>
+      <c r="F45" s="23">
+        <f>SUM(C45:E45)</f>
         <v>1675.9451070046607</v>
       </c>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="1:32">
-      <c r="B45" s="5" t="s">
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:32">
+      <c r="B46" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C46" s="24">
         <f>+C12</f>
         <v>100</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D46" s="24">
         <f>+D12</f>
         <v>1</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E46" s="24">
         <f>+E12</f>
         <v>50</v>
-      </c>
-      <c r="G45" s="1"/>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
-      <c r="AE45"/>
-      <c r="AF45"/>
-    </row>
-    <row r="46" spans="1:32">
-      <c r="B46" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="23">
-        <f>C44/C45</f>
-        <v>11.424505892807643</v>
-      </c>
-      <c r="D46" s="23">
-        <f t="shared" ref="D46:E46" si="7">D44/D45</f>
-        <v>13.907609574791055</v>
-      </c>
-      <c r="E46" s="23">
-        <f t="shared" si="7"/>
-        <v>10.391738162982108</v>
       </c>
       <c r="G46" s="1"/>
       <c r="Y46"/>
@@ -4300,52 +4896,68 @@
       <c r="AE46"/>
       <c r="AF46"/>
     </row>
-    <row r="47" spans="1:32" s="84" customFormat="1">
-      <c r="A47" s="80"/>
-      <c r="B47" s="82" t="s">
+    <row r="47" spans="1:32">
+      <c r="B47" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="23">
+        <f>C45/C46</f>
+        <v>11.424505892807643</v>
+      </c>
+      <c r="D47" s="23">
+        <f t="shared" ref="D47:E47" si="7">D45/D46</f>
+        <v>13.907609574791055</v>
+      </c>
+      <c r="E47" s="23">
+        <f t="shared" si="7"/>
+        <v>10.391738162982108</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+      <c r="AF47"/>
+    </row>
+    <row r="48" spans="1:32" s="84" customFormat="1">
+      <c r="A48" s="80"/>
+      <c r="B48" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="81">
-        <f>C46*$K$31</f>
+      <c r="C48" s="81">
+        <f>C47*$K$32</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="D47" s="81">
-        <f t="shared" ref="D47:E47" si="8">D46*$K$31</f>
+      <c r="D48" s="81">
+        <f t="shared" ref="D48:E48" si="8">D47*$K$32</f>
         <v>51.458155426726904</v>
       </c>
-      <c r="E47" s="81">
+      <c r="E48" s="81">
         <f t="shared" si="8"/>
         <v>38.449431203033804</v>
       </c>
-      <c r="F47" s="83"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
-      <c r="M47" s="80"/>
-      <c r="N47" s="80"/>
-      <c r="O47" s="80"/>
-      <c r="P47" s="80"/>
-      <c r="Q47" s="80"/>
-      <c r="R47" s="80"/>
-      <c r="S47" s="80"/>
-      <c r="T47" s="80"/>
-      <c r="U47" s="80"/>
-      <c r="V47" s="80"/>
-      <c r="W47" s="80"/>
-      <c r="X47" s="80"/>
-    </row>
-    <row r="48" spans="1:32">
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48"/>
-      <c r="AD48"/>
-      <c r="AE48"/>
-      <c r="AF48"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+      <c r="J48" s="80"/>
+      <c r="K48" s="80"/>
+      <c r="L48" s="80"/>
+      <c r="M48" s="80"/>
+      <c r="N48" s="80"/>
+      <c r="O48" s="80"/>
+      <c r="P48" s="80"/>
+      <c r="Q48" s="80"/>
+      <c r="R48" s="80"/>
+      <c r="S48" s="80"/>
+      <c r="T48" s="80"/>
+      <c r="U48" s="80"/>
+      <c r="V48" s="80"/>
+      <c r="W48" s="80"/>
+      <c r="X48" s="80"/>
     </row>
     <row r="49" spans="25:32">
       <c r="Y49"/>
@@ -4357,19 +4969,29 @@
       <c r="AE49"/>
       <c r="AF49"/>
     </row>
+    <row r="50" spans="25:32">
+      <c r="Y50"/>
+      <c r="Z50"/>
+      <c r="AA50"/>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
+      <c r="AE50"/>
+      <c r="AF50"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <cellWatches>
-    <cellWatch r="F31"/>
+    <cellWatch r="F32"/>
   </cellWatches>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DDBFB2-8AA5-4923-B8CD-FB6E86860846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23393C1D-60EF-4868-BC7C-7901553C3538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="555" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -606,10 +606,10 @@
     <t xml:space="preserve">SERVICIO DE IMPORTACIÓN  </t>
   </si>
   <si>
-    <t>RECARGO LOGISTICOS ( MONTACARGAS)</t>
-  </si>
-  <si>
-    <t>RECARGO DE DESPACHO (ALMACEN - AGENCIAS)</t>
+    <t>SERVICIO DE MONTACARGA</t>
+  </si>
+  <si>
+    <t>SERVICIO DE ENVIO (ALMACEN-AGENCIA)</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1195,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1457,6 +1457,14 @@
     <xf numFmtId="165" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1545,9 +1553,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1555,17 +1560,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1578,18 +1588,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2046,82 +2044,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="124"/>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
     </row>
     <row r="3" spans="1:12" ht="26.25">
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="E3" s="129" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="E3" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
     </row>
     <row r="4" spans="1:12" ht="26.25">
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="E4" s="130" t="s">
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="E4" s="134" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
       <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
       <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
       <c r="D6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="120"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="E7" s="121" t="s">
+      <c r="A7" s="124"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="124"/>
+      <c r="E7" s="125" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="K7" s="120"/>
-      <c r="L7" s="120"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
@@ -2134,20 +2132,20 @@
       <c r="E8" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="126" t="s">
+      <c r="F8" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="127"/>
+      <c r="G8" s="131"/>
       <c r="H8" s="86"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="140">
+      <c r="J8" s="144">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
@@ -2160,21 +2158,21 @@
       <c r="E9" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="122">
+      <c r="F9" s="126">
         <f ca="1">+TODAY()</f>
-        <v>46125</v>
-      </c>
-      <c r="G9" s="123"/>
+        <v>46127</v>
+      </c>
+      <c r="G9" s="127"/>
       <c r="H9" s="86"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="119">
+      <c r="J9" s="123">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
@@ -2187,19 +2185,19 @@
       <c r="E10" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="124" t="s">
+      <c r="F10" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="125"/>
+      <c r="G10" s="129"/>
       <c r="H10" s="86"/>
       <c r="I10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="141">
+      <c r="J10" s="145">
         <v>0</v>
       </c>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="145"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
@@ -2212,44 +2210,44 @@
       <c r="E11" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="143"/>
-      <c r="G11" s="144"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
       <c r="H11" s="86"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="152">
+      <c r="J11" s="156">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="156"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="145" t="s">
+      <c r="B13" s="149" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="145"/>
-      <c r="G13" s="145"/>
-      <c r="H13" s="145"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="145"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
       <c r="K13" s="32" t="s">
         <v>34</v>
       </c>
@@ -2258,17 +2256,17 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="146" t="s">
+      <c r="B14" s="150" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
       <c r="K14" s="37">
         <f>'2'!F13</f>
         <v>944.03</v>
@@ -2279,34 +2277,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="92"/>
-      <c r="B15" s="154" t="s">
+      <c r="B15" s="158" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="154"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="90"/>
       <c r="L15" s="91" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="148" t="s">
+      <c r="B16" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="152"/>
       <c r="K16" s="38">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
@@ -2316,17 +2314,17 @@
       </c>
     </row>
     <row r="17" spans="1:29">
-      <c r="B17" s="147" t="s">
+      <c r="B17" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="147"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="147"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="147"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="151"/>
       <c r="K17" s="37">
         <f>SUM(K14:K16)</f>
         <v>1243.51</v>
@@ -2349,13 +2347,13 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="B19" s="153" t="s">
+      <c r="B19" s="157" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="153"/>
-      <c r="D19" s="153"/>
-      <c r="E19" s="153"/>
-      <c r="F19" s="153"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="157"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
@@ -2370,16 +2368,16 @@
       </c>
     </row>
     <row r="20" spans="1:29">
-      <c r="B20" s="149" t="s">
+      <c r="B20" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="149"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
       <c r="J20" s="47">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
@@ -2414,16 +2412,16 @@
       </c>
     </row>
     <row r="22" spans="1:29">
-      <c r="B22" s="149" t="s">
+      <c r="B22" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="I22" s="149"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="153"/>
       <c r="J22" s="47">
         <v>0.16</v>
       </c>
@@ -2436,16 +2434,16 @@
       </c>
     </row>
     <row r="23" spans="1:29">
-      <c r="B23" s="143" t="s">
+      <c r="B23" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="143"/>
-      <c r="D23" s="143"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="143"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="147"/>
+      <c r="I23" s="147"/>
       <c r="J23" s="47">
         <v>0.02</v>
       </c>
@@ -2458,16 +2456,16 @@
       </c>
     </row>
     <row r="24" spans="1:29">
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="147"/>
-      <c r="G24" s="147"/>
-      <c r="H24" s="147"/>
-      <c r="I24" s="147"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="151"/>
       <c r="J24" s="75"/>
       <c r="K24" s="76">
         <f>SUM(K20:K23)</f>
@@ -2478,29 +2476,29 @@
       </c>
     </row>
     <row r="25" spans="1:29">
-      <c r="B25" s="149"/>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="149"/>
-      <c r="I25" s="149"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
       <c r="J25" s="2"/>
       <c r="K25" s="33"/>
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="143"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="147"/>
+      <c r="I26" s="147"/>
       <c r="J26" s="48" t="s">
         <v>76</v>
       </c>
@@ -2513,16 +2511,16 @@
       </c>
     </row>
     <row r="27" spans="1:29">
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="147"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="151"/>
+      <c r="H27" s="151"/>
+      <c r="I27" s="151"/>
       <c r="K27" s="37">
         <f>K24+K26</f>
         <v>316.1151070046609</v>
@@ -2549,14 +2547,14 @@
       <c r="AC27"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B28" s="124"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="128"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
@@ -2577,13 +2575,13 @@
     </row>
     <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="93"/>
-      <c r="B29" s="157" t="s">
+      <c r="B29" s="160" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="158"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
       <c r="G29" s="94"/>
       <c r="H29" s="95"/>
       <c r="I29" s="95"/>
@@ -2810,60 +2808,60 @@
     </row>
     <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="93"/>
-      <c r="B37" s="174" t="s">
+      <c r="B37" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="175"/>
-      <c r="D37" s="175"/>
-      <c r="E37" s="175"/>
-      <c r="F37" s="175"/>
-      <c r="G37" s="175"/>
-      <c r="H37" s="175"/>
-      <c r="I37" s="175"/>
-      <c r="J37" s="170"/>
-      <c r="K37" s="171">
+      <c r="C37" s="163"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="163"/>
+      <c r="I37" s="163"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="120">
         <f>SUM(K33+K35)-K36</f>
         <v>0</v>
       </c>
-      <c r="L37" s="172" t="s">
+      <c r="L37" s="121" t="s">
         <v>35</v>
       </c>
       <c r="M37" s="110"/>
     </row>
     <row r="38" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="93"/>
-      <c r="B38" s="168"/>
-      <c r="C38" s="169"/>
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="169"/>
-      <c r="J38" s="170"/>
-      <c r="K38" s="171"/>
-      <c r="L38" s="172"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="110"/>
+      <c r="K38" s="120"/>
+      <c r="L38" s="121"/>
       <c r="M38" s="110"/>
     </row>
     <row r="39" spans="1:29" ht="15.75">
-      <c r="B39" s="163" t="s">
+      <c r="B39" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="163"/>
-      <c r="D39" s="163"/>
-      <c r="E39" s="163"/>
-      <c r="F39" s="163"/>
-      <c r="G39" s="163"/>
-      <c r="H39" s="163"/>
-      <c r="I39" s="163"/>
-      <c r="J39" s="163"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="166"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="166"/>
       <c r="K39" s="60" t="s">
         <v>34</v>
       </c>
       <c r="L39" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="173"/>
+      <c r="M39" s="122"/>
       <c r="N39"/>
       <c r="O39"/>
       <c r="P39"/>
@@ -2882,17 +2880,17 @@
       <c r="AC39"/>
     </row>
     <row r="40" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B40" s="149" t="s">
+      <c r="B40" s="153" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="149"/>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="149"/>
-      <c r="H40" s="149"/>
-      <c r="I40" s="149"/>
-      <c r="J40" s="149"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="153"/>
+      <c r="H40" s="153"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="153"/>
       <c r="K40" s="37">
         <f>K37</f>
         <v>0</v>
@@ -2919,17 +2917,17 @@
       <c r="AC40"/>
     </row>
     <row r="41" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B41" s="149" t="s">
+      <c r="B41" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="149"/>
-      <c r="D41" s="149"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="I41" s="149"/>
-      <c r="J41" s="149"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="153"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="153"/>
+      <c r="H41" s="153"/>
+      <c r="I41" s="153"/>
+      <c r="J41" s="153"/>
       <c r="K41" s="37">
         <f>K27</f>
         <v>316.1151070046609</v>
@@ -2950,17 +2948,17 @@
       </c>
     </row>
     <row r="43" spans="1:29">
-      <c r="B43" s="159" t="s">
+      <c r="B43" s="164" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="159"/>
-      <c r="D43" s="159"/>
-      <c r="E43" s="159"/>
-      <c r="F43" s="159"/>
-      <c r="G43" s="159"/>
-      <c r="H43" s="159"/>
-      <c r="I43" s="159"/>
-      <c r="J43" s="159"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="164"/>
+      <c r="H43" s="164"/>
+      <c r="I43" s="164"/>
+      <c r="J43" s="164"/>
       <c r="K43" s="37">
         <v>0</v>
       </c>
@@ -2969,17 +2967,17 @@
       </c>
     </row>
     <row r="44" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B44" s="147" t="s">
+      <c r="B44" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="147"/>
-      <c r="D44" s="147"/>
-      <c r="E44" s="147"/>
-      <c r="F44" s="147"/>
-      <c r="G44" s="147"/>
-      <c r="H44" s="147"/>
-      <c r="I44" s="147"/>
-      <c r="J44" s="147"/>
+      <c r="C44" s="151"/>
+      <c r="D44" s="151"/>
+      <c r="E44" s="151"/>
+      <c r="F44" s="151"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="151"/>
+      <c r="I44" s="151"/>
+      <c r="J44" s="151"/>
       <c r="K44" s="76">
         <f>SUM(K40:K43)</f>
         <v>316.1151070046609</v>
@@ -2989,79 +2987,79 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B45" s="162"/>
-      <c r="C45" s="162"/>
-      <c r="D45" s="162"/>
-      <c r="E45" s="162"/>
-      <c r="F45" s="162"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="162"/>
-      <c r="I45" s="162"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="162"/>
-      <c r="L45" s="162"/>
+      <c r="B45" s="165"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="165"/>
+      <c r="E45" s="165"/>
+      <c r="F45" s="165"/>
+      <c r="G45" s="165"/>
+      <c r="H45" s="165"/>
+      <c r="I45" s="165"/>
+      <c r="J45" s="165"/>
+      <c r="K45" s="165"/>
+      <c r="L45" s="165"/>
     </row>
     <row r="46" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B46" s="137" t="s">
+      <c r="B46" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138"/>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138"/>
-      <c r="K46" s="138"/>
-      <c r="L46" s="139"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="142"/>
+      <c r="E46" s="142"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="142"/>
+      <c r="I46" s="142"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="143"/>
     </row>
     <row r="47" spans="1:29" ht="15.75" customHeight="1">
       <c r="B47" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="132" t="s">
+      <c r="C47" s="136" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="133"/>
-      <c r="E47" s="134"/>
+      <c r="D47" s="137"/>
+      <c r="E47" s="138"/>
       <c r="F47" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="132" t="s">
+      <c r="G47" s="136" t="s">
         <v>80</v>
       </c>
-      <c r="H47" s="134"/>
+      <c r="H47" s="138"/>
       <c r="I47" s="5" t="s">
         <v>77</v>
       </c>
       <c r="J47" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="160" t="s">
+      <c r="K47" s="167" t="s">
         <v>78</v>
       </c>
-      <c r="L47" s="161"/>
+      <c r="L47" s="168"/>
     </row>
     <row r="48" spans="1:29">
       <c r="B48" s="46">
         <v>1</v>
       </c>
-      <c r="C48" s="132" t="str">
+      <c r="C48" s="136" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D48" s="133"/>
-      <c r="E48" s="134"/>
+      <c r="D48" s="137"/>
+      <c r="E48" s="138"/>
       <c r="F48" s="7">
         <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G48" s="135">
+      <c r="G48" s="139">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H48" s="136"/>
+      <c r="H48" s="140"/>
       <c r="I48" s="55">
         <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
@@ -3070,11 +3068,11 @@
         <f t="shared" ref="J48" si="0">+F48*I48</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K48" s="131">
+      <c r="K48" s="135">
         <f t="shared" ref="K48" si="1">I48*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L48" s="131"/>
+      <c r="L48" s="135"/>
     </row>
     <row r="49" spans="2:13" ht="15.75">
       <c r="B49" s="49" t="s">
@@ -3136,79 +3134,79 @@
       <c r="K52" s="29"/>
     </row>
     <row r="53" spans="2:13" ht="18.75">
-      <c r="B53" s="142" t="s">
+      <c r="B53" s="146" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="142"/>
-      <c r="D53" s="142"/>
-      <c r="E53" s="142"/>
-      <c r="F53" s="142"/>
-      <c r="G53" s="142"/>
-      <c r="H53" s="142"/>
-      <c r="I53" s="142"/>
-      <c r="J53" s="142"/>
-      <c r="K53" s="142"/>
-      <c r="L53" s="142"/>
+      <c r="C53" s="146"/>
+      <c r="D53" s="146"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="146"/>
+      <c r="G53" s="146"/>
+      <c r="H53" s="146"/>
+      <c r="I53" s="146"/>
+      <c r="J53" s="146"/>
+      <c r="K53" s="146"/>
+      <c r="L53" s="146"/>
     </row>
     <row r="54" spans="2:13" ht="18.75">
-      <c r="B54" s="142" t="s">
+      <c r="B54" s="146" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="142"/>
-      <c r="D54" s="142"/>
-      <c r="E54" s="142"/>
-      <c r="F54" s="142"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="142"/>
-      <c r="I54" s="142"/>
-      <c r="J54" s="142"/>
-      <c r="K54" s="142"/>
-      <c r="L54" s="142"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
+      <c r="E54" s="146"/>
+      <c r="F54" s="146"/>
+      <c r="G54" s="146"/>
+      <c r="H54" s="146"/>
+      <c r="I54" s="146"/>
+      <c r="J54" s="146"/>
+      <c r="K54" s="146"/>
+      <c r="L54" s="146"/>
     </row>
     <row r="55" spans="2:13" ht="18.75">
-      <c r="B55" s="142" t="s">
+      <c r="B55" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
-      <c r="K55" s="142"/>
-      <c r="L55" s="142"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="146"/>
+      <c r="G55" s="146"/>
+      <c r="H55" s="146"/>
+      <c r="I55" s="146"/>
+      <c r="J55" s="146"/>
+      <c r="K55" s="146"/>
+      <c r="L55" s="146"/>
     </row>
     <row r="56" spans="2:13" ht="18.75">
-      <c r="B56" s="142" t="s">
+      <c r="B56" s="146" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="142"/>
-      <c r="D56" s="142"/>
-      <c r="E56" s="142"/>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="142"/>
-      <c r="J56" s="142"/>
-      <c r="K56" s="142"/>
-      <c r="L56" s="142"/>
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="146"/>
+      <c r="H56" s="146"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="146"/>
+      <c r="K56" s="146"/>
+      <c r="L56" s="146"/>
     </row>
     <row r="57" spans="2:13" ht="18.75">
-      <c r="B57" s="142" t="s">
+      <c r="B57" s="146" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="142"/>
-      <c r="D57" s="142"/>
-      <c r="E57" s="142"/>
-      <c r="F57" s="142"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="142"/>
-      <c r="J57" s="142"/>
-      <c r="K57" s="142"/>
-      <c r="L57" s="142"/>
+      <c r="C57" s="146"/>
+      <c r="D57" s="146"/>
+      <c r="E57" s="146"/>
+      <c r="F57" s="146"/>
+      <c r="G57" s="146"/>
+      <c r="H57" s="146"/>
+      <c r="I57" s="146"/>
+      <c r="J57" s="146"/>
+      <c r="K57" s="146"/>
+      <c r="L57" s="146"/>
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="29"/>
@@ -3224,581 +3222,581 @@
       <c r="L58" s="29"/>
     </row>
     <row r="59" spans="2:13" ht="9" customHeight="1">
-      <c r="B59" s="120"/>
-      <c r="C59" s="120"/>
-      <c r="E59" s="120"/>
-      <c r="F59" s="120"/>
-      <c r="G59" s="120"/>
-      <c r="H59" s="120"/>
-      <c r="I59" s="120"/>
-      <c r="J59" s="120"/>
-      <c r="K59" s="120"/>
-      <c r="L59" s="120"/>
-      <c r="M59" s="120"/>
+      <c r="B59" s="124"/>
+      <c r="C59" s="124"/>
+      <c r="E59" s="124"/>
+      <c r="F59" s="124"/>
+      <c r="G59" s="124"/>
+      <c r="H59" s="124"/>
+      <c r="I59" s="124"/>
+      <c r="J59" s="124"/>
+      <c r="K59" s="124"/>
+      <c r="L59" s="124"/>
+      <c r="M59" s="124"/>
     </row>
     <row r="60" spans="2:13" ht="31.9" customHeight="1">
-      <c r="B60" s="120"/>
-      <c r="C60" s="120"/>
-      <c r="D60" s="156" t="s">
+      <c r="B60" s="124"/>
+      <c r="C60" s="124"/>
+      <c r="D60" s="159" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="156"/>
-      <c r="F60" s="156"/>
-      <c r="G60" s="156"/>
-      <c r="H60" s="156"/>
-      <c r="I60" s="156"/>
-      <c r="J60" s="156"/>
-      <c r="K60" s="156"/>
-      <c r="L60" s="156"/>
-      <c r="M60" s="156"/>
+      <c r="E60" s="159"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="159"/>
+      <c r="H60" s="159"/>
+      <c r="I60" s="159"/>
+      <c r="J60" s="159"/>
+      <c r="K60" s="159"/>
+      <c r="L60" s="159"/>
+      <c r="M60" s="159"/>
     </row>
     <row r="61" spans="2:13" ht="21" customHeight="1">
-      <c r="B61" s="120"/>
-      <c r="C61" s="120"/>
-      <c r="D61" s="128" t="s">
+      <c r="B61" s="124"/>
+      <c r="C61" s="124"/>
+      <c r="D61" s="132" t="s">
         <v>121</v>
       </c>
-      <c r="E61" s="128"/>
-      <c r="F61" s="128"/>
-      <c r="G61" s="128"/>
-      <c r="H61" s="128"/>
-      <c r="I61" s="128"/>
+      <c r="E61" s="132"/>
+      <c r="F61" s="132"/>
+      <c r="G61" s="132"/>
+      <c r="H61" s="132"/>
+      <c r="I61" s="132"/>
     </row>
     <row r="62" spans="2:13">
-      <c r="B62" s="120"/>
-      <c r="C62" s="120"/>
+      <c r="B62" s="124"/>
+      <c r="C62" s="124"/>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="120"/>
-      <c r="C63" s="120"/>
+      <c r="B63" s="124"/>
+      <c r="C63" s="124"/>
     </row>
     <row r="64" spans="2:13" ht="21">
-      <c r="B64" s="155" t="s">
+      <c r="B64" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="155"/>
-      <c r="D64" s="155"/>
-      <c r="E64" s="155"/>
-      <c r="F64" s="155"/>
-      <c r="G64" s="155"/>
-      <c r="H64" s="155"/>
-      <c r="I64" s="155"/>
-      <c r="J64" s="155"/>
-      <c r="K64" s="155"/>
-      <c r="L64" s="155"/>
+      <c r="C64" s="169"/>
+      <c r="D64" s="169"/>
+      <c r="E64" s="169"/>
+      <c r="F64" s="169"/>
+      <c r="G64" s="169"/>
+      <c r="H64" s="169"/>
+      <c r="I64" s="169"/>
+      <c r="J64" s="169"/>
+      <c r="K64" s="169"/>
+      <c r="L64" s="169"/>
     </row>
     <row r="66" spans="2:12">
-      <c r="B66" s="150" t="s">
+      <c r="B66" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="C66" s="150"/>
-      <c r="D66" s="150"/>
-      <c r="E66" s="150"/>
-      <c r="F66" s="150"/>
-      <c r="G66" s="150"/>
-      <c r="H66" s="150"/>
-      <c r="I66" s="150"/>
-      <c r="J66" s="150"/>
-      <c r="K66" s="150"/>
-      <c r="L66" s="150"/>
+      <c r="C66" s="154"/>
+      <c r="D66" s="154"/>
+      <c r="E66" s="154"/>
+      <c r="F66" s="154"/>
+      <c r="G66" s="154"/>
+      <c r="H66" s="154"/>
+      <c r="I66" s="154"/>
+      <c r="J66" s="154"/>
+      <c r="K66" s="154"/>
+      <c r="L66" s="154"/>
     </row>
     <row r="67" spans="2:12">
-      <c r="B67" s="150" t="s">
+      <c r="B67" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="150"/>
-      <c r="D67" s="150"/>
-      <c r="E67" s="150"/>
-      <c r="F67" s="150"/>
-      <c r="G67" s="150"/>
-      <c r="H67" s="150"/>
-      <c r="I67" s="150"/>
-      <c r="J67" s="150"/>
-      <c r="K67" s="150"/>
-      <c r="L67" s="150"/>
+      <c r="C67" s="154"/>
+      <c r="D67" s="154"/>
+      <c r="E67" s="154"/>
+      <c r="F67" s="154"/>
+      <c r="G67" s="154"/>
+      <c r="H67" s="154"/>
+      <c r="I67" s="154"/>
+      <c r="J67" s="154"/>
+      <c r="K67" s="154"/>
+      <c r="L67" s="154"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="149" t="s">
+      <c r="B68" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="C68" s="149"/>
-      <c r="D68" s="149"/>
-      <c r="E68" s="149"/>
-      <c r="F68" s="149"/>
-      <c r="G68" s="149"/>
-      <c r="H68" s="149"/>
-      <c r="I68" s="149"/>
-      <c r="J68" s="149"/>
-      <c r="K68" s="149"/>
-      <c r="L68" s="149"/>
+      <c r="C68" s="153"/>
+      <c r="D68" s="153"/>
+      <c r="E68" s="153"/>
+      <c r="F68" s="153"/>
+      <c r="G68" s="153"/>
+      <c r="H68" s="153"/>
+      <c r="I68" s="153"/>
+      <c r="J68" s="153"/>
+      <c r="K68" s="153"/>
+      <c r="L68" s="153"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="150" t="s">
+      <c r="B69" s="154" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="150"/>
-      <c r="D69" s="150"/>
-      <c r="E69" s="150"/>
-      <c r="F69" s="150"/>
-      <c r="G69" s="150"/>
-      <c r="H69" s="150"/>
-      <c r="I69" s="150"/>
-      <c r="J69" s="150"/>
-      <c r="K69" s="150"/>
-      <c r="L69" s="150"/>
+      <c r="C69" s="154"/>
+      <c r="D69" s="154"/>
+      <c r="E69" s="154"/>
+      <c r="F69" s="154"/>
+      <c r="G69" s="154"/>
+      <c r="H69" s="154"/>
+      <c r="I69" s="154"/>
+      <c r="J69" s="154"/>
+      <c r="K69" s="154"/>
+      <c r="L69" s="154"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="150" t="s">
+      <c r="B70" s="154" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="150"/>
-      <c r="D70" s="150"/>
-      <c r="E70" s="150"/>
-      <c r="F70" s="150"/>
-      <c r="G70" s="150"/>
-      <c r="H70" s="150"/>
-      <c r="I70" s="150"/>
-      <c r="J70" s="150"/>
-      <c r="K70" s="150"/>
-      <c r="L70" s="150"/>
+      <c r="C70" s="154"/>
+      <c r="D70" s="154"/>
+      <c r="E70" s="154"/>
+      <c r="F70" s="154"/>
+      <c r="G70" s="154"/>
+      <c r="H70" s="154"/>
+      <c r="I70" s="154"/>
+      <c r="J70" s="154"/>
+      <c r="K70" s="154"/>
+      <c r="L70" s="154"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="149" t="s">
+      <c r="B71" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="149"/>
-      <c r="D71" s="149"/>
-      <c r="E71" s="149"/>
-      <c r="F71" s="149"/>
-      <c r="G71" s="149"/>
-      <c r="H71" s="149"/>
-      <c r="I71" s="149"/>
-      <c r="J71" s="149"/>
-      <c r="K71" s="149"/>
-      <c r="L71" s="149"/>
+      <c r="C71" s="153"/>
+      <c r="D71" s="153"/>
+      <c r="E71" s="153"/>
+      <c r="F71" s="153"/>
+      <c r="G71" s="153"/>
+      <c r="H71" s="153"/>
+      <c r="I71" s="153"/>
+      <c r="J71" s="153"/>
+      <c r="K71" s="153"/>
+      <c r="L71" s="153"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="150" t="s">
+      <c r="B72" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="C72" s="150"/>
-      <c r="D72" s="150"/>
-      <c r="E72" s="150"/>
-      <c r="F72" s="150"/>
-      <c r="G72" s="150"/>
-      <c r="H72" s="150"/>
-      <c r="I72" s="150"/>
-      <c r="J72" s="150"/>
-      <c r="K72" s="150"/>
-      <c r="L72" s="150"/>
+      <c r="C72" s="154"/>
+      <c r="D72" s="154"/>
+      <c r="E72" s="154"/>
+      <c r="F72" s="154"/>
+      <c r="G72" s="154"/>
+      <c r="H72" s="154"/>
+      <c r="I72" s="154"/>
+      <c r="J72" s="154"/>
+      <c r="K72" s="154"/>
+      <c r="L72" s="154"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="150" t="s">
+      <c r="B73" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="150"/>
-      <c r="D73" s="150"/>
-      <c r="E73" s="150"/>
-      <c r="F73" s="150"/>
-      <c r="G73" s="150"/>
-      <c r="H73" s="150"/>
-      <c r="I73" s="150"/>
-      <c r="J73" s="150"/>
-      <c r="K73" s="150"/>
-      <c r="L73" s="150"/>
+      <c r="C73" s="154"/>
+      <c r="D73" s="154"/>
+      <c r="E73" s="154"/>
+      <c r="F73" s="154"/>
+      <c r="G73" s="154"/>
+      <c r="H73" s="154"/>
+      <c r="I73" s="154"/>
+      <c r="J73" s="154"/>
+      <c r="K73" s="154"/>
+      <c r="L73" s="154"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="150" t="s">
+      <c r="B74" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C74" s="150"/>
-      <c r="D74" s="150"/>
-      <c r="E74" s="150"/>
-      <c r="F74" s="150"/>
-      <c r="G74" s="150"/>
-      <c r="H74" s="150"/>
-      <c r="I74" s="150"/>
-      <c r="J74" s="150"/>
-      <c r="K74" s="150"/>
-      <c r="L74" s="150"/>
+      <c r="C74" s="154"/>
+      <c r="D74" s="154"/>
+      <c r="E74" s="154"/>
+      <c r="F74" s="154"/>
+      <c r="G74" s="154"/>
+      <c r="H74" s="154"/>
+      <c r="I74" s="154"/>
+      <c r="J74" s="154"/>
+      <c r="K74" s="154"/>
+      <c r="L74" s="154"/>
     </row>
     <row r="75" spans="2:12">
-      <c r="B75" s="150" t="s">
+      <c r="B75" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="C75" s="150"/>
-      <c r="D75" s="150"/>
-      <c r="E75" s="150"/>
-      <c r="F75" s="150"/>
-      <c r="G75" s="150"/>
-      <c r="H75" s="150"/>
-      <c r="I75" s="150"/>
-      <c r="J75" s="150"/>
-      <c r="K75" s="150"/>
-      <c r="L75" s="150"/>
+      <c r="C75" s="154"/>
+      <c r="D75" s="154"/>
+      <c r="E75" s="154"/>
+      <c r="F75" s="154"/>
+      <c r="G75" s="154"/>
+      <c r="H75" s="154"/>
+      <c r="I75" s="154"/>
+      <c r="J75" s="154"/>
+      <c r="K75" s="154"/>
+      <c r="L75" s="154"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="150" t="s">
+      <c r="B76" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C76" s="150"/>
-      <c r="D76" s="150"/>
-      <c r="E76" s="150"/>
-      <c r="F76" s="150"/>
-      <c r="G76" s="150"/>
-      <c r="H76" s="150"/>
-      <c r="I76" s="150"/>
-      <c r="J76" s="150"/>
-      <c r="K76" s="150"/>
-      <c r="L76" s="150"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="154"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="154"/>
+      <c r="G76" s="154"/>
+      <c r="H76" s="154"/>
+      <c r="I76" s="154"/>
+      <c r="J76" s="154"/>
+      <c r="K76" s="154"/>
+      <c r="L76" s="154"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="150" t="s">
+      <c r="B77" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="C77" s="150"/>
-      <c r="D77" s="150"/>
-      <c r="E77" s="150"/>
-      <c r="F77" s="150"/>
-      <c r="G77" s="150"/>
-      <c r="H77" s="150"/>
-      <c r="I77" s="150"/>
-      <c r="J77" s="150"/>
-      <c r="K77" s="150"/>
-      <c r="L77" s="150"/>
+      <c r="C77" s="154"/>
+      <c r="D77" s="154"/>
+      <c r="E77" s="154"/>
+      <c r="F77" s="154"/>
+      <c r="G77" s="154"/>
+      <c r="H77" s="154"/>
+      <c r="I77" s="154"/>
+      <c r="J77" s="154"/>
+      <c r="K77" s="154"/>
+      <c r="L77" s="154"/>
     </row>
     <row r="78" spans="2:12">
-      <c r="B78" s="150" t="s">
+      <c r="B78" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="150"/>
-      <c r="D78" s="150"/>
-      <c r="E78" s="150"/>
-      <c r="F78" s="150"/>
-      <c r="G78" s="150"/>
-      <c r="H78" s="150"/>
-      <c r="I78" s="150"/>
-      <c r="J78" s="150"/>
-      <c r="K78" s="150"/>
-      <c r="L78" s="150"/>
+      <c r="C78" s="154"/>
+      <c r="D78" s="154"/>
+      <c r="E78" s="154"/>
+      <c r="F78" s="154"/>
+      <c r="G78" s="154"/>
+      <c r="H78" s="154"/>
+      <c r="I78" s="154"/>
+      <c r="J78" s="154"/>
+      <c r="K78" s="154"/>
+      <c r="L78" s="154"/>
     </row>
     <row r="79" spans="2:12">
-      <c r="B79" s="150" t="s">
+      <c r="B79" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="150"/>
-      <c r="D79" s="150"/>
-      <c r="E79" s="150"/>
-      <c r="F79" s="150"/>
-      <c r="G79" s="150"/>
-      <c r="H79" s="150"/>
-      <c r="I79" s="150"/>
-      <c r="J79" s="150"/>
-      <c r="K79" s="150"/>
-      <c r="L79" s="150"/>
+      <c r="C79" s="154"/>
+      <c r="D79" s="154"/>
+      <c r="E79" s="154"/>
+      <c r="F79" s="154"/>
+      <c r="G79" s="154"/>
+      <c r="H79" s="154"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="154"/>
+      <c r="K79" s="154"/>
+      <c r="L79" s="154"/>
     </row>
     <row r="80" spans="2:12">
-      <c r="B80" s="150" t="s">
+      <c r="B80" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="150"/>
-      <c r="D80" s="150"/>
-      <c r="E80" s="150"/>
-      <c r="F80" s="150"/>
-      <c r="G80" s="150"/>
-      <c r="H80" s="150"/>
-      <c r="I80" s="150"/>
-      <c r="J80" s="150"/>
-      <c r="K80" s="150"/>
-      <c r="L80" s="150"/>
+      <c r="C80" s="154"/>
+      <c r="D80" s="154"/>
+      <c r="E80" s="154"/>
+      <c r="F80" s="154"/>
+      <c r="G80" s="154"/>
+      <c r="H80" s="154"/>
+      <c r="I80" s="154"/>
+      <c r="J80" s="154"/>
+      <c r="K80" s="154"/>
+      <c r="L80" s="154"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="B81" s="150" t="s">
+      <c r="B81" s="154" t="s">
         <v>65</v>
       </c>
-      <c r="C81" s="150"/>
-      <c r="D81" s="150"/>
-      <c r="E81" s="150"/>
-      <c r="F81" s="150"/>
-      <c r="G81" s="150"/>
-      <c r="H81" s="150"/>
-      <c r="I81" s="150"/>
-      <c r="J81" s="150"/>
-      <c r="K81" s="150"/>
-      <c r="L81" s="150"/>
+      <c r="C81" s="154"/>
+      <c r="D81" s="154"/>
+      <c r="E81" s="154"/>
+      <c r="F81" s="154"/>
+      <c r="G81" s="154"/>
+      <c r="H81" s="154"/>
+      <c r="I81" s="154"/>
+      <c r="J81" s="154"/>
+      <c r="K81" s="154"/>
+      <c r="L81" s="154"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="B82" s="150" t="s">
+      <c r="B82" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="C82" s="150"/>
-      <c r="D82" s="150"/>
-      <c r="E82" s="150"/>
-      <c r="F82" s="150"/>
-      <c r="G82" s="150"/>
-      <c r="H82" s="150"/>
-      <c r="I82" s="150"/>
-      <c r="J82" s="150"/>
-      <c r="K82" s="150"/>
-      <c r="L82" s="150"/>
+      <c r="C82" s="154"/>
+      <c r="D82" s="154"/>
+      <c r="E82" s="154"/>
+      <c r="F82" s="154"/>
+      <c r="G82" s="154"/>
+      <c r="H82" s="154"/>
+      <c r="I82" s="154"/>
+      <c r="J82" s="154"/>
+      <c r="K82" s="154"/>
+      <c r="L82" s="154"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="B83" s="146" t="s">
+      <c r="B83" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="146"/>
-      <c r="D83" s="146"/>
-      <c r="E83" s="146"/>
-      <c r="F83" s="146"/>
-      <c r="G83" s="146"/>
-      <c r="H83" s="146"/>
-      <c r="I83" s="146"/>
-      <c r="J83" s="146"/>
-      <c r="K83" s="146"/>
-      <c r="L83" s="146"/>
+      <c r="C83" s="150"/>
+      <c r="D83" s="150"/>
+      <c r="E83" s="150"/>
+      <c r="F83" s="150"/>
+      <c r="G83" s="150"/>
+      <c r="H83" s="150"/>
+      <c r="I83" s="150"/>
+      <c r="J83" s="150"/>
+      <c r="K83" s="150"/>
+      <c r="L83" s="150"/>
     </row>
     <row r="84" spans="1:12">
-      <c r="B84" s="150" t="s">
+      <c r="B84" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="C84" s="150"/>
-      <c r="D84" s="150"/>
-      <c r="E84" s="150"/>
-      <c r="F84" s="150"/>
-      <c r="G84" s="150"/>
-      <c r="H84" s="150"/>
-      <c r="I84" s="150"/>
-      <c r="J84" s="150"/>
-      <c r="K84" s="150"/>
-      <c r="L84" s="150"/>
+      <c r="C84" s="154"/>
+      <c r="D84" s="154"/>
+      <c r="E84" s="154"/>
+      <c r="F84" s="154"/>
+      <c r="G84" s="154"/>
+      <c r="H84" s="154"/>
+      <c r="I84" s="154"/>
+      <c r="J84" s="154"/>
+      <c r="K84" s="154"/>
+      <c r="L84" s="154"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="B85" s="146" t="s">
+      <c r="B85" s="150" t="s">
         <v>51</v>
       </c>
-      <c r="C85" s="146"/>
-      <c r="D85" s="146"/>
-      <c r="E85" s="146"/>
-      <c r="F85" s="146"/>
-      <c r="G85" s="146"/>
-      <c r="H85" s="146"/>
-      <c r="I85" s="146"/>
-      <c r="J85" s="146"/>
-      <c r="K85" s="146"/>
-      <c r="L85" s="146"/>
+      <c r="C85" s="150"/>
+      <c r="D85" s="150"/>
+      <c r="E85" s="150"/>
+      <c r="F85" s="150"/>
+      <c r="G85" s="150"/>
+      <c r="H85" s="150"/>
+      <c r="I85" s="150"/>
+      <c r="J85" s="150"/>
+      <c r="K85" s="150"/>
+      <c r="L85" s="150"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="B86" s="150" t="s">
+      <c r="B86" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="C86" s="150"/>
-      <c r="D86" s="150"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="150"/>
-      <c r="G86" s="150"/>
-      <c r="H86" s="150"/>
-      <c r="I86" s="150"/>
-      <c r="J86" s="150"/>
-      <c r="K86" s="150"/>
-      <c r="L86" s="150"/>
+      <c r="C86" s="154"/>
+      <c r="D86" s="154"/>
+      <c r="E86" s="154"/>
+      <c r="F86" s="154"/>
+      <c r="G86" s="154"/>
+      <c r="H86" s="154"/>
+      <c r="I86" s="154"/>
+      <c r="J86" s="154"/>
+      <c r="K86" s="154"/>
+      <c r="L86" s="154"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="B87" s="150" t="s">
+      <c r="B87" s="154" t="s">
         <v>69</v>
       </c>
-      <c r="C87" s="150"/>
-      <c r="D87" s="150"/>
-      <c r="E87" s="150"/>
-      <c r="F87" s="150"/>
-      <c r="G87" s="150"/>
-      <c r="H87" s="150"/>
-      <c r="I87" s="150"/>
-      <c r="J87" s="150"/>
-      <c r="K87" s="150"/>
-      <c r="L87" s="150"/>
+      <c r="C87" s="154"/>
+      <c r="D87" s="154"/>
+      <c r="E87" s="154"/>
+      <c r="F87" s="154"/>
+      <c r="G87" s="154"/>
+      <c r="H87" s="154"/>
+      <c r="I87" s="154"/>
+      <c r="J87" s="154"/>
+      <c r="K87" s="154"/>
+      <c r="L87" s="154"/>
     </row>
     <row r="88" spans="1:12">
-      <c r="B88" s="150" t="s">
+      <c r="B88" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="150"/>
-      <c r="D88" s="150"/>
-      <c r="E88" s="150"/>
-      <c r="F88" s="150"/>
-      <c r="G88" s="150"/>
-      <c r="H88" s="150"/>
-      <c r="I88" s="150"/>
-      <c r="J88" s="150"/>
-      <c r="K88" s="150"/>
-      <c r="L88" s="150"/>
+      <c r="C88" s="154"/>
+      <c r="D88" s="154"/>
+      <c r="E88" s="154"/>
+      <c r="F88" s="154"/>
+      <c r="G88" s="154"/>
+      <c r="H88" s="154"/>
+      <c r="I88" s="154"/>
+      <c r="J88" s="154"/>
+      <c r="K88" s="154"/>
+      <c r="L88" s="154"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="B89" s="150" t="s">
+      <c r="B89" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="150"/>
-      <c r="D89" s="150"/>
-      <c r="E89" s="150"/>
-      <c r="F89" s="150"/>
-      <c r="G89" s="150"/>
-      <c r="H89" s="150"/>
-      <c r="I89" s="150"/>
-      <c r="J89" s="150"/>
-      <c r="K89" s="150"/>
-      <c r="L89" s="150"/>
+      <c r="C89" s="154"/>
+      <c r="D89" s="154"/>
+      <c r="E89" s="154"/>
+      <c r="F89" s="154"/>
+      <c r="G89" s="154"/>
+      <c r="H89" s="154"/>
+      <c r="I89" s="154"/>
+      <c r="J89" s="154"/>
+      <c r="K89" s="154"/>
+      <c r="L89" s="154"/>
     </row>
     <row r="90" spans="1:12">
-      <c r="B90" s="150" t="s">
+      <c r="B90" s="154" t="s">
         <v>72</v>
       </c>
-      <c r="C90" s="150"/>
-      <c r="D90" s="150"/>
-      <c r="E90" s="150"/>
-      <c r="F90" s="150"/>
-      <c r="G90" s="150"/>
-      <c r="H90" s="150"/>
-      <c r="I90" s="150"/>
-      <c r="J90" s="150"/>
-      <c r="K90" s="150"/>
-      <c r="L90" s="150"/>
+      <c r="C90" s="154"/>
+      <c r="D90" s="154"/>
+      <c r="E90" s="154"/>
+      <c r="F90" s="154"/>
+      <c r="G90" s="154"/>
+      <c r="H90" s="154"/>
+      <c r="I90" s="154"/>
+      <c r="J90" s="154"/>
+      <c r="K90" s="154"/>
+      <c r="L90" s="154"/>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="85"/>
-      <c r="B91" s="151" t="s">
+      <c r="B91" s="155" t="s">
         <v>84</v>
       </c>
-      <c r="C91" s="151"/>
-      <c r="D91" s="151"/>
-      <c r="E91" s="151"/>
-      <c r="F91" s="151"/>
-      <c r="G91" s="151"/>
-      <c r="H91" s="151"/>
-      <c r="I91" s="151"/>
-      <c r="J91" s="151"/>
-      <c r="K91" s="151"/>
-      <c r="L91" s="151"/>
+      <c r="C91" s="155"/>
+      <c r="D91" s="155"/>
+      <c r="E91" s="155"/>
+      <c r="F91" s="155"/>
+      <c r="G91" s="155"/>
+      <c r="H91" s="155"/>
+      <c r="I91" s="155"/>
+      <c r="J91" s="155"/>
+      <c r="K91" s="155"/>
+      <c r="L91" s="155"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="85"/>
-      <c r="B92" s="150" t="s">
+      <c r="B92" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="C92" s="150"/>
-      <c r="D92" s="150"/>
-      <c r="E92" s="150"/>
-      <c r="F92" s="150"/>
-      <c r="G92" s="150"/>
-      <c r="H92" s="150"/>
-      <c r="I92" s="150"/>
-      <c r="J92" s="150"/>
-      <c r="K92" s="150"/>
-      <c r="L92" s="150"/>
+      <c r="C92" s="154"/>
+      <c r="D92" s="154"/>
+      <c r="E92" s="154"/>
+      <c r="F92" s="154"/>
+      <c r="G92" s="154"/>
+      <c r="H92" s="154"/>
+      <c r="I92" s="154"/>
+      <c r="J92" s="154"/>
+      <c r="K92" s="154"/>
+      <c r="L92" s="154"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="85"/>
-      <c r="B93" s="151" t="s">
+      <c r="B93" s="155" t="s">
         <v>86</v>
       </c>
-      <c r="C93" s="151"/>
-      <c r="D93" s="151"/>
-      <c r="E93" s="151"/>
-      <c r="F93" s="151"/>
-      <c r="G93" s="151"/>
-      <c r="H93" s="151"/>
-      <c r="I93" s="151"/>
-      <c r="J93" s="151"/>
-      <c r="K93" s="151"/>
-      <c r="L93" s="151"/>
+      <c r="C93" s="155"/>
+      <c r="D93" s="155"/>
+      <c r="E93" s="155"/>
+      <c r="F93" s="155"/>
+      <c r="G93" s="155"/>
+      <c r="H93" s="155"/>
+      <c r="I93" s="155"/>
+      <c r="J93" s="155"/>
+      <c r="K93" s="155"/>
+      <c r="L93" s="155"/>
     </row>
     <row r="95" spans="1:12">
-      <c r="C95" s="120"/>
-      <c r="D95" s="120"/>
-      <c r="E95" s="120"/>
-      <c r="F95" s="120"/>
-      <c r="G95" s="120"/>
-      <c r="H95" s="120"/>
-      <c r="I95" s="120"/>
+      <c r="C95" s="124"/>
+      <c r="D95" s="124"/>
+      <c r="E95" s="124"/>
+      <c r="F95" s="124"/>
+      <c r="G95" s="124"/>
+      <c r="H95" s="124"/>
+      <c r="I95" s="124"/>
     </row>
     <row r="96" spans="1:12">
-      <c r="C96" s="120"/>
-      <c r="D96" s="120"/>
-      <c r="E96" s="120"/>
-      <c r="F96" s="120"/>
-      <c r="G96" s="120"/>
-      <c r="H96" s="120"/>
-      <c r="I96" s="120"/>
+      <c r="C96" s="124"/>
+      <c r="D96" s="124"/>
+      <c r="E96" s="124"/>
+      <c r="F96" s="124"/>
+      <c r="G96" s="124"/>
+      <c r="H96" s="124"/>
+      <c r="I96" s="124"/>
     </row>
     <row r="97" spans="3:9">
-      <c r="C97" s="120"/>
-      <c r="D97" s="120"/>
-      <c r="E97" s="120"/>
-      <c r="F97" s="120"/>
-      <c r="G97" s="120"/>
-      <c r="H97" s="120"/>
-      <c r="I97" s="120"/>
+      <c r="C97" s="124"/>
+      <c r="D97" s="124"/>
+      <c r="E97" s="124"/>
+      <c r="F97" s="124"/>
+      <c r="G97" s="124"/>
+      <c r="H97" s="124"/>
+      <c r="I97" s="124"/>
     </row>
     <row r="98" spans="3:9">
-      <c r="C98" s="120"/>
-      <c r="D98" s="120"/>
-      <c r="E98" s="120"/>
-      <c r="F98" s="120"/>
-      <c r="G98" s="120"/>
-      <c r="H98" s="120"/>
-      <c r="I98" s="120"/>
+      <c r="C98" s="124"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="124"/>
+      <c r="F98" s="124"/>
+      <c r="G98" s="124"/>
+      <c r="H98" s="124"/>
+      <c r="I98" s="124"/>
     </row>
     <row r="99" spans="3:9">
-      <c r="C99" s="120"/>
-      <c r="D99" s="120"/>
-      <c r="E99" s="120"/>
-      <c r="F99" s="120"/>
-      <c r="G99" s="120"/>
-      <c r="H99" s="120"/>
-      <c r="I99" s="120"/>
+      <c r="C99" s="124"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="124"/>
+      <c r="H99" s="124"/>
+      <c r="I99" s="124"/>
     </row>
     <row r="100" spans="3:9">
-      <c r="C100" s="120"/>
-      <c r="D100" s="120"/>
-      <c r="E100" s="120"/>
-      <c r="F100" s="120"/>
-      <c r="G100" s="120"/>
-      <c r="H100" s="120"/>
-      <c r="I100" s="120"/>
+      <c r="C100" s="124"/>
+      <c r="D100" s="124"/>
+      <c r="E100" s="124"/>
+      <c r="F100" s="124"/>
+      <c r="G100" s="124"/>
+      <c r="H100" s="124"/>
+      <c r="I100" s="124"/>
     </row>
     <row r="101" spans="3:9">
-      <c r="C101" s="120"/>
-      <c r="D101" s="120"/>
-      <c r="E101" s="120"/>
-      <c r="F101" s="120"/>
-      <c r="G101" s="120"/>
-      <c r="H101" s="120"/>
-      <c r="I101" s="120"/>
+      <c r="C101" s="124"/>
+      <c r="D101" s="124"/>
+      <c r="E101" s="124"/>
+      <c r="F101" s="124"/>
+      <c r="G101" s="124"/>
+      <c r="H101" s="124"/>
+      <c r="I101" s="124"/>
     </row>
     <row r="102" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C102" s="120"/>
-      <c r="D102" s="120"/>
-      <c r="E102" s="120"/>
-      <c r="F102" s="120"/>
-      <c r="G102" s="120"/>
-      <c r="H102" s="120"/>
-      <c r="I102" s="120"/>
+      <c r="C102" s="124"/>
+      <c r="D102" s="124"/>
+      <c r="E102" s="124"/>
+      <c r="F102" s="124"/>
+      <c r="G102" s="124"/>
+      <c r="H102" s="124"/>
+      <c r="I102" s="124"/>
     </row>
     <row r="103" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C103" s="120"/>
-      <c r="D103" s="120"/>
-      <c r="E103" s="120"/>
-      <c r="F103" s="120"/>
-      <c r="G103" s="120"/>
-      <c r="H103" s="120"/>
-      <c r="I103" s="120"/>
+      <c r="C103" s="124"/>
+      <c r="D103" s="124"/>
+      <c r="E103" s="124"/>
+      <c r="F103" s="124"/>
+      <c r="G103" s="124"/>
+      <c r="H103" s="124"/>
+      <c r="I103" s="124"/>
     </row>
     <row r="104" spans="3:9">
-      <c r="C104" s="120"/>
-      <c r="D104" s="120"/>
-      <c r="E104" s="120"/>
-      <c r="F104" s="120"/>
-      <c r="G104" s="120"/>
-      <c r="H104" s="120"/>
-      <c r="I104" s="120"/>
+      <c r="C104" s="124"/>
+      <c r="D104" s="124"/>
+      <c r="E104" s="124"/>
+      <c r="F104" s="124"/>
+      <c r="G104" s="124"/>
+      <c r="H104" s="124"/>
+      <c r="I104" s="124"/>
     </row>
     <row r="110" spans="3:9" ht="15.6" customHeight="1"/>
   </sheetData>
@@ -3809,6 +3807,12 @@
     <mergeCell ref="B79:L79"/>
     <mergeCell ref="E59:M59"/>
     <mergeCell ref="K47:L47"/>
+    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B53:L53"/>
+    <mergeCell ref="B66:L66"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B64:L64"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="B59:C63"/>
     <mergeCell ref="B19:F19"/>
@@ -3825,12 +3829,6 @@
     <mergeCell ref="B39:J39"/>
     <mergeCell ref="B40:J40"/>
     <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B66:L66"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B64:L64"/>
     <mergeCell ref="B93:L93"/>
     <mergeCell ref="B76:L76"/>
     <mergeCell ref="B77:L77"/>
@@ -3936,14 +3934,14 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
       <c r="B6" s="70" t="s">
@@ -3993,14 +3991,14 @@
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="164" t="s">
+      <c r="J8" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="164"/>
-      <c r="M8" s="164" t="s">
+      <c r="K8" s="170"/>
+      <c r="M8" s="170" t="s">
         <v>107</v>
       </c>
-      <c r="N8" s="164"/>
+      <c r="N8" s="170"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
@@ -4473,14 +4471,14 @@
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="165" t="s">
+      <c r="B23" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="165"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165"/>
-      <c r="F23" s="165"/>
-      <c r="G23" s="165"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
@@ -4746,14 +4744,14 @@
       <c r="AF35"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="B36" s="167" t="s">
+      <c r="B36" s="173" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="167"/>
-      <c r="D36" s="167"/>
-      <c r="E36" s="167"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="167"/>
+      <c r="C36" s="173"/>
+      <c r="D36" s="173"/>
+      <c r="E36" s="173"/>
+      <c r="F36" s="173"/>
+      <c r="G36" s="173"/>
     </row>
     <row r="38" spans="1:32">
       <c r="C38" s="21">

--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -1,28 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23393C1D-60EF-4868-BC7C-7901553C3538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F696C-A1AD-4EC8-8EAC-308E0B22255E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19520" yWindow="320" windowWidth="14400" windowHeight="7310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
     <sheet name="2" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -82,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="136">
   <si>
     <t>VALOR UNITARIO</t>
   </si>
@@ -610,6 +619,9 @@
   </si>
   <si>
     <t>SERVICIO DE ENVIO (ALMACEN-AGENCIA)</t>
+  </si>
+  <si>
+    <t>RECARGOS ADUANEROS (BQ O SANCIONES)</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1465,6 +1477,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1669,7 +1683,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>511628</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>10885</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1209675" cy="1190625"/>
@@ -1708,14 +1722,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>696686</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>107313</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>500744</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>174173</xdr:rowOff>
+      <xdr:colOff>498204</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>365</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2025,101 +2039,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AC110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:AC111"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="0.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="0.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.7109375" style="1"/>
+    <col min="1" max="1" width="7.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="0.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="0.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="128"/>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-    </row>
-    <row r="3" spans="1:12" ht="26.25">
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="E3" s="133" t="s">
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+    </row>
+    <row r="3" spans="1:12" ht="25.8">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="E3" s="135" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-    </row>
-    <row r="4" spans="1:12" ht="26.25">
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="E4" s="134" t="s">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.8">
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="E4" s="136" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
       <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
       <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="124"/>
-      <c r="B7" s="124"/>
-      <c r="C7" s="124"/>
-      <c r="E7" s="125" t="s">
+      <c r="A7" s="126"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="E7" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
@@ -2132,20 +2146,20 @@
       <c r="E8" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="130" t="s">
+      <c r="F8" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="131"/>
+      <c r="G8" s="133"/>
       <c r="H8" s="86"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="144">
+      <c r="J8" s="146">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="144"/>
-      <c r="L8" s="144"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
@@ -2158,21 +2172,21 @@
       <c r="E9" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="126">
+      <c r="F9" s="128">
         <f ca="1">+TODAY()</f>
-        <v>46127</v>
-      </c>
-      <c r="G9" s="127"/>
+        <v>46128</v>
+      </c>
+      <c r="G9" s="129"/>
       <c r="H9" s="86"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="123">
+      <c r="J9" s="125">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="123"/>
-      <c r="L9" s="123"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
@@ -2185,19 +2199,19 @@
       <c r="E10" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="128" t="s">
+      <c r="F10" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="129"/>
+      <c r="G10" s="131"/>
       <c r="H10" s="86"/>
       <c r="I10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="145">
+      <c r="J10" s="147">
         <v>0</v>
       </c>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
@@ -2210,44 +2224,44 @@
       <c r="E11" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="147"/>
-      <c r="G11" s="148"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="150"/>
       <c r="H11" s="86"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="156">
+      <c r="J11" s="158">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="156"/>
-      <c r="L11" s="156"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="158"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="149" t="s">
+      <c r="B13" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="151"/>
       <c r="K13" s="32" t="s">
         <v>34</v>
       </c>
@@ -2256,17 +2270,17 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="150" t="s">
+      <c r="B14" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="152"/>
+      <c r="J14" s="152"/>
       <c r="K14" s="37">
         <f>'2'!F13</f>
         <v>944.03</v>
@@ -2277,34 +2291,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="92"/>
-      <c r="B15" s="158" t="s">
+      <c r="B15" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="158"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="90"/>
       <c r="L15" s="91" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="152" t="s">
+      <c r="B16" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="152"/>
-      <c r="I16" s="152"/>
-      <c r="J16" s="152"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="154"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="154"/>
       <c r="K16" s="38">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
@@ -2314,17 +2328,17 @@
       </c>
     </row>
     <row r="17" spans="1:29">
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="151"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="151"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
       <c r="K17" s="37">
         <f>SUM(K14:K16)</f>
         <v>1243.51</v>
@@ -2347,13 +2361,13 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="B19" s="157" t="s">
+      <c r="B19" s="159" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
@@ -2368,16 +2382,16 @@
       </c>
     </row>
     <row r="20" spans="1:29">
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="153"/>
-      <c r="D20" s="153"/>
-      <c r="E20" s="153"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="153"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="155"/>
+      <c r="G20" s="155"/>
+      <c r="H20" s="155"/>
+      <c r="I20" s="155"/>
       <c r="J20" s="47">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
@@ -2412,16 +2426,16 @@
       </c>
     </row>
     <row r="22" spans="1:29">
-      <c r="B22" s="153" t="s">
+      <c r="B22" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="155"/>
       <c r="J22" s="47">
         <v>0.16</v>
       </c>
@@ -2434,16 +2448,16 @@
       </c>
     </row>
     <row r="23" spans="1:29">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="147"/>
-      <c r="I23" s="147"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="149"/>
       <c r="J23" s="47">
         <v>0.02</v>
       </c>
@@ -2456,16 +2470,16 @@
       </c>
     </row>
     <row r="24" spans="1:29">
-      <c r="B24" s="151" t="s">
+      <c r="B24" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="151"/>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="151"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="153"/>
       <c r="J24" s="75"/>
       <c r="K24" s="76">
         <f>SUM(K20:K23)</f>
@@ -2476,29 +2490,29 @@
       </c>
     </row>
     <row r="25" spans="1:29">
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="153"/>
+      <c r="B25" s="155"/>
+      <c r="C25" s="155"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="155"/>
+      <c r="I25" s="155"/>
       <c r="J25" s="2"/>
       <c r="K25" s="33"/>
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="147"/>
-      <c r="G26" s="147"/>
-      <c r="H26" s="147"/>
-      <c r="I26" s="147"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="149"/>
       <c r="J26" s="48" t="s">
         <v>76</v>
       </c>
@@ -2511,16 +2525,16 @@
       </c>
     </row>
     <row r="27" spans="1:29">
-      <c r="B27" s="151" t="s">
+      <c r="B27" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="151"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
       <c r="K27" s="37">
         <f>K24+K26</f>
         <v>316.1151070046609</v>
@@ -2547,14 +2561,14 @@
       <c r="AC27"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B28" s="128"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
@@ -2575,13 +2589,13 @@
     </row>
     <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="93"/>
-      <c r="B29" s="160" t="s">
+      <c r="B29" s="162" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="161"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="163"/>
       <c r="G29" s="94"/>
       <c r="H29" s="95"/>
       <c r="I29" s="95"/>
@@ -2808,16 +2822,16 @@
     </row>
     <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="93"/>
-      <c r="B37" s="162" t="s">
+      <c r="B37" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="163"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="163"/>
-      <c r="F37" s="163"/>
-      <c r="G37" s="163"/>
-      <c r="H37" s="163"/>
-      <c r="I37" s="163"/>
+      <c r="C37" s="165"/>
+      <c r="D37" s="165"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="165"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="165"/>
       <c r="J37" s="110"/>
       <c r="K37" s="120">
         <f>SUM(K33+K35)-K36</f>
@@ -2843,18 +2857,18 @@
       <c r="L38" s="121"/>
       <c r="M38" s="110"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75">
-      <c r="B39" s="166" t="s">
+    <row r="39" spans="1:29" ht="15.6">
+      <c r="B39" s="168" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="166"/>
-      <c r="D39" s="166"/>
-      <c r="E39" s="166"/>
-      <c r="F39" s="166"/>
-      <c r="G39" s="166"/>
-      <c r="H39" s="166"/>
-      <c r="I39" s="166"/>
-      <c r="J39" s="166"/>
+      <c r="C39" s="168"/>
+      <c r="D39" s="168"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="168"/>
+      <c r="G39" s="168"/>
+      <c r="H39" s="168"/>
+      <c r="I39" s="168"/>
+      <c r="J39" s="168"/>
       <c r="K39" s="60" t="s">
         <v>34</v>
       </c>
@@ -2880,17 +2894,17 @@
       <c r="AC39"/>
     </row>
     <row r="40" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B40" s="153" t="s">
+      <c r="B40" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="153"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="153"/>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
       <c r="K40" s="37">
         <f>K37</f>
         <v>0</v>
@@ -2917,17 +2931,17 @@
       <c r="AC40"/>
     </row>
     <row r="41" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B41" s="153" t="s">
+      <c r="B41" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="153"/>
-      <c r="D41" s="153"/>
-      <c r="E41" s="153"/>
-      <c r="F41" s="153"/>
-      <c r="G41" s="153"/>
-      <c r="H41" s="153"/>
-      <c r="I41" s="153"/>
-      <c r="J41" s="153"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
       <c r="K41" s="37">
         <f>K27</f>
         <v>316.1151070046609</v>
@@ -2948,17 +2962,17 @@
       </c>
     </row>
     <row r="43" spans="1:29">
-      <c r="B43" s="164" t="s">
+      <c r="B43" s="166" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="164"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="164"/>
-      <c r="H43" s="164"/>
-      <c r="I43" s="164"/>
-      <c r="J43" s="164"/>
+      <c r="C43" s="166"/>
+      <c r="D43" s="166"/>
+      <c r="E43" s="166"/>
+      <c r="F43" s="166"/>
+      <c r="G43" s="166"/>
+      <c r="H43" s="166"/>
+      <c r="I43" s="166"/>
+      <c r="J43" s="166"/>
       <c r="K43" s="37">
         <v>0</v>
       </c>
@@ -2966,163 +2980,167 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B44" s="151" t="s">
+    <row r="44" spans="1:29" s="123" customFormat="1">
+      <c r="B44" s="124" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="124"/>
+      <c r="D44" s="124"/>
+      <c r="E44" s="124"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="124"/>
+      <c r="H44" s="124"/>
+      <c r="I44" s="124"/>
+      <c r="J44" s="124"/>
+      <c r="K44" s="37">
+        <v>0</v>
+      </c>
+      <c r="L44" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B45" s="153" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="151"/>
-      <c r="D44" s="151"/>
-      <c r="E44" s="151"/>
-      <c r="F44" s="151"/>
-      <c r="G44" s="151"/>
-      <c r="H44" s="151"/>
-      <c r="I44" s="151"/>
-      <c r="J44" s="151"/>
-      <c r="K44" s="76">
-        <f>SUM(K40:K43)</f>
+      <c r="C45" s="153"/>
+      <c r="D45" s="153"/>
+      <c r="E45" s="153"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="153"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="153"/>
+      <c r="J45" s="153"/>
+      <c r="K45" s="76">
+        <f>SUM(K40:K44)</f>
         <v>316.1151070046609</v>
       </c>
-      <c r="L44" s="75" t="s">
+      <c r="L45" s="75" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B45" s="165"/>
-      <c r="C45" s="165"/>
-      <c r="D45" s="165"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="165"/>
-      <c r="G45" s="165"/>
-      <c r="H45" s="165"/>
-      <c r="I45" s="165"/>
-      <c r="J45" s="165"/>
-      <c r="K45" s="165"/>
-      <c r="L45" s="165"/>
-    </row>
     <row r="46" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B46" s="141" t="s">
+      <c r="B46" s="167"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
+      <c r="E46" s="167"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
+    </row>
+    <row r="47" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B47" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="142"/>
-      <c r="I46" s="142"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="143"/>
-    </row>
-    <row r="47" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B47" s="46" t="s">
+      <c r="C47" s="144"/>
+      <c r="D47" s="144"/>
+      <c r="E47" s="144"/>
+      <c r="F47" s="144"/>
+      <c r="G47" s="144"/>
+      <c r="H47" s="144"/>
+      <c r="I47" s="144"/>
+      <c r="J47" s="144"/>
+      <c r="K47" s="144"/>
+      <c r="L47" s="145"/>
+    </row>
+    <row r="48" spans="1:29" ht="15.75" customHeight="1">
+      <c r="B48" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="136" t="s">
+      <c r="C48" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="137"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="7" t="s">
+      <c r="D48" s="139"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="136" t="s">
+      <c r="G48" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="H47" s="138"/>
-      <c r="I47" s="5" t="s">
+      <c r="H48" s="140"/>
+      <c r="I48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J47" s="54" t="s">
+      <c r="J48" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="167" t="s">
+      <c r="K48" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="L47" s="168"/>
-    </row>
-    <row r="48" spans="1:29">
-      <c r="B48" s="46">
+      <c r="L48" s="170"/>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" s="46">
         <v>1</v>
       </c>
-      <c r="C48" s="136" t="str">
+      <c r="C49" s="138" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D48" s="137"/>
-      <c r="E48" s="138"/>
-      <c r="F48" s="7">
+      <c r="D49" s="139"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="7">
         <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G48" s="139">
+      <c r="G49" s="141">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H48" s="140"/>
-      <c r="I48" s="55">
+      <c r="H49" s="142"/>
+      <c r="I49" s="55">
         <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
       </c>
-      <c r="J48" s="55">
-        <f t="shared" ref="J48" si="0">+F48*I48</f>
+      <c r="J49" s="55">
+        <f t="shared" ref="J49" si="0">+F49*I49</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K48" s="135">
-        <f t="shared" ref="K48" si="1">I48*3.7</f>
+      <c r="K49" s="137">
+        <f t="shared" ref="K49" si="1">I49*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L48" s="135"/>
-    </row>
-    <row r="49" spans="2:13" ht="15.75">
-      <c r="B49" s="49" t="s">
+      <c r="L49" s="137"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.6">
+      <c r="B50" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="36">
-        <f>+SUM(F48:F48)</f>
-        <v>100</v>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="J49" s="56">
-        <f>+SUM(J48:J48)</f>
-        <v>1142.4505892807642</v>
-      </c>
-      <c r="K49" s="77"/>
-      <c r="L49" s="78"/>
-    </row>
-    <row r="50" spans="2:13" ht="15.75">
-      <c r="B50" s="49"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="36"/>
+      <c r="F50" s="36">
+        <f>+SUM(F49:F49)</f>
+        <v>100</v>
+      </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="J50" s="62"/>
+      <c r="J50" s="56">
+        <f>+SUM(J49:J49)</f>
+        <v>1142.4505892807642</v>
+      </c>
       <c r="K50" s="77"/>
       <c r="L50" s="78"/>
     </row>
-    <row r="51" spans="2:13">
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="79"/>
-      <c r="L51" s="80"/>
-    </row>
-    <row r="52" spans="2:13" ht="18.75">
-      <c r="B52" s="61" t="s">
-        <v>53</v>
-      </c>
+    <row r="51" spans="2:13" ht="15.6">
+      <c r="B51" s="49"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="J51" s="62"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="78"/>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" s="29"/>
       <c r="C52" s="29"/>
       <c r="D52" s="29"/>
       <c r="E52" s="29"/>
@@ -3131,726 +3149,741 @@
       <c r="H52" s="29"/>
       <c r="I52" s="29"/>
       <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-    </row>
-    <row r="53" spans="2:13" ht="18.75">
-      <c r="B53" s="146" t="s">
+      <c r="K52" s="79"/>
+      <c r="L52" s="80"/>
+    </row>
+    <row r="53" spans="2:13" ht="18">
+      <c r="B53" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+    </row>
+    <row r="54" spans="2:13" ht="18">
+      <c r="B54" s="148" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="146"/>
-      <c r="D53" s="146"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="146"/>
-      <c r="G53" s="146"/>
-      <c r="H53" s="146"/>
-      <c r="I53" s="146"/>
-      <c r="J53" s="146"/>
-      <c r="K53" s="146"/>
-      <c r="L53" s="146"/>
-    </row>
-    <row r="54" spans="2:13" ht="18.75">
-      <c r="B54" s="146" t="s">
+      <c r="C54" s="148"/>
+      <c r="D54" s="148"/>
+      <c r="E54" s="148"/>
+      <c r="F54" s="148"/>
+      <c r="G54" s="148"/>
+      <c r="H54" s="148"/>
+      <c r="I54" s="148"/>
+      <c r="J54" s="148"/>
+      <c r="K54" s="148"/>
+      <c r="L54" s="148"/>
+    </row>
+    <row r="55" spans="2:13" ht="18">
+      <c r="B55" s="148" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="146"/>
-      <c r="D54" s="146"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="146"/>
-      <c r="G54" s="146"/>
-      <c r="H54" s="146"/>
-      <c r="I54" s="146"/>
-      <c r="J54" s="146"/>
-      <c r="K54" s="146"/>
-      <c r="L54" s="146"/>
-    </row>
-    <row r="55" spans="2:13" ht="18.75">
-      <c r="B55" s="146" t="s">
+      <c r="C55" s="148"/>
+      <c r="D55" s="148"/>
+      <c r="E55" s="148"/>
+      <c r="F55" s="148"/>
+      <c r="G55" s="148"/>
+      <c r="H55" s="148"/>
+      <c r="I55" s="148"/>
+      <c r="J55" s="148"/>
+      <c r="K55" s="148"/>
+      <c r="L55" s="148"/>
+    </row>
+    <row r="56" spans="2:13" ht="18">
+      <c r="B56" s="148" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="146"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="146"/>
-      <c r="G55" s="146"/>
-      <c r="H55" s="146"/>
-      <c r="I55" s="146"/>
-      <c r="J55" s="146"/>
-      <c r="K55" s="146"/>
-      <c r="L55" s="146"/>
-    </row>
-    <row r="56" spans="2:13" ht="18.75">
-      <c r="B56" s="146" t="s">
+      <c r="C56" s="148"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="148"/>
+      <c r="F56" s="148"/>
+      <c r="G56" s="148"/>
+      <c r="H56" s="148"/>
+      <c r="I56" s="148"/>
+      <c r="J56" s="148"/>
+      <c r="K56" s="148"/>
+      <c r="L56" s="148"/>
+    </row>
+    <row r="57" spans="2:13" ht="18">
+      <c r="B57" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="146"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="146"/>
-      <c r="H56" s="146"/>
-      <c r="I56" s="146"/>
-      <c r="J56" s="146"/>
-      <c r="K56" s="146"/>
-      <c r="L56" s="146"/>
-    </row>
-    <row r="57" spans="2:13" ht="18.75">
-      <c r="B57" s="146" t="s">
+      <c r="C57" s="148"/>
+      <c r="D57" s="148"/>
+      <c r="E57" s="148"/>
+      <c r="F57" s="148"/>
+      <c r="G57" s="148"/>
+      <c r="H57" s="148"/>
+      <c r="I57" s="148"/>
+      <c r="J57" s="148"/>
+      <c r="K57" s="148"/>
+      <c r="L57" s="148"/>
+    </row>
+    <row r="58" spans="2:13" ht="18">
+      <c r="B58" s="148" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="146"/>
-      <c r="D57" s="146"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="146"/>
-      <c r="G57" s="146"/>
-      <c r="H57" s="146"/>
-      <c r="I57" s="146"/>
-      <c r="J57" s="146"/>
-      <c r="K57" s="146"/>
-      <c r="L57" s="146"/>
-    </row>
-    <row r="58" spans="2:13">
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-    </row>
-    <row r="59" spans="2:13" ht="9" customHeight="1">
-      <c r="B59" s="124"/>
-      <c r="C59" s="124"/>
-      <c r="E59" s="124"/>
-      <c r="F59" s="124"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="124"/>
-      <c r="I59" s="124"/>
-      <c r="J59" s="124"/>
-      <c r="K59" s="124"/>
-      <c r="L59" s="124"/>
-      <c r="M59" s="124"/>
-    </row>
-    <row r="60" spans="2:13" ht="31.9" customHeight="1">
-      <c r="B60" s="124"/>
-      <c r="C60" s="124"/>
-      <c r="D60" s="159" t="s">
+      <c r="C58" s="148"/>
+      <c r="D58" s="148"/>
+      <c r="E58" s="148"/>
+      <c r="F58" s="148"/>
+      <c r="G58" s="148"/>
+      <c r="H58" s="148"/>
+      <c r="I58" s="148"/>
+      <c r="J58" s="148"/>
+      <c r="K58" s="148"/>
+      <c r="L58" s="148"/>
+    </row>
+    <row r="59" spans="2:13">
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+    </row>
+    <row r="60" spans="2:13" ht="9" customHeight="1">
+      <c r="B60" s="126"/>
+      <c r="C60" s="126"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="126"/>
+      <c r="I60" s="126"/>
+      <c r="J60" s="126"/>
+      <c r="K60" s="126"/>
+      <c r="L60" s="126"/>
+      <c r="M60" s="126"/>
+    </row>
+    <row r="61" spans="2:13" ht="31.95" customHeight="1">
+      <c r="B61" s="126"/>
+      <c r="C61" s="126"/>
+      <c r="D61" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="159"/>
-      <c r="F60" s="159"/>
-      <c r="G60" s="159"/>
-      <c r="H60" s="159"/>
-      <c r="I60" s="159"/>
-      <c r="J60" s="159"/>
-      <c r="K60" s="159"/>
-      <c r="L60" s="159"/>
-      <c r="M60" s="159"/>
-    </row>
-    <row r="61" spans="2:13" ht="21" customHeight="1">
-      <c r="B61" s="124"/>
-      <c r="C61" s="124"/>
-      <c r="D61" s="132" t="s">
+      <c r="E61" s="161"/>
+      <c r="F61" s="161"/>
+      <c r="G61" s="161"/>
+      <c r="H61" s="161"/>
+      <c r="I61" s="161"/>
+      <c r="J61" s="161"/>
+      <c r="K61" s="161"/>
+      <c r="L61" s="161"/>
+      <c r="M61" s="161"/>
+    </row>
+    <row r="62" spans="2:13" ht="21" customHeight="1">
+      <c r="B62" s="126"/>
+      <c r="C62" s="126"/>
+      <c r="D62" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="E61" s="132"/>
-      <c r="F61" s="132"/>
-      <c r="G61" s="132"/>
-      <c r="H61" s="132"/>
-      <c r="I61" s="132"/>
-    </row>
-    <row r="62" spans="2:13">
-      <c r="B62" s="124"/>
-      <c r="C62" s="124"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="134"/>
+      <c r="G62" s="134"/>
+      <c r="H62" s="134"/>
+      <c r="I62" s="134"/>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="124"/>
-      <c r="C63" s="124"/>
-    </row>
-    <row r="64" spans="2:13" ht="21">
-      <c r="B64" s="169" t="s">
+      <c r="B63" s="126"/>
+      <c r="C63" s="126"/>
+    </row>
+    <row r="64" spans="2:13">
+      <c r="B64" s="126"/>
+      <c r="C64" s="126"/>
+    </row>
+    <row r="65" spans="2:12" ht="21">
+      <c r="B65" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="169"/>
-      <c r="D64" s="169"/>
-      <c r="E64" s="169"/>
-      <c r="F64" s="169"/>
-      <c r="G64" s="169"/>
-      <c r="H64" s="169"/>
-      <c r="I64" s="169"/>
-      <c r="J64" s="169"/>
-      <c r="K64" s="169"/>
-      <c r="L64" s="169"/>
-    </row>
-    <row r="66" spans="2:12">
-      <c r="B66" s="154" t="s">
+      <c r="C65" s="171"/>
+      <c r="D65" s="171"/>
+      <c r="E65" s="171"/>
+      <c r="F65" s="171"/>
+      <c r="G65" s="171"/>
+      <c r="H65" s="171"/>
+      <c r="I65" s="171"/>
+      <c r="J65" s="171"/>
+      <c r="K65" s="171"/>
+      <c r="L65" s="171"/>
+    </row>
+    <row r="67" spans="2:12">
+      <c r="B67" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C66" s="154"/>
-      <c r="D66" s="154"/>
-      <c r="E66" s="154"/>
-      <c r="F66" s="154"/>
-      <c r="G66" s="154"/>
-      <c r="H66" s="154"/>
-      <c r="I66" s="154"/>
-      <c r="J66" s="154"/>
-      <c r="K66" s="154"/>
-      <c r="L66" s="154"/>
-    </row>
-    <row r="67" spans="2:12">
-      <c r="B67" s="154" t="s">
+      <c r="C67" s="156"/>
+      <c r="D67" s="156"/>
+      <c r="E67" s="156"/>
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="156"/>
+      <c r="K67" s="156"/>
+      <c r="L67" s="156"/>
+    </row>
+    <row r="68" spans="2:12">
+      <c r="B68" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="154"/>
-      <c r="D67" s="154"/>
-      <c r="E67" s="154"/>
-      <c r="F67" s="154"/>
-      <c r="G67" s="154"/>
-      <c r="H67" s="154"/>
-      <c r="I67" s="154"/>
-      <c r="J67" s="154"/>
-      <c r="K67" s="154"/>
-      <c r="L67" s="154"/>
-    </row>
-    <row r="68" spans="2:12">
-      <c r="B68" s="153" t="s">
+      <c r="C68" s="156"/>
+      <c r="D68" s="156"/>
+      <c r="E68" s="156"/>
+      <c r="F68" s="156"/>
+      <c r="G68" s="156"/>
+      <c r="H68" s="156"/>
+      <c r="I68" s="156"/>
+      <c r="J68" s="156"/>
+      <c r="K68" s="156"/>
+      <c r="L68" s="156"/>
+    </row>
+    <row r="69" spans="2:12">
+      <c r="B69" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="C68" s="153"/>
-      <c r="D68" s="153"/>
-      <c r="E68" s="153"/>
-      <c r="F68" s="153"/>
-      <c r="G68" s="153"/>
-      <c r="H68" s="153"/>
-      <c r="I68" s="153"/>
-      <c r="J68" s="153"/>
-      <c r="K68" s="153"/>
-      <c r="L68" s="153"/>
-    </row>
-    <row r="69" spans="2:12">
-      <c r="B69" s="154" t="s">
+      <c r="C69" s="155"/>
+      <c r="D69" s="155"/>
+      <c r="E69" s="155"/>
+      <c r="F69" s="155"/>
+      <c r="G69" s="155"/>
+      <c r="H69" s="155"/>
+      <c r="I69" s="155"/>
+      <c r="J69" s="155"/>
+      <c r="K69" s="155"/>
+      <c r="L69" s="155"/>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="B70" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="154"/>
-      <c r="D69" s="154"/>
-      <c r="E69" s="154"/>
-      <c r="F69" s="154"/>
-      <c r="G69" s="154"/>
-      <c r="H69" s="154"/>
-      <c r="I69" s="154"/>
-      <c r="J69" s="154"/>
-      <c r="K69" s="154"/>
-      <c r="L69" s="154"/>
-    </row>
-    <row r="70" spans="2:12">
-      <c r="B70" s="154" t="s">
+      <c r="C70" s="156"/>
+      <c r="D70" s="156"/>
+      <c r="E70" s="156"/>
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="156"/>
+      <c r="I70" s="156"/>
+      <c r="J70" s="156"/>
+      <c r="K70" s="156"/>
+      <c r="L70" s="156"/>
+    </row>
+    <row r="71" spans="2:12">
+      <c r="B71" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="154"/>
-      <c r="D70" s="154"/>
-      <c r="E70" s="154"/>
-      <c r="F70" s="154"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="154"/>
-      <c r="I70" s="154"/>
-      <c r="J70" s="154"/>
-      <c r="K70" s="154"/>
-      <c r="L70" s="154"/>
-    </row>
-    <row r="71" spans="2:12">
-      <c r="B71" s="153" t="s">
+      <c r="C71" s="156"/>
+      <c r="D71" s="156"/>
+      <c r="E71" s="156"/>
+      <c r="F71" s="156"/>
+      <c r="G71" s="156"/>
+      <c r="H71" s="156"/>
+      <c r="I71" s="156"/>
+      <c r="J71" s="156"/>
+      <c r="K71" s="156"/>
+      <c r="L71" s="156"/>
+    </row>
+    <row r="72" spans="2:12">
+      <c r="B72" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="153"/>
-      <c r="D71" s="153"/>
-      <c r="E71" s="153"/>
-      <c r="F71" s="153"/>
-      <c r="G71" s="153"/>
-      <c r="H71" s="153"/>
-      <c r="I71" s="153"/>
-      <c r="J71" s="153"/>
-      <c r="K71" s="153"/>
-      <c r="L71" s="153"/>
-    </row>
-    <row r="72" spans="2:12">
-      <c r="B72" s="154" t="s">
+      <c r="C72" s="155"/>
+      <c r="D72" s="155"/>
+      <c r="E72" s="155"/>
+      <c r="F72" s="155"/>
+      <c r="G72" s="155"/>
+      <c r="H72" s="155"/>
+      <c r="I72" s="155"/>
+      <c r="J72" s="155"/>
+      <c r="K72" s="155"/>
+      <c r="L72" s="155"/>
+    </row>
+    <row r="73" spans="2:12">
+      <c r="B73" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="C72" s="154"/>
-      <c r="D72" s="154"/>
-      <c r="E72" s="154"/>
-      <c r="F72" s="154"/>
-      <c r="G72" s="154"/>
-      <c r="H72" s="154"/>
-      <c r="I72" s="154"/>
-      <c r="J72" s="154"/>
-      <c r="K72" s="154"/>
-      <c r="L72" s="154"/>
-    </row>
-    <row r="73" spans="2:12">
-      <c r="B73" s="154" t="s">
+      <c r="C73" s="156"/>
+      <c r="D73" s="156"/>
+      <c r="E73" s="156"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="156"/>
+      <c r="H73" s="156"/>
+      <c r="I73" s="156"/>
+      <c r="J73" s="156"/>
+      <c r="K73" s="156"/>
+      <c r="L73" s="156"/>
+    </row>
+    <row r="74" spans="2:12">
+      <c r="B74" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="154"/>
-      <c r="D73" s="154"/>
-      <c r="E73" s="154"/>
-      <c r="F73" s="154"/>
-      <c r="G73" s="154"/>
-      <c r="H73" s="154"/>
-      <c r="I73" s="154"/>
-      <c r="J73" s="154"/>
-      <c r="K73" s="154"/>
-      <c r="L73" s="154"/>
-    </row>
-    <row r="74" spans="2:12">
-      <c r="B74" s="154" t="s">
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="156"/>
+      <c r="G74" s="156"/>
+      <c r="H74" s="156"/>
+      <c r="I74" s="156"/>
+      <c r="J74" s="156"/>
+      <c r="K74" s="156"/>
+      <c r="L74" s="156"/>
+    </row>
+    <row r="75" spans="2:12">
+      <c r="B75" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="C74" s="154"/>
-      <c r="D74" s="154"/>
-      <c r="E74" s="154"/>
-      <c r="F74" s="154"/>
-      <c r="G74" s="154"/>
-      <c r="H74" s="154"/>
-      <c r="I74" s="154"/>
-      <c r="J74" s="154"/>
-      <c r="K74" s="154"/>
-      <c r="L74" s="154"/>
-    </row>
-    <row r="75" spans="2:12">
-      <c r="B75" s="154" t="s">
+      <c r="C75" s="156"/>
+      <c r="D75" s="156"/>
+      <c r="E75" s="156"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
+      <c r="H75" s="156"/>
+      <c r="I75" s="156"/>
+      <c r="J75" s="156"/>
+      <c r="K75" s="156"/>
+      <c r="L75" s="156"/>
+    </row>
+    <row r="76" spans="2:12">
+      <c r="B76" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="C75" s="154"/>
-      <c r="D75" s="154"/>
-      <c r="E75" s="154"/>
-      <c r="F75" s="154"/>
-      <c r="G75" s="154"/>
-      <c r="H75" s="154"/>
-      <c r="I75" s="154"/>
-      <c r="J75" s="154"/>
-      <c r="K75" s="154"/>
-      <c r="L75" s="154"/>
-    </row>
-    <row r="76" spans="2:12">
-      <c r="B76" s="154" t="s">
+      <c r="C76" s="156"/>
+      <c r="D76" s="156"/>
+      <c r="E76" s="156"/>
+      <c r="F76" s="156"/>
+      <c r="G76" s="156"/>
+      <c r="H76" s="156"/>
+      <c r="I76" s="156"/>
+      <c r="J76" s="156"/>
+      <c r="K76" s="156"/>
+      <c r="L76" s="156"/>
+    </row>
+    <row r="77" spans="2:12">
+      <c r="B77" s="156" t="s">
         <v>62</v>
       </c>
-      <c r="C76" s="154"/>
-      <c r="D76" s="154"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="154"/>
-      <c r="H76" s="154"/>
-      <c r="I76" s="154"/>
-      <c r="J76" s="154"/>
-      <c r="K76" s="154"/>
-      <c r="L76" s="154"/>
-    </row>
-    <row r="77" spans="2:12">
-      <c r="B77" s="154" t="s">
+      <c r="C77" s="156"/>
+      <c r="D77" s="156"/>
+      <c r="E77" s="156"/>
+      <c r="F77" s="156"/>
+      <c r="G77" s="156"/>
+      <c r="H77" s="156"/>
+      <c r="I77" s="156"/>
+      <c r="J77" s="156"/>
+      <c r="K77" s="156"/>
+      <c r="L77" s="156"/>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="C77" s="154"/>
-      <c r="D77" s="154"/>
-      <c r="E77" s="154"/>
-      <c r="F77" s="154"/>
-      <c r="G77" s="154"/>
-      <c r="H77" s="154"/>
-      <c r="I77" s="154"/>
-      <c r="J77" s="154"/>
-      <c r="K77" s="154"/>
-      <c r="L77" s="154"/>
-    </row>
-    <row r="78" spans="2:12">
-      <c r="B78" s="154" t="s">
+      <c r="C78" s="156"/>
+      <c r="D78" s="156"/>
+      <c r="E78" s="156"/>
+      <c r="F78" s="156"/>
+      <c r="G78" s="156"/>
+      <c r="H78" s="156"/>
+      <c r="I78" s="156"/>
+      <c r="J78" s="156"/>
+      <c r="K78" s="156"/>
+      <c r="L78" s="156"/>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="154"/>
-      <c r="D78" s="154"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="154"/>
-      <c r="G78" s="154"/>
-      <c r="H78" s="154"/>
-      <c r="I78" s="154"/>
-      <c r="J78" s="154"/>
-      <c r="K78" s="154"/>
-      <c r="L78" s="154"/>
-    </row>
-    <row r="79" spans="2:12">
-      <c r="B79" s="154" t="s">
+      <c r="C79" s="156"/>
+      <c r="D79" s="156"/>
+      <c r="E79" s="156"/>
+      <c r="F79" s="156"/>
+      <c r="G79" s="156"/>
+      <c r="H79" s="156"/>
+      <c r="I79" s="156"/>
+      <c r="J79" s="156"/>
+      <c r="K79" s="156"/>
+      <c r="L79" s="156"/>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="B80" s="156" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="154"/>
-      <c r="D79" s="154"/>
-      <c r="E79" s="154"/>
-      <c r="F79" s="154"/>
-      <c r="G79" s="154"/>
-      <c r="H79" s="154"/>
-      <c r="I79" s="154"/>
-      <c r="J79" s="154"/>
-      <c r="K79" s="154"/>
-      <c r="L79" s="154"/>
-    </row>
-    <row r="80" spans="2:12">
-      <c r="B80" s="154" t="s">
+      <c r="C80" s="156"/>
+      <c r="D80" s="156"/>
+      <c r="E80" s="156"/>
+      <c r="F80" s="156"/>
+      <c r="G80" s="156"/>
+      <c r="H80" s="156"/>
+      <c r="I80" s="156"/>
+      <c r="J80" s="156"/>
+      <c r="K80" s="156"/>
+      <c r="L80" s="156"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="B81" s="156" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="154"/>
-      <c r="D80" s="154"/>
-      <c r="E80" s="154"/>
-      <c r="F80" s="154"/>
-      <c r="G80" s="154"/>
-      <c r="H80" s="154"/>
-      <c r="I80" s="154"/>
-      <c r="J80" s="154"/>
-      <c r="K80" s="154"/>
-      <c r="L80" s="154"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="B81" s="154" t="s">
+      <c r="C81" s="156"/>
+      <c r="D81" s="156"/>
+      <c r="E81" s="156"/>
+      <c r="F81" s="156"/>
+      <c r="G81" s="156"/>
+      <c r="H81" s="156"/>
+      <c r="I81" s="156"/>
+      <c r="J81" s="156"/>
+      <c r="K81" s="156"/>
+      <c r="L81" s="156"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="B82" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="C81" s="154"/>
-      <c r="D81" s="154"/>
-      <c r="E81" s="154"/>
-      <c r="F81" s="154"/>
-      <c r="G81" s="154"/>
-      <c r="H81" s="154"/>
-      <c r="I81" s="154"/>
-      <c r="J81" s="154"/>
-      <c r="K81" s="154"/>
-      <c r="L81" s="154"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="B82" s="154" t="s">
+      <c r="C82" s="156"/>
+      <c r="D82" s="156"/>
+      <c r="E82" s="156"/>
+      <c r="F82" s="156"/>
+      <c r="G82" s="156"/>
+      <c r="H82" s="156"/>
+      <c r="I82" s="156"/>
+      <c r="J82" s="156"/>
+      <c r="K82" s="156"/>
+      <c r="L82" s="156"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="B83" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="C82" s="154"/>
-      <c r="D82" s="154"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="154"/>
-      <c r="G82" s="154"/>
-      <c r="H82" s="154"/>
-      <c r="I82" s="154"/>
-      <c r="J82" s="154"/>
-      <c r="K82" s="154"/>
-      <c r="L82" s="154"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="B83" s="150" t="s">
+      <c r="C83" s="156"/>
+      <c r="D83" s="156"/>
+      <c r="E83" s="156"/>
+      <c r="F83" s="156"/>
+      <c r="G83" s="156"/>
+      <c r="H83" s="156"/>
+      <c r="I83" s="156"/>
+      <c r="J83" s="156"/>
+      <c r="K83" s="156"/>
+      <c r="L83" s="156"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="B84" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="C83" s="150"/>
-      <c r="D83" s="150"/>
-      <c r="E83" s="150"/>
-      <c r="F83" s="150"/>
-      <c r="G83" s="150"/>
-      <c r="H83" s="150"/>
-      <c r="I83" s="150"/>
-      <c r="J83" s="150"/>
-      <c r="K83" s="150"/>
-      <c r="L83" s="150"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="B84" s="154" t="s">
+      <c r="C84" s="152"/>
+      <c r="D84" s="152"/>
+      <c r="E84" s="152"/>
+      <c r="F84" s="152"/>
+      <c r="G84" s="152"/>
+      <c r="H84" s="152"/>
+      <c r="I84" s="152"/>
+      <c r="J84" s="152"/>
+      <c r="K84" s="152"/>
+      <c r="L84" s="152"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="B85" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
-      <c r="E84" s="154"/>
-      <c r="F84" s="154"/>
-      <c r="G84" s="154"/>
-      <c r="H84" s="154"/>
-      <c r="I84" s="154"/>
-      <c r="J84" s="154"/>
-      <c r="K84" s="154"/>
-      <c r="L84" s="154"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="B85" s="150" t="s">
+      <c r="C85" s="156"/>
+      <c r="D85" s="156"/>
+      <c r="E85" s="156"/>
+      <c r="F85" s="156"/>
+      <c r="G85" s="156"/>
+      <c r="H85" s="156"/>
+      <c r="I85" s="156"/>
+      <c r="J85" s="156"/>
+      <c r="K85" s="156"/>
+      <c r="L85" s="156"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="B86" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="C85" s="150"/>
-      <c r="D85" s="150"/>
-      <c r="E85" s="150"/>
-      <c r="F85" s="150"/>
-      <c r="G85" s="150"/>
-      <c r="H85" s="150"/>
-      <c r="I85" s="150"/>
-      <c r="J85" s="150"/>
-      <c r="K85" s="150"/>
-      <c r="L85" s="150"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="B86" s="154" t="s">
+      <c r="C86" s="152"/>
+      <c r="D86" s="152"/>
+      <c r="E86" s="152"/>
+      <c r="F86" s="152"/>
+      <c r="G86" s="152"/>
+      <c r="H86" s="152"/>
+      <c r="I86" s="152"/>
+      <c r="J86" s="152"/>
+      <c r="K86" s="152"/>
+      <c r="L86" s="152"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="B87" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C86" s="154"/>
-      <c r="D86" s="154"/>
-      <c r="E86" s="154"/>
-      <c r="F86" s="154"/>
-      <c r="G86" s="154"/>
-      <c r="H86" s="154"/>
-      <c r="I86" s="154"/>
-      <c r="J86" s="154"/>
-      <c r="K86" s="154"/>
-      <c r="L86" s="154"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="B87" s="154" t="s">
+      <c r="C87" s="156"/>
+      <c r="D87" s="156"/>
+      <c r="E87" s="156"/>
+      <c r="F87" s="156"/>
+      <c r="G87" s="156"/>
+      <c r="H87" s="156"/>
+      <c r="I87" s="156"/>
+      <c r="J87" s="156"/>
+      <c r="K87" s="156"/>
+      <c r="L87" s="156"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="B88" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="C87" s="154"/>
-      <c r="D87" s="154"/>
-      <c r="E87" s="154"/>
-      <c r="F87" s="154"/>
-      <c r="G87" s="154"/>
-      <c r="H87" s="154"/>
-      <c r="I87" s="154"/>
-      <c r="J87" s="154"/>
-      <c r="K87" s="154"/>
-      <c r="L87" s="154"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="B88" s="154" t="s">
+      <c r="C88" s="156"/>
+      <c r="D88" s="156"/>
+      <c r="E88" s="156"/>
+      <c r="F88" s="156"/>
+      <c r="G88" s="156"/>
+      <c r="H88" s="156"/>
+      <c r="I88" s="156"/>
+      <c r="J88" s="156"/>
+      <c r="K88" s="156"/>
+      <c r="L88" s="156"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="B89" s="156" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="154"/>
-      <c r="D88" s="154"/>
-      <c r="E88" s="154"/>
-      <c r="F88" s="154"/>
-      <c r="G88" s="154"/>
-      <c r="H88" s="154"/>
-      <c r="I88" s="154"/>
-      <c r="J88" s="154"/>
-      <c r="K88" s="154"/>
-      <c r="L88" s="154"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="B89" s="154" t="s">
+      <c r="C89" s="156"/>
+      <c r="D89" s="156"/>
+      <c r="E89" s="156"/>
+      <c r="F89" s="156"/>
+      <c r="G89" s="156"/>
+      <c r="H89" s="156"/>
+      <c r="I89" s="156"/>
+      <c r="J89" s="156"/>
+      <c r="K89" s="156"/>
+      <c r="L89" s="156"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="156" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="154"/>
-      <c r="D89" s="154"/>
-      <c r="E89" s="154"/>
-      <c r="F89" s="154"/>
-      <c r="G89" s="154"/>
-      <c r="H89" s="154"/>
-      <c r="I89" s="154"/>
-      <c r="J89" s="154"/>
-      <c r="K89" s="154"/>
-      <c r="L89" s="154"/>
-    </row>
-    <row r="90" spans="1:12">
-      <c r="B90" s="154" t="s">
+      <c r="C90" s="156"/>
+      <c r="D90" s="156"/>
+      <c r="E90" s="156"/>
+      <c r="F90" s="156"/>
+      <c r="G90" s="156"/>
+      <c r="H90" s="156"/>
+      <c r="I90" s="156"/>
+      <c r="J90" s="156"/>
+      <c r="K90" s="156"/>
+      <c r="L90" s="156"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="C90" s="154"/>
-      <c r="D90" s="154"/>
-      <c r="E90" s="154"/>
-      <c r="F90" s="154"/>
-      <c r="G90" s="154"/>
-      <c r="H90" s="154"/>
-      <c r="I90" s="154"/>
-      <c r="J90" s="154"/>
-      <c r="K90" s="154"/>
-      <c r="L90" s="154"/>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="A91" s="85"/>
-      <c r="B91" s="155" t="s">
-        <v>84</v>
-      </c>
-      <c r="C91" s="155"/>
-      <c r="D91" s="155"/>
-      <c r="E91" s="155"/>
-      <c r="F91" s="155"/>
-      <c r="G91" s="155"/>
-      <c r="H91" s="155"/>
-      <c r="I91" s="155"/>
-      <c r="J91" s="155"/>
-      <c r="K91" s="155"/>
-      <c r="L91" s="155"/>
+      <c r="C91" s="156"/>
+      <c r="D91" s="156"/>
+      <c r="E91" s="156"/>
+      <c r="F91" s="156"/>
+      <c r="G91" s="156"/>
+      <c r="H91" s="156"/>
+      <c r="I91" s="156"/>
+      <c r="J91" s="156"/>
+      <c r="K91" s="156"/>
+      <c r="L91" s="156"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="85"/>
-      <c r="B92" s="154" t="s">
-        <v>85</v>
-      </c>
-      <c r="C92" s="154"/>
-      <c r="D92" s="154"/>
-      <c r="E92" s="154"/>
-      <c r="F92" s="154"/>
-      <c r="G92" s="154"/>
-      <c r="H92" s="154"/>
-      <c r="I92" s="154"/>
-      <c r="J92" s="154"/>
-      <c r="K92" s="154"/>
-      <c r="L92" s="154"/>
+      <c r="B92" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="157"/>
+      <c r="D92" s="157"/>
+      <c r="E92" s="157"/>
+      <c r="F92" s="157"/>
+      <c r="G92" s="157"/>
+      <c r="H92" s="157"/>
+      <c r="I92" s="157"/>
+      <c r="J92" s="157"/>
+      <c r="K92" s="157"/>
+      <c r="L92" s="157"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="85"/>
-      <c r="B93" s="155" t="s">
+      <c r="B93" s="156" t="s">
+        <v>85</v>
+      </c>
+      <c r="C93" s="156"/>
+      <c r="D93" s="156"/>
+      <c r="E93" s="156"/>
+      <c r="F93" s="156"/>
+      <c r="G93" s="156"/>
+      <c r="H93" s="156"/>
+      <c r="I93" s="156"/>
+      <c r="J93" s="156"/>
+      <c r="K93" s="156"/>
+      <c r="L93" s="156"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="85"/>
+      <c r="B94" s="157" t="s">
         <v>86</v>
       </c>
-      <c r="C93" s="155"/>
-      <c r="D93" s="155"/>
-      <c r="E93" s="155"/>
-      <c r="F93" s="155"/>
-      <c r="G93" s="155"/>
-      <c r="H93" s="155"/>
-      <c r="I93" s="155"/>
-      <c r="J93" s="155"/>
-      <c r="K93" s="155"/>
-      <c r="L93" s="155"/>
-    </row>
-    <row r="95" spans="1:12">
-      <c r="C95" s="124"/>
-      <c r="D95" s="124"/>
-      <c r="E95" s="124"/>
-      <c r="F95" s="124"/>
-      <c r="G95" s="124"/>
-      <c r="H95" s="124"/>
-      <c r="I95" s="124"/>
+      <c r="C94" s="157"/>
+      <c r="D94" s="157"/>
+      <c r="E94" s="157"/>
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="157"/>
+      <c r="K94" s="157"/>
+      <c r="L94" s="157"/>
     </row>
     <row r="96" spans="1:12">
-      <c r="C96" s="124"/>
-      <c r="D96" s="124"/>
-      <c r="E96" s="124"/>
-      <c r="F96" s="124"/>
-      <c r="G96" s="124"/>
-      <c r="H96" s="124"/>
-      <c r="I96" s="124"/>
+      <c r="C96" s="126"/>
+      <c r="D96" s="126"/>
+      <c r="E96" s="126"/>
+      <c r="F96" s="126"/>
+      <c r="G96" s="126"/>
+      <c r="H96" s="126"/>
+      <c r="I96" s="126"/>
     </row>
     <row r="97" spans="3:9">
-      <c r="C97" s="124"/>
-      <c r="D97" s="124"/>
-      <c r="E97" s="124"/>
-      <c r="F97" s="124"/>
-      <c r="G97" s="124"/>
-      <c r="H97" s="124"/>
-      <c r="I97" s="124"/>
+      <c r="C97" s="126"/>
+      <c r="D97" s="126"/>
+      <c r="E97" s="126"/>
+      <c r="F97" s="126"/>
+      <c r="G97" s="126"/>
+      <c r="H97" s="126"/>
+      <c r="I97" s="126"/>
     </row>
     <row r="98" spans="3:9">
-      <c r="C98" s="124"/>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="124"/>
+      <c r="C98" s="126"/>
+      <c r="D98" s="126"/>
+      <c r="E98" s="126"/>
+      <c r="F98" s="126"/>
+      <c r="G98" s="126"/>
+      <c r="H98" s="126"/>
+      <c r="I98" s="126"/>
     </row>
     <row r="99" spans="3:9">
-      <c r="C99" s="124"/>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="124"/>
+      <c r="C99" s="126"/>
+      <c r="D99" s="126"/>
+      <c r="E99" s="126"/>
+      <c r="F99" s="126"/>
+      <c r="G99" s="126"/>
+      <c r="H99" s="126"/>
+      <c r="I99" s="126"/>
     </row>
     <row r="100" spans="3:9">
-      <c r="C100" s="124"/>
-      <c r="D100" s="124"/>
-      <c r="E100" s="124"/>
-      <c r="F100" s="124"/>
-      <c r="G100" s="124"/>
-      <c r="H100" s="124"/>
-      <c r="I100" s="124"/>
+      <c r="C100" s="126"/>
+      <c r="D100" s="126"/>
+      <c r="E100" s="126"/>
+      <c r="F100" s="126"/>
+      <c r="G100" s="126"/>
+      <c r="H100" s="126"/>
+      <c r="I100" s="126"/>
     </row>
     <row r="101" spans="3:9">
-      <c r="C101" s="124"/>
-      <c r="D101" s="124"/>
-      <c r="E101" s="124"/>
-      <c r="F101" s="124"/>
-      <c r="G101" s="124"/>
-      <c r="H101" s="124"/>
-      <c r="I101" s="124"/>
-    </row>
-    <row r="102" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C102" s="124"/>
-      <c r="D102" s="124"/>
-      <c r="E102" s="124"/>
-      <c r="F102" s="124"/>
-      <c r="G102" s="124"/>
-      <c r="H102" s="124"/>
-      <c r="I102" s="124"/>
+      <c r="C101" s="126"/>
+      <c r="D101" s="126"/>
+      <c r="E101" s="126"/>
+      <c r="F101" s="126"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="126"/>
+      <c r="I101" s="126"/>
+    </row>
+    <row r="102" spans="3:9">
+      <c r="C102" s="126"/>
+      <c r="D102" s="126"/>
+      <c r="E102" s="126"/>
+      <c r="F102" s="126"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="126"/>
+      <c r="I102" s="126"/>
     </row>
     <row r="103" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C103" s="124"/>
-      <c r="D103" s="124"/>
-      <c r="E103" s="124"/>
-      <c r="F103" s="124"/>
-      <c r="G103" s="124"/>
-      <c r="H103" s="124"/>
-      <c r="I103" s="124"/>
-    </row>
-    <row r="104" spans="3:9">
-      <c r="C104" s="124"/>
-      <c r="D104" s="124"/>
-      <c r="E104" s="124"/>
-      <c r="F104" s="124"/>
-      <c r="G104" s="124"/>
-      <c r="H104" s="124"/>
-      <c r="I104" s="124"/>
-    </row>
-    <row r="110" spans="3:9" ht="15.6" customHeight="1"/>
+      <c r="C103" s="126"/>
+      <c r="D103" s="126"/>
+      <c r="E103" s="126"/>
+      <c r="F103" s="126"/>
+      <c r="G103" s="126"/>
+      <c r="H103" s="126"/>
+      <c r="I103" s="126"/>
+    </row>
+    <row r="104" spans="3:9" ht="15.6" customHeight="1">
+      <c r="C104" s="126"/>
+      <c r="D104" s="126"/>
+      <c r="E104" s="126"/>
+      <c r="F104" s="126"/>
+      <c r="G104" s="126"/>
+      <c r="H104" s="126"/>
+      <c r="I104" s="126"/>
+    </row>
+    <row r="105" spans="3:9">
+      <c r="C105" s="126"/>
+      <c r="D105" s="126"/>
+      <c r="E105" s="126"/>
+      <c r="F105" s="126"/>
+      <c r="G105" s="126"/>
+      <c r="H105" s="126"/>
+      <c r="I105" s="126"/>
+    </row>
+    <row r="111" spans="3:9" ht="15.6" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="86">
-    <mergeCell ref="B83:L83"/>
     <mergeCell ref="B84:L84"/>
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="E59:M59"/>
-    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="B85:L85"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="E60:M60"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B67:L67"/>
     <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B66:L66"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="B65:L65"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="B59:C63"/>
+    <mergeCell ref="B60:C64"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="D60:J60"/>
-    <mergeCell ref="K60:M60"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="D61:J61"/>
+    <mergeCell ref="K61:M61"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B45:L45"/>
-    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B45:J45"/>
     <mergeCell ref="B39:J39"/>
     <mergeCell ref="B40:J40"/>
     <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B93:L93"/>
-    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B94:L94"/>
     <mergeCell ref="B77:L77"/>
     <mergeCell ref="B78:L78"/>
-    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B79:L79"/>
     <mergeCell ref="B70:L70"/>
     <mergeCell ref="B71:L71"/>
     <mergeCell ref="B72:L72"/>
     <mergeCell ref="B73:L73"/>
     <mergeCell ref="B74:L74"/>
     <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="B76:L76"/>
     <mergeCell ref="B81:L81"/>
     <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B93:L93"/>
     <mergeCell ref="B92:L92"/>
     <mergeCell ref="B91:L91"/>
-    <mergeCell ref="B90:L90"/>
-    <mergeCell ref="B85:L85"/>
     <mergeCell ref="B86:L86"/>
     <mergeCell ref="B87:L87"/>
     <mergeCell ref="B88:L88"/>
     <mergeCell ref="B89:L89"/>
+    <mergeCell ref="B90:L90"/>
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B20:I20"/>
@@ -3864,21 +3897,21 @@
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B16:J16"/>
-    <mergeCell ref="C95:I104"/>
+    <mergeCell ref="C96:I105"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D61:I61"/>
+    <mergeCell ref="D62:I62"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="G48:H48"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B47:L47"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B55:L55"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B2:C6"/>
@@ -3904,7 +3937,7 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="71" fitToWidth="2" fitToHeight="2" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="58" max="12" man="1"/>
+    <brk id="59" max="12" man="1"/>
   </rowBreaks>
   <cellWatches>
     <cellWatch r="K17"/>
@@ -3920,28 +3953,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A3:AG50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="11.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="2"/>
-    <col min="8" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" style="1" customWidth="1"/>
-    <col min="12" max="32" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="11.44140625" style="2"/>
+    <col min="8" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="32" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
       <c r="B6" s="70" t="s">
@@ -3991,14 +4024,14 @@
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="170" t="s">
+      <c r="J8" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="170"/>
-      <c r="M8" s="170" t="s">
+      <c r="K8" s="172"/>
+      <c r="M8" s="172" t="s">
         <v>107</v>
       </c>
-      <c r="N8" s="170"/>
+      <c r="N8" s="172"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
@@ -4471,14 +4504,14 @@
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="171" t="s">
+      <c r="B23" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="171"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="173"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
@@ -4744,14 +4777,14 @@
       <c r="AF35"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="B36" s="173" t="s">
+      <c r="B36" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="173"/>
-      <c r="D36" s="173"/>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="173"/>
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="175"/>
+      <c r="G36" s="175"/>
     </row>
     <row r="38" spans="1:32">
       <c r="C38" s="21">

--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F696C-A1AD-4EC8-8EAC-308E0B22255E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2FE29A-C464-4B82-8530-7D4F0ECD29AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19520" yWindow="320" windowWidth="14400" windowHeight="7310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -23,15 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -573,9 +564,6 @@
     <t>COTIZACION N002</t>
   </si>
   <si>
-    <t>MEDIDA:</t>
-  </si>
-  <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
   <si>
@@ -622,13 +610,16 @@
   </si>
   <si>
     <t>RECARGOS ADUANEROS (BQ O SANCIONES)</t>
+  </si>
+  <si>
+    <t>QTY PROVEEDORES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="13">
+  <numFmts count="12">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;S/&quot;* #,##0.00_-;\-&quot;S/&quot;* #,##0.00_-;_-&quot;S/&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -636,7 +627,6 @@
     <numFmt numFmtId="167" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="168" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="169" formatCode="#,##0.000\ &quot;m3&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0\ &quot;cm&quot;"/>
     <numFmt numFmtId="171" formatCode="0.0\ &quot;kg&quot;"/>
     <numFmt numFmtId="172" formatCode="_-[$S/-280A]\ * #,##0.00_-;\-[$S/-280A]\ * #,##0.00_-;_-[$S/-280A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="173" formatCode="_-[$$-409]* #,##0.0_ ;_-[$$-409]* \-#,##0.0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -1207,7 +1197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1477,7 +1467,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1535,9 +1524,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1601,6 +1587,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2040,100 +2029,100 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AC111"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="0.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="0.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.6640625" style="1"/>
+    <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="0.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="0.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="130"/>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
+      <c r="A1" s="129"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-    </row>
-    <row r="3" spans="1:12" ht="25.8">
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="E3" s="135" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="135"/>
-    </row>
-    <row r="4" spans="1:12" ht="25.8">
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="E4" s="136" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+    </row>
+    <row r="3" spans="1:12" ht="26.25">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="E3" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+    </row>
+    <row r="4" spans="1:12" ht="26.25">
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="E4" s="135" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
       <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
       <c r="D5" s="89"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
       <c r="D6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="126"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="E7" s="127" t="s">
+      <c r="A7" s="125"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="125"/>
+      <c r="E7" s="126" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
@@ -2146,20 +2135,20 @@
       <c r="E8" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="132" t="s">
+      <c r="F8" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="133"/>
+      <c r="G8" s="132"/>
       <c r="H8" s="86"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="146">
+      <c r="J8" s="145">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="146"/>
-      <c r="L8" s="146"/>
+      <c r="K8" s="145"/>
+      <c r="L8" s="145"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
@@ -2172,21 +2161,21 @@
       <c r="E9" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="128">
+      <c r="F9" s="127">
         <f ca="1">+TODAY()</f>
-        <v>46128</v>
-      </c>
-      <c r="G9" s="129"/>
+        <v>46140</v>
+      </c>
+      <c r="G9" s="128"/>
       <c r="H9" s="86"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="125">
+      <c r="J9" s="124">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
+      <c r="K9" s="124"/>
+      <c r="L9" s="124"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
@@ -2199,19 +2188,19 @@
       <c r="E10" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="130" t="s">
+      <c r="F10" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="131"/>
+      <c r="G10" s="130"/>
       <c r="H10" s="86"/>
       <c r="I10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="147">
+        <v>135</v>
+      </c>
+      <c r="J10" s="174">
         <v>0</v>
       </c>
-      <c r="K10" s="147"/>
-      <c r="L10" s="147"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
@@ -2224,44 +2213,44 @@
       <c r="E11" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="149"/>
-      <c r="G11" s="150"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
       <c r="H11" s="86"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="158">
+      <c r="J11" s="156">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="158"/>
-      <c r="L11" s="158"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="156"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="149" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="151"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="151"/>
-      <c r="H13" s="151"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="151"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
       <c r="K13" s="32" t="s">
         <v>34</v>
       </c>
@@ -2270,17 +2259,17 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="152" t="s">
+      <c r="B14" s="150" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="152"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
       <c r="K14" s="37">
         <f>'2'!F13</f>
         <v>944.03</v>
@@ -2291,34 +2280,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="92"/>
-      <c r="B15" s="160" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="160"/>
-      <c r="D15" s="160"/>
-      <c r="E15" s="160"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="160"/>
-      <c r="H15" s="160"/>
-      <c r="I15" s="160"/>
-      <c r="J15" s="160"/>
+      <c r="B15" s="158" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="90"/>
       <c r="L15" s="91" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="154" t="s">
+      <c r="B16" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="154"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="152"/>
       <c r="K16" s="38">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
@@ -2328,17 +2317,17 @@
       </c>
     </row>
     <row r="17" spans="1:29">
-      <c r="B17" s="153" t="s">
+      <c r="B17" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="153"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="153"/>
-      <c r="J17" s="153"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="151"/>
       <c r="K17" s="37">
         <f>SUM(K14:K16)</f>
         <v>1243.51</v>
@@ -2361,13 +2350,13 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="B19" s="159" t="s">
+      <c r="B19" s="157" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="159"/>
-      <c r="D19" s="159"/>
-      <c r="E19" s="159"/>
-      <c r="F19" s="159"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="157"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
@@ -2382,16 +2371,16 @@
       </c>
     </row>
     <row r="20" spans="1:29">
-      <c r="B20" s="155" t="s">
+      <c r="B20" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="155"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
-      <c r="F20" s="155"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="155"/>
-      <c r="I20" s="155"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
       <c r="J20" s="47">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
@@ -2406,7 +2395,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="B21" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
@@ -2426,16 +2415,16 @@
       </c>
     </row>
     <row r="22" spans="1:29">
-      <c r="B22" s="155" t="s">
+      <c r="B22" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="155"/>
-      <c r="D22" s="155"/>
-      <c r="E22" s="155"/>
-      <c r="F22" s="155"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="155"/>
-      <c r="I22" s="155"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="153"/>
       <c r="J22" s="47">
         <v>0.16</v>
       </c>
@@ -2448,16 +2437,16 @@
       </c>
     </row>
     <row r="23" spans="1:29">
-      <c r="B23" s="149" t="s">
+      <c r="B23" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="149"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="147"/>
+      <c r="I23" s="147"/>
       <c r="J23" s="47">
         <v>0.02</v>
       </c>
@@ -2470,16 +2459,16 @@
       </c>
     </row>
     <row r="24" spans="1:29">
-      <c r="B24" s="153" t="s">
+      <c r="B24" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="153"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="151"/>
       <c r="J24" s="75"/>
       <c r="K24" s="76">
         <f>SUM(K20:K23)</f>
@@ -2490,29 +2479,29 @@
       </c>
     </row>
     <row r="25" spans="1:29">
-      <c r="B25" s="155"/>
-      <c r="C25" s="155"/>
-      <c r="D25" s="155"/>
-      <c r="E25" s="155"/>
-      <c r="F25" s="155"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="155"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
       <c r="J25" s="2"/>
       <c r="K25" s="33"/>
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="B26" s="149" t="s">
+      <c r="B26" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="149"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="147"/>
+      <c r="I26" s="147"/>
       <c r="J26" s="48" t="s">
         <v>76</v>
       </c>
@@ -2525,16 +2514,16 @@
       </c>
     </row>
     <row r="27" spans="1:29">
-      <c r="B27" s="153" t="s">
+      <c r="B27" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="151"/>
+      <c r="H27" s="151"/>
+      <c r="I27" s="151"/>
       <c r="K27" s="37">
         <f>K24+K26</f>
         <v>316.1151070046609</v>
@@ -2561,14 +2550,14 @@
       <c r="AC27"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B28" s="130"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
+      <c r="B28" s="129"/>
+      <c r="C28" s="129"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="129"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
@@ -2589,13 +2578,13 @@
     </row>
     <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="93"/>
-      <c r="B29" s="162" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="163"/>
-      <c r="D29" s="163"/>
-      <c r="E29" s="163"/>
-      <c r="F29" s="163"/>
+      <c r="B29" s="160" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="161"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
       <c r="G29" s="94"/>
       <c r="H29" s="95"/>
       <c r="I29" s="95"/>
@@ -2621,7 +2610,7 @@
     <row r="30" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="93"/>
       <c r="B30" s="93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="97"/>
       <c r="D30" s="97"/>
@@ -2631,7 +2620,7 @@
       <c r="H30" s="97"/>
       <c r="I30" s="97"/>
       <c r="J30" s="98" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K30" s="99"/>
       <c r="L30" s="98" t="s">
@@ -2650,7 +2639,7 @@
     <row r="31" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A31" s="93"/>
       <c r="B31" s="100" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C31" s="97"/>
       <c r="D31" s="97"/>
@@ -2660,7 +2649,7 @@
       <c r="H31" s="97"/>
       <c r="I31" s="97"/>
       <c r="J31" s="98" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K31" s="99"/>
       <c r="L31" s="98" t="s">
@@ -2684,7 +2673,7 @@
     <row r="32" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="93"/>
       <c r="B32" s="101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C32" s="102"/>
       <c r="D32" s="102"/>
@@ -2694,7 +2683,7 @@
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K32" s="104"/>
       <c r="L32" s="105" t="s">
@@ -2765,7 +2754,7 @@
     <row r="35" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="93"/>
       <c r="B35" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C35" s="97"/>
       <c r="D35" s="97"/>
@@ -2794,7 +2783,7 @@
     <row r="36" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="93"/>
       <c r="B36" s="101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C36" s="102"/>
       <c r="D36" s="102"/>
@@ -2822,16 +2811,16 @@
     </row>
     <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="93"/>
-      <c r="B37" s="164" t="s">
+      <c r="B37" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="165"/>
-      <c r="D37" s="165"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="165"/>
-      <c r="G37" s="165"/>
-      <c r="H37" s="165"/>
-      <c r="I37" s="165"/>
+      <c r="C37" s="163"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="163"/>
+      <c r="I37" s="163"/>
       <c r="J37" s="110"/>
       <c r="K37" s="120">
         <f>SUM(K33+K35)-K36</f>
@@ -2857,18 +2846,18 @@
       <c r="L38" s="121"/>
       <c r="M38" s="110"/>
     </row>
-    <row r="39" spans="1:29" ht="15.6">
-      <c r="B39" s="168" t="s">
+    <row r="39" spans="1:29" ht="15.75">
+      <c r="B39" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="168"/>
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="168"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="166"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="166"/>
       <c r="K39" s="60" t="s">
         <v>34</v>
       </c>
@@ -2894,17 +2883,17 @@
       <c r="AC39"/>
     </row>
     <row r="40" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B40" s="155" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="155"/>
-      <c r="D40" s="155"/>
-      <c r="E40" s="155"/>
-      <c r="F40" s="155"/>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="155"/>
-      <c r="J40" s="155"/>
+      <c r="B40" s="153" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="153"/>
+      <c r="H40" s="153"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="153"/>
       <c r="K40" s="37">
         <f>K37</f>
         <v>0</v>
@@ -2931,17 +2920,17 @@
       <c r="AC40"/>
     </row>
     <row r="41" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B41" s="155" t="s">
+      <c r="B41" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="155"/>
-      <c r="D41" s="155"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="155"/>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
-      <c r="I41" s="155"/>
-      <c r="J41" s="155"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="153"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="153"/>
+      <c r="H41" s="153"/>
+      <c r="I41" s="153"/>
+      <c r="J41" s="153"/>
       <c r="K41" s="37">
         <f>K27</f>
         <v>316.1151070046609</v>
@@ -2952,7 +2941,7 @@
     </row>
     <row r="42" spans="1:29">
       <c r="B42" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K42" s="37">
         <v>0</v>
@@ -2962,17 +2951,17 @@
       </c>
     </row>
     <row r="43" spans="1:29">
-      <c r="B43" s="166" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="166"/>
-      <c r="D43" s="166"/>
-      <c r="E43" s="166"/>
-      <c r="F43" s="166"/>
-      <c r="G43" s="166"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="166"/>
-      <c r="J43" s="166"/>
+      <c r="B43" s="164" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="164"/>
+      <c r="H43" s="164"/>
+      <c r="I43" s="164"/>
+      <c r="J43" s="164"/>
       <c r="K43" s="37">
         <v>0</v>
       </c>
@@ -2980,18 +2969,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:29" s="123" customFormat="1">
-      <c r="B44" s="124" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
+    <row r="44" spans="1:29">
+      <c r="B44" s="123" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="123"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="123"/>
+      <c r="F44" s="123"/>
+      <c r="G44" s="123"/>
+      <c r="H44" s="123"/>
+      <c r="I44" s="123"/>
+      <c r="J44" s="123"/>
       <c r="K44" s="37">
         <v>0</v>
       </c>
@@ -3000,17 +2989,17 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B45" s="153" t="s">
+      <c r="B45" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="153"/>
-      <c r="D45" s="153"/>
-      <c r="E45" s="153"/>
-      <c r="F45" s="153"/>
-      <c r="G45" s="153"/>
-      <c r="H45" s="153"/>
-      <c r="I45" s="153"/>
-      <c r="J45" s="153"/>
+      <c r="C45" s="151"/>
+      <c r="D45" s="151"/>
+      <c r="E45" s="151"/>
+      <c r="F45" s="151"/>
+      <c r="G45" s="151"/>
+      <c r="H45" s="151"/>
+      <c r="I45" s="151"/>
+      <c r="J45" s="151"/>
       <c r="K45" s="76">
         <f>SUM(K40:K44)</f>
         <v>316.1151070046609</v>
@@ -3020,79 +3009,79 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B46" s="167"/>
-      <c r="C46" s="167"/>
-      <c r="D46" s="167"/>
-      <c r="E46" s="167"/>
-      <c r="F46" s="167"/>
-      <c r="G46" s="167"/>
-      <c r="H46" s="167"/>
-      <c r="I46" s="167"/>
-      <c r="J46" s="167"/>
-      <c r="K46" s="167"/>
-      <c r="L46" s="167"/>
+      <c r="B46" s="165"/>
+      <c r="C46" s="165"/>
+      <c r="D46" s="165"/>
+      <c r="E46" s="165"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="165"/>
+      <c r="H46" s="165"/>
+      <c r="I46" s="165"/>
+      <c r="J46" s="165"/>
+      <c r="K46" s="165"/>
+      <c r="L46" s="165"/>
     </row>
     <row r="47" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B47" s="143" t="s">
+      <c r="B47" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="144"/>
-      <c r="D47" s="144"/>
-      <c r="E47" s="144"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="144"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="144"/>
-      <c r="J47" s="144"/>
-      <c r="K47" s="144"/>
-      <c r="L47" s="145"/>
+      <c r="C47" s="143"/>
+      <c r="D47" s="143"/>
+      <c r="E47" s="143"/>
+      <c r="F47" s="143"/>
+      <c r="G47" s="143"/>
+      <c r="H47" s="143"/>
+      <c r="I47" s="143"/>
+      <c r="J47" s="143"/>
+      <c r="K47" s="143"/>
+      <c r="L47" s="144"/>
     </row>
     <row r="48" spans="1:29" ht="15.75" customHeight="1">
       <c r="B48" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="138" t="s">
+      <c r="C48" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="139"/>
-      <c r="E48" s="140"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="139"/>
       <c r="F48" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G48" s="138" t="s">
+      <c r="G48" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="H48" s="140"/>
+      <c r="H48" s="139"/>
       <c r="I48" s="5" t="s">
         <v>77</v>
       </c>
       <c r="J48" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="169" t="s">
+      <c r="K48" s="167" t="s">
         <v>78</v>
       </c>
-      <c r="L48" s="170"/>
+      <c r="L48" s="168"/>
     </row>
     <row r="49" spans="2:13">
       <c r="B49" s="46">
         <v>1</v>
       </c>
-      <c r="C49" s="138" t="str">
+      <c r="C49" s="137" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D49" s="139"/>
-      <c r="E49" s="140"/>
+      <c r="D49" s="138"/>
+      <c r="E49" s="139"/>
       <c r="F49" s="7">
         <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G49" s="141">
+      <c r="G49" s="140">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H49" s="142"/>
+      <c r="H49" s="141"/>
       <c r="I49" s="55">
         <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
@@ -3101,13 +3090,13 @@
         <f t="shared" ref="J49" si="0">+F49*I49</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K49" s="137">
+      <c r="K49" s="136">
         <f t="shared" ref="K49" si="1">I49*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L49" s="137"/>
-    </row>
-    <row r="50" spans="2:13" ht="15.6">
+      <c r="L49" s="136"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.75">
       <c r="B50" s="49" t="s">
         <v>8</v>
       </c>
@@ -3127,7 +3116,7 @@
       <c r="K50" s="77"/>
       <c r="L50" s="78"/>
     </row>
-    <row r="51" spans="2:13" ht="15.6">
+    <row r="51" spans="2:13" ht="15.75">
       <c r="B51" s="49"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -3152,7 +3141,7 @@
       <c r="K52" s="79"/>
       <c r="L52" s="80"/>
     </row>
-    <row r="53" spans="2:13" ht="18">
+    <row r="53" spans="2:13" ht="18.75">
       <c r="B53" s="61" t="s">
         <v>53</v>
       </c>
@@ -3166,80 +3155,80 @@
       <c r="J53" s="29"/>
       <c r="K53" s="29"/>
     </row>
-    <row r="54" spans="2:13" ht="18">
-      <c r="B54" s="148" t="s">
+    <row r="54" spans="2:13" ht="18.75">
+      <c r="B54" s="146" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="148"/>
-      <c r="D54" s="148"/>
-      <c r="E54" s="148"/>
-      <c r="F54" s="148"/>
-      <c r="G54" s="148"/>
-      <c r="H54" s="148"/>
-      <c r="I54" s="148"/>
-      <c r="J54" s="148"/>
-      <c r="K54" s="148"/>
-      <c r="L54" s="148"/>
-    </row>
-    <row r="55" spans="2:13" ht="18">
-      <c r="B55" s="148" t="s">
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
+      <c r="E54" s="146"/>
+      <c r="F54" s="146"/>
+      <c r="G54" s="146"/>
+      <c r="H54" s="146"/>
+      <c r="I54" s="146"/>
+      <c r="J54" s="146"/>
+      <c r="K54" s="146"/>
+      <c r="L54" s="146"/>
+    </row>
+    <row r="55" spans="2:13" ht="18.75">
+      <c r="B55" s="146" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="148"/>
-      <c r="D55" s="148"/>
-      <c r="E55" s="148"/>
-      <c r="F55" s="148"/>
-      <c r="G55" s="148"/>
-      <c r="H55" s="148"/>
-      <c r="I55" s="148"/>
-      <c r="J55" s="148"/>
-      <c r="K55" s="148"/>
-      <c r="L55" s="148"/>
-    </row>
-    <row r="56" spans="2:13" ht="18">
-      <c r="B56" s="148" t="s">
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="146"/>
+      <c r="G55" s="146"/>
+      <c r="H55" s="146"/>
+      <c r="I55" s="146"/>
+      <c r="J55" s="146"/>
+      <c r="K55" s="146"/>
+      <c r="L55" s="146"/>
+    </row>
+    <row r="56" spans="2:13" ht="18.75">
+      <c r="B56" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="148"/>
-      <c r="D56" s="148"/>
-      <c r="E56" s="148"/>
-      <c r="F56" s="148"/>
-      <c r="G56" s="148"/>
-      <c r="H56" s="148"/>
-      <c r="I56" s="148"/>
-      <c r="J56" s="148"/>
-      <c r="K56" s="148"/>
-      <c r="L56" s="148"/>
-    </row>
-    <row r="57" spans="2:13" ht="18">
-      <c r="B57" s="148" t="s">
+      <c r="C56" s="146"/>
+      <c r="D56" s="146"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="146"/>
+      <c r="H56" s="146"/>
+      <c r="I56" s="146"/>
+      <c r="J56" s="146"/>
+      <c r="K56" s="146"/>
+      <c r="L56" s="146"/>
+    </row>
+    <row r="57" spans="2:13" ht="18.75">
+      <c r="B57" s="146" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="148"/>
-      <c r="D57" s="148"/>
-      <c r="E57" s="148"/>
-      <c r="F57" s="148"/>
-      <c r="G57" s="148"/>
-      <c r="H57" s="148"/>
-      <c r="I57" s="148"/>
-      <c r="J57" s="148"/>
-      <c r="K57" s="148"/>
-      <c r="L57" s="148"/>
-    </row>
-    <row r="58" spans="2:13" ht="18">
-      <c r="B58" s="148" t="s">
+      <c r="C57" s="146"/>
+      <c r="D57" s="146"/>
+      <c r="E57" s="146"/>
+      <c r="F57" s="146"/>
+      <c r="G57" s="146"/>
+      <c r="H57" s="146"/>
+      <c r="I57" s="146"/>
+      <c r="J57" s="146"/>
+      <c r="K57" s="146"/>
+      <c r="L57" s="146"/>
+    </row>
+    <row r="58" spans="2:13" ht="18.75">
+      <c r="B58" s="146" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="148"/>
-      <c r="D58" s="148"/>
-      <c r="E58" s="148"/>
-      <c r="F58" s="148"/>
-      <c r="G58" s="148"/>
-      <c r="H58" s="148"/>
-      <c r="I58" s="148"/>
-      <c r="J58" s="148"/>
-      <c r="K58" s="148"/>
-      <c r="L58" s="148"/>
+      <c r="C58" s="146"/>
+      <c r="D58" s="146"/>
+      <c r="E58" s="146"/>
+      <c r="F58" s="146"/>
+      <c r="G58" s="146"/>
+      <c r="H58" s="146"/>
+      <c r="I58" s="146"/>
+      <c r="J58" s="146"/>
+      <c r="K58" s="146"/>
+      <c r="L58" s="146"/>
     </row>
     <row r="59" spans="2:13">
       <c r="B59" s="29"/>
@@ -3255,581 +3244,581 @@
       <c r="L59" s="29"/>
     </row>
     <row r="60" spans="2:13" ht="9" customHeight="1">
-      <c r="B60" s="126"/>
-      <c r="C60" s="126"/>
-      <c r="E60" s="126"/>
-      <c r="F60" s="126"/>
-      <c r="G60" s="126"/>
-      <c r="H60" s="126"/>
-      <c r="I60" s="126"/>
-      <c r="J60" s="126"/>
-      <c r="K60" s="126"/>
-      <c r="L60" s="126"/>
-      <c r="M60" s="126"/>
-    </row>
-    <row r="61" spans="2:13" ht="31.95" customHeight="1">
-      <c r="B61" s="126"/>
-      <c r="C61" s="126"/>
-      <c r="D61" s="161" t="s">
+      <c r="B60" s="125"/>
+      <c r="C60" s="125"/>
+      <c r="E60" s="125"/>
+      <c r="F60" s="125"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
+      <c r="I60" s="125"/>
+      <c r="J60" s="125"/>
+      <c r="K60" s="125"/>
+      <c r="L60" s="125"/>
+      <c r="M60" s="125"/>
+    </row>
+    <row r="61" spans="2:13" ht="31.9" customHeight="1">
+      <c r="B61" s="125"/>
+      <c r="C61" s="125"/>
+      <c r="D61" s="159" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" s="159"/>
+      <c r="F61" s="159"/>
+      <c r="G61" s="159"/>
+      <c r="H61" s="159"/>
+      <c r="I61" s="159"/>
+      <c r="J61" s="159"/>
+      <c r="K61" s="159"/>
+      <c r="L61" s="159"/>
+      <c r="M61" s="159"/>
+    </row>
+    <row r="62" spans="2:13" ht="21" customHeight="1">
+      <c r="B62" s="125"/>
+      <c r="C62" s="125"/>
+      <c r="D62" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="E61" s="161"/>
-      <c r="F61" s="161"/>
-      <c r="G61" s="161"/>
-      <c r="H61" s="161"/>
-      <c r="I61" s="161"/>
-      <c r="J61" s="161"/>
-      <c r="K61" s="161"/>
-      <c r="L61" s="161"/>
-      <c r="M61" s="161"/>
-    </row>
-    <row r="62" spans="2:13" ht="21" customHeight="1">
-      <c r="B62" s="126"/>
-      <c r="C62" s="126"/>
-      <c r="D62" s="134" t="s">
-        <v>121</v>
-      </c>
-      <c r="E62" s="134"/>
-      <c r="F62" s="134"/>
-      <c r="G62" s="134"/>
-      <c r="H62" s="134"/>
-      <c r="I62" s="134"/>
+      <c r="E62" s="133"/>
+      <c r="F62" s="133"/>
+      <c r="G62" s="133"/>
+      <c r="H62" s="133"/>
+      <c r="I62" s="133"/>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="126"/>
-      <c r="C63" s="126"/>
+      <c r="B63" s="125"/>
+      <c r="C63" s="125"/>
     </row>
     <row r="64" spans="2:13">
-      <c r="B64" s="126"/>
-      <c r="C64" s="126"/>
+      <c r="B64" s="125"/>
+      <c r="C64" s="125"/>
     </row>
     <row r="65" spans="2:12" ht="21">
-      <c r="B65" s="171" t="s">
+      <c r="B65" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="171"/>
-      <c r="D65" s="171"/>
-      <c r="E65" s="171"/>
-      <c r="F65" s="171"/>
-      <c r="G65" s="171"/>
-      <c r="H65" s="171"/>
-      <c r="I65" s="171"/>
-      <c r="J65" s="171"/>
-      <c r="K65" s="171"/>
-      <c r="L65" s="171"/>
+      <c r="C65" s="169"/>
+      <c r="D65" s="169"/>
+      <c r="E65" s="169"/>
+      <c r="F65" s="169"/>
+      <c r="G65" s="169"/>
+      <c r="H65" s="169"/>
+      <c r="I65" s="169"/>
+      <c r="J65" s="169"/>
+      <c r="K65" s="169"/>
+      <c r="L65" s="169"/>
     </row>
     <row r="67" spans="2:12">
-      <c r="B67" s="156" t="s">
+      <c r="B67" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="156"/>
-      <c r="D67" s="156"/>
-      <c r="E67" s="156"/>
-      <c r="F67" s="156"/>
-      <c r="G67" s="156"/>
-      <c r="H67" s="156"/>
-      <c r="I67" s="156"/>
-      <c r="J67" s="156"/>
-      <c r="K67" s="156"/>
-      <c r="L67" s="156"/>
+      <c r="C67" s="154"/>
+      <c r="D67" s="154"/>
+      <c r="E67" s="154"/>
+      <c r="F67" s="154"/>
+      <c r="G67" s="154"/>
+      <c r="H67" s="154"/>
+      <c r="I67" s="154"/>
+      <c r="J67" s="154"/>
+      <c r="K67" s="154"/>
+      <c r="L67" s="154"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="156" t="s">
+      <c r="B68" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="156"/>
-      <c r="D68" s="156"/>
-      <c r="E68" s="156"/>
-      <c r="F68" s="156"/>
-      <c r="G68" s="156"/>
-      <c r="H68" s="156"/>
-      <c r="I68" s="156"/>
-      <c r="J68" s="156"/>
-      <c r="K68" s="156"/>
-      <c r="L68" s="156"/>
+      <c r="C68" s="154"/>
+      <c r="D68" s="154"/>
+      <c r="E68" s="154"/>
+      <c r="F68" s="154"/>
+      <c r="G68" s="154"/>
+      <c r="H68" s="154"/>
+      <c r="I68" s="154"/>
+      <c r="J68" s="154"/>
+      <c r="K68" s="154"/>
+      <c r="L68" s="154"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="155" t="s">
+      <c r="B69" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="155"/>
-      <c r="D69" s="155"/>
-      <c r="E69" s="155"/>
-      <c r="F69" s="155"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="155"/>
-      <c r="I69" s="155"/>
-      <c r="J69" s="155"/>
-      <c r="K69" s="155"/>
-      <c r="L69" s="155"/>
+      <c r="C69" s="153"/>
+      <c r="D69" s="153"/>
+      <c r="E69" s="153"/>
+      <c r="F69" s="153"/>
+      <c r="G69" s="153"/>
+      <c r="H69" s="153"/>
+      <c r="I69" s="153"/>
+      <c r="J69" s="153"/>
+      <c r="K69" s="153"/>
+      <c r="L69" s="153"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="156" t="s">
+      <c r="B70" s="154" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="156"/>
-      <c r="D70" s="156"/>
-      <c r="E70" s="156"/>
-      <c r="F70" s="156"/>
-      <c r="G70" s="156"/>
-      <c r="H70" s="156"/>
-      <c r="I70" s="156"/>
-      <c r="J70" s="156"/>
-      <c r="K70" s="156"/>
-      <c r="L70" s="156"/>
+      <c r="C70" s="154"/>
+      <c r="D70" s="154"/>
+      <c r="E70" s="154"/>
+      <c r="F70" s="154"/>
+      <c r="G70" s="154"/>
+      <c r="H70" s="154"/>
+      <c r="I70" s="154"/>
+      <c r="J70" s="154"/>
+      <c r="K70" s="154"/>
+      <c r="L70" s="154"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="156" t="s">
+      <c r="B71" s="154" t="s">
         <v>58</v>
       </c>
-      <c r="C71" s="156"/>
-      <c r="D71" s="156"/>
-      <c r="E71" s="156"/>
-      <c r="F71" s="156"/>
-      <c r="G71" s="156"/>
-      <c r="H71" s="156"/>
-      <c r="I71" s="156"/>
-      <c r="J71" s="156"/>
-      <c r="K71" s="156"/>
-      <c r="L71" s="156"/>
+      <c r="C71" s="154"/>
+      <c r="D71" s="154"/>
+      <c r="E71" s="154"/>
+      <c r="F71" s="154"/>
+      <c r="G71" s="154"/>
+      <c r="H71" s="154"/>
+      <c r="I71" s="154"/>
+      <c r="J71" s="154"/>
+      <c r="K71" s="154"/>
+      <c r="L71" s="154"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="155" t="s">
+      <c r="B72" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="155"/>
-      <c r="D72" s="155"/>
-      <c r="E72" s="155"/>
-      <c r="F72" s="155"/>
-      <c r="G72" s="155"/>
-      <c r="H72" s="155"/>
-      <c r="I72" s="155"/>
-      <c r="J72" s="155"/>
-      <c r="K72" s="155"/>
-      <c r="L72" s="155"/>
+      <c r="C72" s="153"/>
+      <c r="D72" s="153"/>
+      <c r="E72" s="153"/>
+      <c r="F72" s="153"/>
+      <c r="G72" s="153"/>
+      <c r="H72" s="153"/>
+      <c r="I72" s="153"/>
+      <c r="J72" s="153"/>
+      <c r="K72" s="153"/>
+      <c r="L72" s="153"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="156" t="s">
+      <c r="B73" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="156"/>
-      <c r="D73" s="156"/>
-      <c r="E73" s="156"/>
-      <c r="F73" s="156"/>
-      <c r="G73" s="156"/>
-      <c r="H73" s="156"/>
-      <c r="I73" s="156"/>
-      <c r="J73" s="156"/>
-      <c r="K73" s="156"/>
-      <c r="L73" s="156"/>
+      <c r="C73" s="154"/>
+      <c r="D73" s="154"/>
+      <c r="E73" s="154"/>
+      <c r="F73" s="154"/>
+      <c r="G73" s="154"/>
+      <c r="H73" s="154"/>
+      <c r="I73" s="154"/>
+      <c r="J73" s="154"/>
+      <c r="K73" s="154"/>
+      <c r="L73" s="154"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="156" t="s">
+      <c r="B74" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="156"/>
-      <c r="D74" s="156"/>
-      <c r="E74" s="156"/>
-      <c r="F74" s="156"/>
-      <c r="G74" s="156"/>
-      <c r="H74" s="156"/>
-      <c r="I74" s="156"/>
-      <c r="J74" s="156"/>
-      <c r="K74" s="156"/>
-      <c r="L74" s="156"/>
+      <c r="C74" s="154"/>
+      <c r="D74" s="154"/>
+      <c r="E74" s="154"/>
+      <c r="F74" s="154"/>
+      <c r="G74" s="154"/>
+      <c r="H74" s="154"/>
+      <c r="I74" s="154"/>
+      <c r="J74" s="154"/>
+      <c r="K74" s="154"/>
+      <c r="L74" s="154"/>
     </row>
     <row r="75" spans="2:12">
-      <c r="B75" s="156" t="s">
+      <c r="B75" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="156"/>
-      <c r="D75" s="156"/>
-      <c r="E75" s="156"/>
-      <c r="F75" s="156"/>
-      <c r="G75" s="156"/>
-      <c r="H75" s="156"/>
-      <c r="I75" s="156"/>
-      <c r="J75" s="156"/>
-      <c r="K75" s="156"/>
-      <c r="L75" s="156"/>
+      <c r="C75" s="154"/>
+      <c r="D75" s="154"/>
+      <c r="E75" s="154"/>
+      <c r="F75" s="154"/>
+      <c r="G75" s="154"/>
+      <c r="H75" s="154"/>
+      <c r="I75" s="154"/>
+      <c r="J75" s="154"/>
+      <c r="K75" s="154"/>
+      <c r="L75" s="154"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="156" t="s">
+      <c r="B76" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="156"/>
-      <c r="D76" s="156"/>
-      <c r="E76" s="156"/>
-      <c r="F76" s="156"/>
-      <c r="G76" s="156"/>
-      <c r="H76" s="156"/>
-      <c r="I76" s="156"/>
-      <c r="J76" s="156"/>
-      <c r="K76" s="156"/>
-      <c r="L76" s="156"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="154"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="154"/>
+      <c r="G76" s="154"/>
+      <c r="H76" s="154"/>
+      <c r="I76" s="154"/>
+      <c r="J76" s="154"/>
+      <c r="K76" s="154"/>
+      <c r="L76" s="154"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="156" t="s">
+      <c r="B77" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C77" s="156"/>
-      <c r="D77" s="156"/>
-      <c r="E77" s="156"/>
-      <c r="F77" s="156"/>
-      <c r="G77" s="156"/>
-      <c r="H77" s="156"/>
-      <c r="I77" s="156"/>
-      <c r="J77" s="156"/>
-      <c r="K77" s="156"/>
-      <c r="L77" s="156"/>
+      <c r="C77" s="154"/>
+      <c r="D77" s="154"/>
+      <c r="E77" s="154"/>
+      <c r="F77" s="154"/>
+      <c r="G77" s="154"/>
+      <c r="H77" s="154"/>
+      <c r="I77" s="154"/>
+      <c r="J77" s="154"/>
+      <c r="K77" s="154"/>
+      <c r="L77" s="154"/>
     </row>
     <row r="78" spans="2:12">
-      <c r="B78" s="156" t="s">
+      <c r="B78" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="156"/>
-      <c r="D78" s="156"/>
-      <c r="E78" s="156"/>
-      <c r="F78" s="156"/>
-      <c r="G78" s="156"/>
-      <c r="H78" s="156"/>
-      <c r="I78" s="156"/>
-      <c r="J78" s="156"/>
-      <c r="K78" s="156"/>
-      <c r="L78" s="156"/>
+      <c r="C78" s="154"/>
+      <c r="D78" s="154"/>
+      <c r="E78" s="154"/>
+      <c r="F78" s="154"/>
+      <c r="G78" s="154"/>
+      <c r="H78" s="154"/>
+      <c r="I78" s="154"/>
+      <c r="J78" s="154"/>
+      <c r="K78" s="154"/>
+      <c r="L78" s="154"/>
     </row>
     <row r="79" spans="2:12">
-      <c r="B79" s="156" t="s">
+      <c r="B79" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="C79" s="156"/>
-      <c r="D79" s="156"/>
-      <c r="E79" s="156"/>
-      <c r="F79" s="156"/>
-      <c r="G79" s="156"/>
-      <c r="H79" s="156"/>
-      <c r="I79" s="156"/>
-      <c r="J79" s="156"/>
-      <c r="K79" s="156"/>
-      <c r="L79" s="156"/>
+      <c r="C79" s="154"/>
+      <c r="D79" s="154"/>
+      <c r="E79" s="154"/>
+      <c r="F79" s="154"/>
+      <c r="G79" s="154"/>
+      <c r="H79" s="154"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="154"/>
+      <c r="K79" s="154"/>
+      <c r="L79" s="154"/>
     </row>
     <row r="80" spans="2:12">
-      <c r="B80" s="156" t="s">
+      <c r="B80" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="156"/>
-      <c r="D80" s="156"/>
-      <c r="E80" s="156"/>
-      <c r="F80" s="156"/>
-      <c r="G80" s="156"/>
-      <c r="H80" s="156"/>
-      <c r="I80" s="156"/>
-      <c r="J80" s="156"/>
-      <c r="K80" s="156"/>
-      <c r="L80" s="156"/>
+      <c r="C80" s="154"/>
+      <c r="D80" s="154"/>
+      <c r="E80" s="154"/>
+      <c r="F80" s="154"/>
+      <c r="G80" s="154"/>
+      <c r="H80" s="154"/>
+      <c r="I80" s="154"/>
+      <c r="J80" s="154"/>
+      <c r="K80" s="154"/>
+      <c r="L80" s="154"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="B81" s="156" t="s">
+      <c r="B81" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="156"/>
-      <c r="D81" s="156"/>
-      <c r="E81" s="156"/>
-      <c r="F81" s="156"/>
-      <c r="G81" s="156"/>
-      <c r="H81" s="156"/>
-      <c r="I81" s="156"/>
-      <c r="J81" s="156"/>
-      <c r="K81" s="156"/>
-      <c r="L81" s="156"/>
+      <c r="C81" s="154"/>
+      <c r="D81" s="154"/>
+      <c r="E81" s="154"/>
+      <c r="F81" s="154"/>
+      <c r="G81" s="154"/>
+      <c r="H81" s="154"/>
+      <c r="I81" s="154"/>
+      <c r="J81" s="154"/>
+      <c r="K81" s="154"/>
+      <c r="L81" s="154"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="B82" s="156" t="s">
+      <c r="B82" s="154" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="156"/>
-      <c r="D82" s="156"/>
-      <c r="E82" s="156"/>
-      <c r="F82" s="156"/>
-      <c r="G82" s="156"/>
-      <c r="H82" s="156"/>
-      <c r="I82" s="156"/>
-      <c r="J82" s="156"/>
-      <c r="K82" s="156"/>
-      <c r="L82" s="156"/>
+      <c r="C82" s="154"/>
+      <c r="D82" s="154"/>
+      <c r="E82" s="154"/>
+      <c r="F82" s="154"/>
+      <c r="G82" s="154"/>
+      <c r="H82" s="154"/>
+      <c r="I82" s="154"/>
+      <c r="J82" s="154"/>
+      <c r="K82" s="154"/>
+      <c r="L82" s="154"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="B83" s="156" t="s">
+      <c r="B83" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="C83" s="156"/>
-      <c r="D83" s="156"/>
-      <c r="E83" s="156"/>
-      <c r="F83" s="156"/>
-      <c r="G83" s="156"/>
-      <c r="H83" s="156"/>
-      <c r="I83" s="156"/>
-      <c r="J83" s="156"/>
-      <c r="K83" s="156"/>
-      <c r="L83" s="156"/>
+      <c r="C83" s="154"/>
+      <c r="D83" s="154"/>
+      <c r="E83" s="154"/>
+      <c r="F83" s="154"/>
+      <c r="G83" s="154"/>
+      <c r="H83" s="154"/>
+      <c r="I83" s="154"/>
+      <c r="J83" s="154"/>
+      <c r="K83" s="154"/>
+      <c r="L83" s="154"/>
     </row>
     <row r="84" spans="1:12">
-      <c r="B84" s="152" t="s">
+      <c r="B84" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="C84" s="152"/>
-      <c r="D84" s="152"/>
-      <c r="E84" s="152"/>
-      <c r="F84" s="152"/>
-      <c r="G84" s="152"/>
-      <c r="H84" s="152"/>
-      <c r="I84" s="152"/>
-      <c r="J84" s="152"/>
-      <c r="K84" s="152"/>
-      <c r="L84" s="152"/>
+      <c r="C84" s="150"/>
+      <c r="D84" s="150"/>
+      <c r="E84" s="150"/>
+      <c r="F84" s="150"/>
+      <c r="G84" s="150"/>
+      <c r="H84" s="150"/>
+      <c r="I84" s="150"/>
+      <c r="J84" s="150"/>
+      <c r="K84" s="150"/>
+      <c r="L84" s="150"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="B85" s="156" t="s">
+      <c r="B85" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="C85" s="156"/>
-      <c r="D85" s="156"/>
-      <c r="E85" s="156"/>
-      <c r="F85" s="156"/>
-      <c r="G85" s="156"/>
-      <c r="H85" s="156"/>
-      <c r="I85" s="156"/>
-      <c r="J85" s="156"/>
-      <c r="K85" s="156"/>
-      <c r="L85" s="156"/>
+      <c r="C85" s="154"/>
+      <c r="D85" s="154"/>
+      <c r="E85" s="154"/>
+      <c r="F85" s="154"/>
+      <c r="G85" s="154"/>
+      <c r="H85" s="154"/>
+      <c r="I85" s="154"/>
+      <c r="J85" s="154"/>
+      <c r="K85" s="154"/>
+      <c r="L85" s="154"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="B86" s="152" t="s">
+      <c r="B86" s="150" t="s">
         <v>51</v>
       </c>
-      <c r="C86" s="152"/>
-      <c r="D86" s="152"/>
-      <c r="E86" s="152"/>
-      <c r="F86" s="152"/>
-      <c r="G86" s="152"/>
-      <c r="H86" s="152"/>
-      <c r="I86" s="152"/>
-      <c r="J86" s="152"/>
-      <c r="K86" s="152"/>
-      <c r="L86" s="152"/>
+      <c r="C86" s="150"/>
+      <c r="D86" s="150"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="150"/>
+      <c r="G86" s="150"/>
+      <c r="H86" s="150"/>
+      <c r="I86" s="150"/>
+      <c r="J86" s="150"/>
+      <c r="K86" s="150"/>
+      <c r="L86" s="150"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="B87" s="156" t="s">
+      <c r="B87" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="C87" s="156"/>
-      <c r="D87" s="156"/>
-      <c r="E87" s="156"/>
-      <c r="F87" s="156"/>
-      <c r="G87" s="156"/>
-      <c r="H87" s="156"/>
-      <c r="I87" s="156"/>
-      <c r="J87" s="156"/>
-      <c r="K87" s="156"/>
-      <c r="L87" s="156"/>
+      <c r="C87" s="154"/>
+      <c r="D87" s="154"/>
+      <c r="E87" s="154"/>
+      <c r="F87" s="154"/>
+      <c r="G87" s="154"/>
+      <c r="H87" s="154"/>
+      <c r="I87" s="154"/>
+      <c r="J87" s="154"/>
+      <c r="K87" s="154"/>
+      <c r="L87" s="154"/>
     </row>
     <row r="88" spans="1:12">
-      <c r="B88" s="156" t="s">
+      <c r="B88" s="154" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="156"/>
-      <c r="D88" s="156"/>
-      <c r="E88" s="156"/>
-      <c r="F88" s="156"/>
-      <c r="G88" s="156"/>
-      <c r="H88" s="156"/>
-      <c r="I88" s="156"/>
-      <c r="J88" s="156"/>
-      <c r="K88" s="156"/>
-      <c r="L88" s="156"/>
+      <c r="C88" s="154"/>
+      <c r="D88" s="154"/>
+      <c r="E88" s="154"/>
+      <c r="F88" s="154"/>
+      <c r="G88" s="154"/>
+      <c r="H88" s="154"/>
+      <c r="I88" s="154"/>
+      <c r="J88" s="154"/>
+      <c r="K88" s="154"/>
+      <c r="L88" s="154"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="B89" s="156" t="s">
+      <c r="B89" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="C89" s="156"/>
-      <c r="D89" s="156"/>
-      <c r="E89" s="156"/>
-      <c r="F89" s="156"/>
-      <c r="G89" s="156"/>
-      <c r="H89" s="156"/>
-      <c r="I89" s="156"/>
-      <c r="J89" s="156"/>
-      <c r="K89" s="156"/>
-      <c r="L89" s="156"/>
+      <c r="C89" s="154"/>
+      <c r="D89" s="154"/>
+      <c r="E89" s="154"/>
+      <c r="F89" s="154"/>
+      <c r="G89" s="154"/>
+      <c r="H89" s="154"/>
+      <c r="I89" s="154"/>
+      <c r="J89" s="154"/>
+      <c r="K89" s="154"/>
+      <c r="L89" s="154"/>
     </row>
     <row r="90" spans="1:12">
-      <c r="B90" s="156" t="s">
+      <c r="B90" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="C90" s="156"/>
-      <c r="D90" s="156"/>
-      <c r="E90" s="156"/>
-      <c r="F90" s="156"/>
-      <c r="G90" s="156"/>
-      <c r="H90" s="156"/>
-      <c r="I90" s="156"/>
-      <c r="J90" s="156"/>
-      <c r="K90" s="156"/>
-      <c r="L90" s="156"/>
+      <c r="C90" s="154"/>
+      <c r="D90" s="154"/>
+      <c r="E90" s="154"/>
+      <c r="F90" s="154"/>
+      <c r="G90" s="154"/>
+      <c r="H90" s="154"/>
+      <c r="I90" s="154"/>
+      <c r="J90" s="154"/>
+      <c r="K90" s="154"/>
+      <c r="L90" s="154"/>
     </row>
     <row r="91" spans="1:12">
-      <c r="B91" s="156" t="s">
+      <c r="B91" s="154" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="156"/>
-      <c r="D91" s="156"/>
-      <c r="E91" s="156"/>
-      <c r="F91" s="156"/>
-      <c r="G91" s="156"/>
-      <c r="H91" s="156"/>
-      <c r="I91" s="156"/>
-      <c r="J91" s="156"/>
-      <c r="K91" s="156"/>
-      <c r="L91" s="156"/>
+      <c r="C91" s="154"/>
+      <c r="D91" s="154"/>
+      <c r="E91" s="154"/>
+      <c r="F91" s="154"/>
+      <c r="G91" s="154"/>
+      <c r="H91" s="154"/>
+      <c r="I91" s="154"/>
+      <c r="J91" s="154"/>
+      <c r="K91" s="154"/>
+      <c r="L91" s="154"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="85"/>
-      <c r="B92" s="157" t="s">
+      <c r="B92" s="155" t="s">
         <v>84</v>
       </c>
-      <c r="C92" s="157"/>
-      <c r="D92" s="157"/>
-      <c r="E92" s="157"/>
-      <c r="F92" s="157"/>
-      <c r="G92" s="157"/>
-      <c r="H92" s="157"/>
-      <c r="I92" s="157"/>
-      <c r="J92" s="157"/>
-      <c r="K92" s="157"/>
-      <c r="L92" s="157"/>
+      <c r="C92" s="155"/>
+      <c r="D92" s="155"/>
+      <c r="E92" s="155"/>
+      <c r="F92" s="155"/>
+      <c r="G92" s="155"/>
+      <c r="H92" s="155"/>
+      <c r="I92" s="155"/>
+      <c r="J92" s="155"/>
+      <c r="K92" s="155"/>
+      <c r="L92" s="155"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="85"/>
-      <c r="B93" s="156" t="s">
+      <c r="B93" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="C93" s="156"/>
-      <c r="D93" s="156"/>
-      <c r="E93" s="156"/>
-      <c r="F93" s="156"/>
-      <c r="G93" s="156"/>
-      <c r="H93" s="156"/>
-      <c r="I93" s="156"/>
-      <c r="J93" s="156"/>
-      <c r="K93" s="156"/>
-      <c r="L93" s="156"/>
+      <c r="C93" s="154"/>
+      <c r="D93" s="154"/>
+      <c r="E93" s="154"/>
+      <c r="F93" s="154"/>
+      <c r="G93" s="154"/>
+      <c r="H93" s="154"/>
+      <c r="I93" s="154"/>
+      <c r="J93" s="154"/>
+      <c r="K93" s="154"/>
+      <c r="L93" s="154"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="85"/>
-      <c r="B94" s="157" t="s">
+      <c r="B94" s="155" t="s">
         <v>86</v>
       </c>
-      <c r="C94" s="157"/>
-      <c r="D94" s="157"/>
-      <c r="E94" s="157"/>
-      <c r="F94" s="157"/>
-      <c r="G94" s="157"/>
-      <c r="H94" s="157"/>
-      <c r="I94" s="157"/>
-      <c r="J94" s="157"/>
-      <c r="K94" s="157"/>
-      <c r="L94" s="157"/>
+      <c r="C94" s="155"/>
+      <c r="D94" s="155"/>
+      <c r="E94" s="155"/>
+      <c r="F94" s="155"/>
+      <c r="G94" s="155"/>
+      <c r="H94" s="155"/>
+      <c r="I94" s="155"/>
+      <c r="J94" s="155"/>
+      <c r="K94" s="155"/>
+      <c r="L94" s="155"/>
     </row>
     <row r="96" spans="1:12">
-      <c r="C96" s="126"/>
-      <c r="D96" s="126"/>
-      <c r="E96" s="126"/>
-      <c r="F96" s="126"/>
-      <c r="G96" s="126"/>
-      <c r="H96" s="126"/>
-      <c r="I96" s="126"/>
+      <c r="C96" s="125"/>
+      <c r="D96" s="125"/>
+      <c r="E96" s="125"/>
+      <c r="F96" s="125"/>
+      <c r="G96" s="125"/>
+      <c r="H96" s="125"/>
+      <c r="I96" s="125"/>
     </row>
     <row r="97" spans="3:9">
-      <c r="C97" s="126"/>
-      <c r="D97" s="126"/>
-      <c r="E97" s="126"/>
-      <c r="F97" s="126"/>
-      <c r="G97" s="126"/>
-      <c r="H97" s="126"/>
-      <c r="I97" s="126"/>
+      <c r="C97" s="125"/>
+      <c r="D97" s="125"/>
+      <c r="E97" s="125"/>
+      <c r="F97" s="125"/>
+      <c r="G97" s="125"/>
+      <c r="H97" s="125"/>
+      <c r="I97" s="125"/>
     </row>
     <row r="98" spans="3:9">
-      <c r="C98" s="126"/>
-      <c r="D98" s="126"/>
-      <c r="E98" s="126"/>
-      <c r="F98" s="126"/>
-      <c r="G98" s="126"/>
-      <c r="H98" s="126"/>
-      <c r="I98" s="126"/>
+      <c r="C98" s="125"/>
+      <c r="D98" s="125"/>
+      <c r="E98" s="125"/>
+      <c r="F98" s="125"/>
+      <c r="G98" s="125"/>
+      <c r="H98" s="125"/>
+      <c r="I98" s="125"/>
     </row>
     <row r="99" spans="3:9">
-      <c r="C99" s="126"/>
-      <c r="D99" s="126"/>
-      <c r="E99" s="126"/>
-      <c r="F99" s="126"/>
-      <c r="G99" s="126"/>
-      <c r="H99" s="126"/>
-      <c r="I99" s="126"/>
+      <c r="C99" s="125"/>
+      <c r="D99" s="125"/>
+      <c r="E99" s="125"/>
+      <c r="F99" s="125"/>
+      <c r="G99" s="125"/>
+      <c r="H99" s="125"/>
+      <c r="I99" s="125"/>
     </row>
     <row r="100" spans="3:9">
-      <c r="C100" s="126"/>
-      <c r="D100" s="126"/>
-      <c r="E100" s="126"/>
-      <c r="F100" s="126"/>
-      <c r="G100" s="126"/>
-      <c r="H100" s="126"/>
-      <c r="I100" s="126"/>
+      <c r="C100" s="125"/>
+      <c r="D100" s="125"/>
+      <c r="E100" s="125"/>
+      <c r="F100" s="125"/>
+      <c r="G100" s="125"/>
+      <c r="H100" s="125"/>
+      <c r="I100" s="125"/>
     </row>
     <row r="101" spans="3:9">
-      <c r="C101" s="126"/>
-      <c r="D101" s="126"/>
-      <c r="E101" s="126"/>
-      <c r="F101" s="126"/>
-      <c r="G101" s="126"/>
-      <c r="H101" s="126"/>
-      <c r="I101" s="126"/>
+      <c r="C101" s="125"/>
+      <c r="D101" s="125"/>
+      <c r="E101" s="125"/>
+      <c r="F101" s="125"/>
+      <c r="G101" s="125"/>
+      <c r="H101" s="125"/>
+      <c r="I101" s="125"/>
     </row>
     <row r="102" spans="3:9">
-      <c r="C102" s="126"/>
-      <c r="D102" s="126"/>
-      <c r="E102" s="126"/>
-      <c r="F102" s="126"/>
-      <c r="G102" s="126"/>
-      <c r="H102" s="126"/>
-      <c r="I102" s="126"/>
+      <c r="C102" s="125"/>
+      <c r="D102" s="125"/>
+      <c r="E102" s="125"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="125"/>
+      <c r="H102" s="125"/>
+      <c r="I102" s="125"/>
     </row>
     <row r="103" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C103" s="126"/>
-      <c r="D103" s="126"/>
-      <c r="E103" s="126"/>
-      <c r="F103" s="126"/>
-      <c r="G103" s="126"/>
-      <c r="H103" s="126"/>
-      <c r="I103" s="126"/>
+      <c r="C103" s="125"/>
+      <c r="D103" s="125"/>
+      <c r="E103" s="125"/>
+      <c r="F103" s="125"/>
+      <c r="G103" s="125"/>
+      <c r="H103" s="125"/>
+      <c r="I103" s="125"/>
     </row>
     <row r="104" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C104" s="126"/>
-      <c r="D104" s="126"/>
-      <c r="E104" s="126"/>
-      <c r="F104" s="126"/>
-      <c r="G104" s="126"/>
-      <c r="H104" s="126"/>
-      <c r="I104" s="126"/>
+      <c r="C104" s="125"/>
+      <c r="D104" s="125"/>
+      <c r="E104" s="125"/>
+      <c r="F104" s="125"/>
+      <c r="G104" s="125"/>
+      <c r="H104" s="125"/>
+      <c r="I104" s="125"/>
     </row>
     <row r="105" spans="3:9">
-      <c r="C105" s="126"/>
-      <c r="D105" s="126"/>
-      <c r="E105" s="126"/>
-      <c r="F105" s="126"/>
-      <c r="G105" s="126"/>
-      <c r="H105" s="126"/>
-      <c r="I105" s="126"/>
+      <c r="C105" s="125"/>
+      <c r="D105" s="125"/>
+      <c r="E105" s="125"/>
+      <c r="F105" s="125"/>
+      <c r="G105" s="125"/>
+      <c r="H105" s="125"/>
+      <c r="I105" s="125"/>
     </row>
     <row r="111" spans="3:9" ht="15.6" customHeight="1"/>
   </sheetData>
@@ -3953,28 +3942,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A3:AG50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="11.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="11.44140625" style="2"/>
-    <col min="8" max="9" width="11.44140625" style="1"/>
-    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
-    <col min="12" max="32" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="2"/>
+    <col min="8" max="9" width="11.42578125" style="1"/>
+    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" style="1" customWidth="1"/>
+    <col min="12" max="32" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
       <c r="B6" s="70" t="s">
@@ -4024,14 +4013,14 @@
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="172" t="s">
+      <c r="J8" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="172"/>
-      <c r="M8" s="172" t="s">
+      <c r="K8" s="170"/>
+      <c r="M8" s="170" t="s">
         <v>107</v>
       </c>
-      <c r="N8" s="172"/>
+      <c r="N8" s="170"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
@@ -4504,14 +4493,14 @@
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="173" t="s">
+      <c r="B23" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="173"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="173"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="173"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
@@ -4572,7 +4561,7 @@
     </row>
     <row r="28" spans="1:33">
       <c r="B28" s="116" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="117">
         <v>0</v>
@@ -4777,14 +4766,14 @@
       <c r="AF35"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="B36" s="175" t="s">
+      <c r="B36" s="173" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="175"/>
-      <c r="D36" s="175"/>
-      <c r="E36" s="175"/>
-      <c r="F36" s="175"/>
-      <c r="G36" s="175"/>
+      <c r="C36" s="173"/>
+      <c r="D36" s="173"/>
+      <c r="E36" s="173"/>
+      <c r="F36" s="173"/>
+      <c r="G36" s="173"/>
     </row>
     <row r="38" spans="1:32">
       <c r="C38" s="21">

--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Proyectos\Probusiness\probusiness_intranetv2_back\public\assets\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2FE29A-C464-4B82-8530-7D4F0ECD29AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C427EF-525D-4329-9861-01649CA78B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-840" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -19,10 +19,22 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$114</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -627,13 +639,13 @@
     <numFmt numFmtId="167" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="168" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="169" formatCode="#,##0.000\ &quot;m3&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.0\ &quot;kg&quot;"/>
-    <numFmt numFmtId="172" formatCode="_-[$S/-280A]\ * #,##0.00_-;\-[$S/-280A]\ * #,##0.00_-;_-[$S/-280A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-[$$-409]* #,##0.0_ ;_-[$$-409]* \-#,##0.0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="174" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="_-[$$-80A]* #,##0.000_-;\-[$$-80A]* #,##0.000_-;_-[$$-80A]* &quot;-&quot;???_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0\ &quot;kg&quot;"/>
+    <numFmt numFmtId="171" formatCode="_-[$S/-280A]\ * #,##0.00_-;\-[$S/-280A]\ * #,##0.00_-;_-[$S/-280A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-[$$-409]* #,##0.0_ ;_-[$$-409]* \-#,##0.0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="173" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-[$$-80A]* #,##0.000_-;\-[$$-80A]* #,##0.000_-;_-[$$-80A]* &quot;-&quot;???_-;_-@_-"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,6 +911,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -922,12 +947,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF009999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -977,6 +996,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CBAD"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1197,7 +1222,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1270,9 +1295,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1295,16 +1317,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1326,17 +1345,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="16" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="16" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1344,27 +1363,27 @@
     <xf numFmtId="169" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="174" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1373,22 +1392,22 @@
     <xf numFmtId="168" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1398,46 +1417,46 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="28" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="30" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="30" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="36" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="36" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1452,11 +1471,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1467,11 +1486,91 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1483,99 +1582,9 @@
     <xf numFmtId="14" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1588,7 +1597,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="29" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="29" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="39" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2047,230 +2075,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="129"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
+      <c r="A1" s="146"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
     </row>
     <row r="3" spans="1:12" ht="26.25">
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="E3" s="134" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="E3" s="150" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:12" ht="26.25">
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="E4" s="135" t="s">
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="E4" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="35"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="34"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="89"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="87"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="125"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="125"/>
-      <c r="E7" s="126" t="s">
+      <c r="A7" s="126"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="E7" s="158" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="87"/>
-      <c r="E8" s="50" t="s">
+      <c r="D8" s="85"/>
+      <c r="E8" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="131" t="s">
+      <c r="F8" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="132"/>
-      <c r="H8" s="86"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="145">
+      <c r="J8" s="154">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="145"/>
-      <c r="L8" s="145"/>
+      <c r="K8" s="154"/>
+      <c r="L8" s="154"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="87"/>
-      <c r="E9" s="51" t="s">
+      <c r="D9" s="85"/>
+      <c r="E9" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="127">
+      <c r="F9" s="159">
         <f ca="1">+TODAY()</f>
-        <v>46140</v>
-      </c>
-      <c r="G9" s="128"/>
-      <c r="H9" s="86"/>
+        <v>46142</v>
+      </c>
+      <c r="G9" s="160"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="124">
+      <c r="J9" s="157">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="38">
         <v>40828284</v>
       </c>
-      <c r="D10" s="87"/>
-      <c r="E10" s="57" t="s">
+      <c r="D10" s="85"/>
+      <c r="E10" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="129" t="s">
+      <c r="F10" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="130"/>
-      <c r="H10" s="86"/>
+      <c r="G10" s="161"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J10" s="174">
+      <c r="J10" s="155">
         <v>0</v>
       </c>
-      <c r="K10" s="174"/>
-      <c r="L10" s="174"/>
+      <c r="K10" s="155"/>
+      <c r="L10" s="155"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="39">
         <v>969094294</v>
       </c>
-      <c r="D11" s="88"/>
-      <c r="E11" s="52" t="s">
+      <c r="D11" s="86"/>
+      <c r="E11" s="50" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="147"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="86"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="156">
+      <c r="J11" s="130">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="156"/>
-      <c r="L11" s="156"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="146"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="146"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="146"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="149" t="s">
+      <c r="B13" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="32" t="s">
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
+      <c r="E13" s="170"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="170"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="170"/>
+      <c r="J13" s="170"/>
+      <c r="K13" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="L13" s="171" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="150" t="s">
+      <c r="B14" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="37">
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="124"/>
+      <c r="J14" s="124"/>
+      <c r="K14" s="36">
         <f>'2'!F13</f>
         <v>944.03</v>
       </c>
@@ -2279,56 +2307,56 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="92"/>
-      <c r="B15" s="158" t="s">
+      <c r="A15" s="90"/>
+      <c r="B15" s="132" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="158"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="91" t="s">
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="89" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="152" t="s">
+      <c r="B16" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="152"/>
-      <c r="I16" s="152"/>
-      <c r="J16" s="152"/>
-      <c r="K16" s="38">
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="37">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
       </c>
-      <c r="L16" s="34" t="s">
+      <c r="L16" s="33" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:29">
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="151"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="37">
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="36">
         <f>SUM(K14:K16)</f>
         <v>1243.51</v>
       </c>
@@ -2350,42 +2378,42 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="B19" s="157" t="s">
+      <c r="B19" s="131" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="32" t="s">
+      <c r="C19" s="131"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="32" t="s">
+      <c r="K19" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="32" t="s">
+      <c r="L19" s="123" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:29">
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="153"/>
-      <c r="D20" s="153"/>
-      <c r="E20" s="153"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="153"/>
-      <c r="J20" s="47">
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="127"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="45">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="36">
         <f>'2'!F27</f>
         <v>33.510475726407002</v>
       </c>
@@ -2404,10 +2432,10 @@
       <c r="G21" s="29"/>
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
-      <c r="J21" s="47">
+      <c r="J21" s="45">
         <v>0</v>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="36">
         <v>0</v>
       </c>
       <c r="L21" s="31" t="s">
@@ -2415,20 +2443,20 @@
       </c>
     </row>
     <row r="22" spans="1:29">
-      <c r="B22" s="153" t="s">
+      <c r="B22" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
-      <c r="J22" s="47">
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
+      <c r="H22" s="127"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="45">
         <v>0.16</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="36">
         <f>'2'!F29</f>
         <v>204.32327611622512</v>
       </c>
@@ -2447,10 +2475,10 @@
       <c r="G23" s="147"/>
       <c r="H23" s="147"/>
       <c r="I23" s="147"/>
-      <c r="J23" s="47">
+      <c r="J23" s="45">
         <v>0.02</v>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="36">
         <f>'2'!F30</f>
         <v>25.54040951452814</v>
       </c>
@@ -2459,36 +2487,36 @@
       </c>
     </row>
     <row r="24" spans="1:29">
-      <c r="B24" s="151" t="s">
+      <c r="B24" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="151"/>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="151"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="76">
+      <c r="C24" s="143"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="74">
         <f>SUM(K20:K23)</f>
         <v>263.37416135716029</v>
       </c>
-      <c r="L24" s="75" t="s">
+      <c r="L24" s="73" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:29">
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="153"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="33"/>
+      <c r="K25" s="32"/>
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:29">
@@ -2502,29 +2530,29 @@
       <c r="G26" s="147"/>
       <c r="H26" s="147"/>
       <c r="I26" s="147"/>
-      <c r="J26" s="48" t="s">
+      <c r="J26" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="37">
         <f>'2'!F31</f>
         <v>52.74094564750061</v>
       </c>
-      <c r="L26" s="34" t="s">
+      <c r="L26" s="33" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:29">
-      <c r="B27" s="151" t="s">
+      <c r="B27" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="151"/>
-      <c r="K27" s="37">
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="143"/>
+      <c r="K27" s="36">
         <f>K24+K26</f>
         <v>316.1151070046609</v>
       </c>
@@ -2550,14 +2578,14 @@
       <c r="AC27"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B28" s="129"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="129"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="146"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="146"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="146"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
@@ -2577,294 +2605,294 @@
       <c r="AC28"/>
     </row>
     <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A29" s="93"/>
-      <c r="B29" s="160" t="s">
+      <c r="A29" s="91"/>
+      <c r="B29" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="C29" s="161"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="95"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96" t="s">
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="K29" s="96" t="s">
+      <c r="K29" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="L29" s="96" t="s">
+      <c r="L29" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="110"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="111"/>
-      <c r="S29" s="111"/>
-      <c r="T29" s="111"/>
-      <c r="W29" s="111"/>
-      <c r="X29" s="111"/>
-      <c r="AA29" s="111"/>
-      <c r="AB29" s="111"/>
+      <c r="M29" s="108"/>
+      <c r="O29" s="109"/>
+      <c r="P29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="AA29" s="109"/>
+      <c r="AB29" s="109"/>
     </row>
     <row r="30" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A30" s="93"/>
-      <c r="B30" s="93" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="91" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="98" t="s">
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="K30" s="99"/>
-      <c r="L30" s="98" t="s">
+      <c r="K30" s="97"/>
+      <c r="L30" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="M30" s="110"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="S30" s="112"/>
-      <c r="T30" s="112"/>
-      <c r="W30" s="112"/>
-      <c r="X30" s="112"/>
-      <c r="AA30" s="112"/>
-      <c r="AB30" s="112"/>
+      <c r="M30" s="108"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="110"/>
+      <c r="S30" s="110"/>
+      <c r="T30" s="110"/>
+      <c r="W30" s="110"/>
+      <c r="X30" s="110"/>
+      <c r="AA30" s="110"/>
+      <c r="AB30" s="110"/>
     </row>
     <row r="31" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A31" s="93"/>
-      <c r="B31" s="100" t="s">
+      <c r="A31" s="91"/>
+      <c r="B31" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="98" t="s">
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="96" t="s">
         <v>127</v>
       </c>
-      <c r="K31" s="99"/>
-      <c r="L31" s="98" t="s">
+      <c r="K31" s="97"/>
+      <c r="L31" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="M31" s="110"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="113"/>
-      <c r="S31" s="112"/>
-      <c r="T31" s="112"/>
-      <c r="U31" s="112"/>
-      <c r="W31" s="112"/>
-      <c r="X31" s="112"/>
-      <c r="Y31" s="112"/>
-      <c r="AA31" s="112"/>
-      <c r="AB31" s="112"/>
-      <c r="AC31" s="112"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="110"/>
+      <c r="P31" s="110"/>
+      <c r="Q31" s="111"/>
+      <c r="S31" s="110"/>
+      <c r="T31" s="110"/>
+      <c r="U31" s="110"/>
+      <c r="W31" s="110"/>
+      <c r="X31" s="110"/>
+      <c r="Y31" s="110"/>
+      <c r="AA31" s="110"/>
+      <c r="AB31" s="110"/>
+      <c r="AC31" s="110"/>
     </row>
     <row r="32" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A32" s="93"/>
-      <c r="B32" s="101" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="102"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="103" t="s">
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="101" t="s">
         <v>125</v>
       </c>
-      <c r="K32" s="104"/>
-      <c r="L32" s="105" t="s">
+      <c r="K32" s="102"/>
+      <c r="L32" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="M32" s="110"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
-      <c r="S32" s="112"/>
-      <c r="T32" s="112"/>
-      <c r="W32" s="112"/>
-      <c r="X32" s="112"/>
-      <c r="AA32" s="112"/>
-      <c r="AB32" s="112"/>
+      <c r="M32" s="108"/>
+      <c r="O32" s="110"/>
+      <c r="P32" s="110"/>
+      <c r="S32" s="110"/>
+      <c r="T32" s="110"/>
+      <c r="W32" s="110"/>
+      <c r="X32" s="110"/>
+      <c r="AA32" s="110"/>
+      <c r="AB32" s="110"/>
     </row>
     <row r="33" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A33" s="93"/>
-      <c r="B33" s="106" t="s">
+      <c r="A33" s="91"/>
+      <c r="B33" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="99">
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="97">
         <f>SUM(K30:K32)</f>
         <v>0</v>
       </c>
-      <c r="L33" s="98" t="s">
+      <c r="L33" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="M33" s="110"/>
-      <c r="O33" s="112"/>
-      <c r="P33" s="112"/>
-      <c r="S33" s="112"/>
-      <c r="T33" s="114"/>
-      <c r="W33" s="112"/>
-      <c r="AA33" s="112"/>
-      <c r="AB33" s="115"/>
+      <c r="M33" s="108"/>
+      <c r="O33" s="110"/>
+      <c r="P33" s="110"/>
+      <c r="S33" s="110"/>
+      <c r="T33" s="112"/>
+      <c r="W33" s="110"/>
+      <c r="AA33" s="110"/>
+      <c r="AB33" s="113"/>
     </row>
     <row r="34" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A34" s="93"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
-      <c r="J34" s="107"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="110"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="112"/>
-      <c r="S34" s="112"/>
-      <c r="T34" s="112"/>
-      <c r="W34" s="112"/>
-      <c r="X34" s="112"/>
-      <c r="AA34" s="112"/>
-      <c r="AB34" s="112"/>
+      <c r="A34" s="91"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="108"/>
+      <c r="O34" s="110"/>
+      <c r="P34" s="110"/>
+      <c r="S34" s="110"/>
+      <c r="T34" s="110"/>
+      <c r="W34" s="110"/>
+      <c r="X34" s="110"/>
+      <c r="AA34" s="110"/>
+      <c r="AB34" s="110"/>
     </row>
     <row r="35" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A35" s="93"/>
-      <c r="B35" s="100" t="s">
+      <c r="A35" s="91"/>
+      <c r="B35" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="97"/>
-      <c r="D35" s="97"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="97"/>
-      <c r="J35" s="107"/>
-      <c r="K35" s="99">
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="97">
         <v>0</v>
       </c>
-      <c r="L35" s="98" t="s">
+      <c r="L35" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="M35" s="110"/>
-      <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
-      <c r="S35" s="112"/>
-      <c r="T35" s="112"/>
-      <c r="W35" s="112"/>
-      <c r="X35" s="112"/>
-      <c r="AA35" s="112"/>
-      <c r="AB35" s="112"/>
+      <c r="M35" s="108"/>
+      <c r="O35" s="110"/>
+      <c r="P35" s="110"/>
+      <c r="S35" s="110"/>
+      <c r="T35" s="110"/>
+      <c r="W35" s="110"/>
+      <c r="X35" s="110"/>
+      <c r="AA35" s="110"/>
+      <c r="AB35" s="110"/>
     </row>
     <row r="36" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A36" s="93"/>
-      <c r="B36" s="101" t="s">
+      <c r="A36" s="91"/>
+      <c r="B36" s="99" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="102"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="108">
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="106">
         <v>0</v>
       </c>
-      <c r="L36" s="109" t="s">
+      <c r="L36" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="M36" s="110"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="112"/>
-      <c r="S36" s="112"/>
-      <c r="T36" s="112"/>
-      <c r="W36" s="112"/>
-      <c r="X36" s="112"/>
-      <c r="AA36" s="112"/>
-      <c r="AB36" s="112"/>
+      <c r="M36" s="108"/>
+      <c r="O36" s="110"/>
+      <c r="P36" s="110"/>
+      <c r="S36" s="110"/>
+      <c r="T36" s="110"/>
+      <c r="W36" s="110"/>
+      <c r="X36" s="110"/>
+      <c r="AA36" s="110"/>
+      <c r="AB36" s="110"/>
     </row>
     <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="93"/>
-      <c r="B37" s="162" t="s">
+      <c r="A37" s="91"/>
+      <c r="B37" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="163"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="163"/>
-      <c r="F37" s="163"/>
-      <c r="G37" s="163"/>
-      <c r="H37" s="163"/>
-      <c r="I37" s="163"/>
-      <c r="J37" s="110"/>
-      <c r="K37" s="120">
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="108"/>
+      <c r="K37" s="118">
         <f>SUM(K33+K35)-K36</f>
         <v>0</v>
       </c>
-      <c r="L37" s="121" t="s">
+      <c r="L37" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="M37" s="110"/>
+      <c r="M37" s="108"/>
     </row>
     <row r="38" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A38" s="93"/>
-      <c r="B38" s="119"/>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
-      <c r="J38" s="110"/>
-      <c r="K38" s="120"/>
-      <c r="L38" s="121"/>
-      <c r="M38" s="110"/>
+      <c r="A38" s="91"/>
+      <c r="B38" s="117"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="119"/>
+      <c r="M38" s="108"/>
     </row>
     <row r="39" spans="1:29" ht="15.75">
-      <c r="B39" s="166" t="s">
+      <c r="B39" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="166"/>
-      <c r="D39" s="166"/>
-      <c r="E39" s="166"/>
-      <c r="F39" s="166"/>
-      <c r="G39" s="166"/>
-      <c r="H39" s="166"/>
-      <c r="I39" s="166"/>
-      <c r="J39" s="166"/>
-      <c r="K39" s="60" t="s">
+      <c r="C39" s="144"/>
+      <c r="D39" s="144"/>
+      <c r="E39" s="144"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="144"/>
+      <c r="H39" s="144"/>
+      <c r="I39" s="144"/>
+      <c r="J39" s="144"/>
+      <c r="K39" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="L39" s="60" t="s">
+      <c r="L39" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="122"/>
+      <c r="M39" s="120"/>
       <c r="N39"/>
       <c r="O39"/>
       <c r="P39"/>
@@ -2883,18 +2911,18 @@
       <c r="AC39"/>
     </row>
     <row r="40" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B40" s="153" t="s">
+      <c r="B40" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="153"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="153"/>
-      <c r="K40" s="37">
+      <c r="C40" s="127"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="127"/>
+      <c r="K40" s="36">
         <f>K37</f>
         <v>0</v>
       </c>
@@ -2920,18 +2948,18 @@
       <c r="AC40"/>
     </row>
     <row r="41" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B41" s="153" t="s">
+      <c r="B41" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="153"/>
-      <c r="D41" s="153"/>
-      <c r="E41" s="153"/>
-      <c r="F41" s="153"/>
-      <c r="G41" s="153"/>
-      <c r="H41" s="153"/>
-      <c r="I41" s="153"/>
-      <c r="J41" s="153"/>
-      <c r="K41" s="37">
+      <c r="C41" s="127"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="36">
         <f>K27</f>
         <v>316.1151070046609</v>
       </c>
@@ -2943,7 +2971,7 @@
       <c r="B42" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K42" s="37">
+      <c r="K42" s="36">
         <v>0</v>
       </c>
       <c r="L42" s="31" t="s">
@@ -2951,18 +2979,18 @@
       </c>
     </row>
     <row r="43" spans="1:29">
-      <c r="B43" s="164" t="s">
+      <c r="B43" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="164"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="164"/>
-      <c r="H43" s="164"/>
-      <c r="I43" s="164"/>
-      <c r="J43" s="164"/>
-      <c r="K43" s="37">
+      <c r="C43" s="141"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="141"/>
+      <c r="I43" s="141"/>
+      <c r="J43" s="141"/>
+      <c r="K43" s="36">
         <v>0</v>
       </c>
       <c r="L43" s="31" t="s">
@@ -2970,18 +2998,18 @@
       </c>
     </row>
     <row r="44" spans="1:29">
-      <c r="B44" s="123" t="s">
+      <c r="B44" s="121" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="123"/>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="123"/>
-      <c r="I44" s="123"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="37">
+      <c r="C44" s="121"/>
+      <c r="D44" s="121"/>
+      <c r="E44" s="121"/>
+      <c r="F44" s="121"/>
+      <c r="G44" s="121"/>
+      <c r="H44" s="121"/>
+      <c r="I44" s="121"/>
+      <c r="J44" s="121"/>
+      <c r="K44" s="36">
         <v>0</v>
       </c>
       <c r="L44" s="31" t="s">
@@ -2989,144 +3017,144 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B45" s="151" t="s">
+      <c r="B45" s="143" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="151"/>
-      <c r="D45" s="151"/>
-      <c r="E45" s="151"/>
-      <c r="F45" s="151"/>
-      <c r="G45" s="151"/>
-      <c r="H45" s="151"/>
-      <c r="I45" s="151"/>
-      <c r="J45" s="151"/>
-      <c r="K45" s="76">
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
+      <c r="E45" s="143"/>
+      <c r="F45" s="143"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="143"/>
+      <c r="J45" s="143"/>
+      <c r="K45" s="74">
         <f>SUM(K40:K44)</f>
         <v>316.1151070046609</v>
       </c>
-      <c r="L45" s="75" t="s">
+      <c r="L45" s="73" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B46" s="165"/>
-      <c r="C46" s="165"/>
-      <c r="D46" s="165"/>
-      <c r="E46" s="165"/>
-      <c r="F46" s="165"/>
-      <c r="G46" s="165"/>
-      <c r="H46" s="165"/>
-      <c r="I46" s="165"/>
-      <c r="J46" s="165"/>
-      <c r="K46" s="165"/>
-      <c r="L46" s="165"/>
+      <c r="B46" s="142"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="142"/>
+      <c r="E46" s="142"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="142"/>
+      <c r="I46" s="142"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="142"/>
     </row>
     <row r="47" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B47" s="142" t="s">
+      <c r="B47" s="172" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="143"/>
-      <c r="D47" s="143"/>
-      <c r="E47" s="143"/>
-      <c r="F47" s="143"/>
-      <c r="G47" s="143"/>
-      <c r="H47" s="143"/>
-      <c r="I47" s="143"/>
-      <c r="J47" s="143"/>
-      <c r="K47" s="143"/>
-      <c r="L47" s="144"/>
+      <c r="C47" s="173"/>
+      <c r="D47" s="173"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="173"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="173"/>
+      <c r="I47" s="173"/>
+      <c r="J47" s="173"/>
+      <c r="K47" s="173"/>
+      <c r="L47" s="174"/>
     </row>
     <row r="48" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="137" t="s">
+      <c r="C48" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="138"/>
-      <c r="E48" s="139"/>
+      <c r="D48" s="134"/>
+      <c r="E48" s="135"/>
       <c r="F48" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G48" s="137" t="s">
+      <c r="G48" s="133" t="s">
         <v>80</v>
       </c>
-      <c r="H48" s="139"/>
+      <c r="H48" s="135"/>
       <c r="I48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J48" s="54" t="s">
+      <c r="J48" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="167" t="s">
+      <c r="K48" s="168" t="s">
         <v>78</v>
       </c>
-      <c r="L48" s="168"/>
+      <c r="L48" s="169"/>
     </row>
     <row r="49" spans="2:13">
-      <c r="B49" s="46">
+      <c r="B49" s="44">
         <v>1</v>
       </c>
-      <c r="C49" s="137" t="str">
+      <c r="C49" s="133" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D49" s="138"/>
-      <c r="E49" s="139"/>
+      <c r="D49" s="134"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="7">
         <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G49" s="140">
+      <c r="G49" s="152">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H49" s="141"/>
-      <c r="I49" s="55">
+      <c r="H49" s="153"/>
+      <c r="I49" s="53">
         <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
       </c>
-      <c r="J49" s="55">
+      <c r="J49" s="53">
         <f t="shared" ref="J49" si="0">+F49*I49</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K49" s="136">
+      <c r="K49" s="175">
         <f t="shared" ref="K49" si="1">I49*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L49" s="136"/>
+      <c r="L49" s="175"/>
     </row>
     <row r="50" spans="2:13" ht="15.75">
-      <c r="B50" s="49" t="s">
+      <c r="B50" s="47" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="36">
+      <c r="F50" s="35">
         <f>+SUM(F49:F49)</f>
         <v>100</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="J50" s="56">
+      <c r="J50" s="54">
         <f>+SUM(J49:J49)</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K50" s="77"/>
-      <c r="L50" s="78"/>
+      <c r="K50" s="75"/>
+      <c r="L50" s="76"/>
     </row>
     <row r="51" spans="2:13" ht="15.75">
-      <c r="B51" s="49"/>
+      <c r="B51" s="47"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="36"/>
+      <c r="F51" s="35"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-      <c r="J51" s="62"/>
-      <c r="K51" s="77"/>
-      <c r="L51" s="78"/>
+      <c r="J51" s="60"/>
+      <c r="K51" s="75"/>
+      <c r="L51" s="76"/>
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="29"/>
@@ -3138,11 +3166,11 @@
       <c r="H52" s="29"/>
       <c r="I52" s="29"/>
       <c r="J52" s="29"/>
-      <c r="K52" s="79"/>
-      <c r="L52" s="80"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="78"/>
     </row>
     <row r="53" spans="2:13" ht="18.75">
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="59" t="s">
         <v>53</v>
       </c>
       <c r="C53" s="29"/>
@@ -3156,79 +3184,79 @@
       <c r="K53" s="29"/>
     </row>
     <row r="54" spans="2:13" ht="18.75">
-      <c r="B54" s="146" t="s">
+      <c r="B54" s="128" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="146"/>
-      <c r="D54" s="146"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="146"/>
-      <c r="G54" s="146"/>
-      <c r="H54" s="146"/>
-      <c r="I54" s="146"/>
-      <c r="J54" s="146"/>
-      <c r="K54" s="146"/>
-      <c r="L54" s="146"/>
+      <c r="C54" s="128"/>
+      <c r="D54" s="128"/>
+      <c r="E54" s="128"/>
+      <c r="F54" s="128"/>
+      <c r="G54" s="128"/>
+      <c r="H54" s="128"/>
+      <c r="I54" s="128"/>
+      <c r="J54" s="128"/>
+      <c r="K54" s="128"/>
+      <c r="L54" s="128"/>
     </row>
     <row r="55" spans="2:13" ht="18.75">
-      <c r="B55" s="146" t="s">
+      <c r="B55" s="128" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="146"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="146"/>
-      <c r="G55" s="146"/>
-      <c r="H55" s="146"/>
-      <c r="I55" s="146"/>
-      <c r="J55" s="146"/>
-      <c r="K55" s="146"/>
-      <c r="L55" s="146"/>
+      <c r="C55" s="128"/>
+      <c r="D55" s="128"/>
+      <c r="E55" s="128"/>
+      <c r="F55" s="128"/>
+      <c r="G55" s="128"/>
+      <c r="H55" s="128"/>
+      <c r="I55" s="128"/>
+      <c r="J55" s="128"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
     </row>
     <row r="56" spans="2:13" ht="18.75">
-      <c r="B56" s="146" t="s">
+      <c r="B56" s="128" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="146"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="146"/>
-      <c r="H56" s="146"/>
-      <c r="I56" s="146"/>
-      <c r="J56" s="146"/>
-      <c r="K56" s="146"/>
-      <c r="L56" s="146"/>
+      <c r="C56" s="128"/>
+      <c r="D56" s="128"/>
+      <c r="E56" s="128"/>
+      <c r="F56" s="128"/>
+      <c r="G56" s="128"/>
+      <c r="H56" s="128"/>
+      <c r="I56" s="128"/>
+      <c r="J56" s="128"/>
+      <c r="K56" s="128"/>
+      <c r="L56" s="128"/>
     </row>
     <row r="57" spans="2:13" ht="18.75">
-      <c r="B57" s="146" t="s">
+      <c r="B57" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="146"/>
-      <c r="D57" s="146"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="146"/>
-      <c r="G57" s="146"/>
-      <c r="H57" s="146"/>
-      <c r="I57" s="146"/>
-      <c r="J57" s="146"/>
-      <c r="K57" s="146"/>
-      <c r="L57" s="146"/>
+      <c r="C57" s="128"/>
+      <c r="D57" s="128"/>
+      <c r="E57" s="128"/>
+      <c r="F57" s="128"/>
+      <c r="G57" s="128"/>
+      <c r="H57" s="128"/>
+      <c r="I57" s="128"/>
+      <c r="J57" s="128"/>
+      <c r="K57" s="128"/>
+      <c r="L57" s="128"/>
     </row>
     <row r="58" spans="2:13" ht="18.75">
-      <c r="B58" s="146" t="s">
+      <c r="B58" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="146"/>
-      <c r="D58" s="146"/>
-      <c r="E58" s="146"/>
-      <c r="F58" s="146"/>
-      <c r="G58" s="146"/>
-      <c r="H58" s="146"/>
-      <c r="I58" s="146"/>
-      <c r="J58" s="146"/>
-      <c r="K58" s="146"/>
-      <c r="L58" s="146"/>
+      <c r="C58" s="128"/>
+      <c r="D58" s="128"/>
+      <c r="E58" s="128"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="128"/>
+      <c r="H58" s="128"/>
+      <c r="I58" s="128"/>
+      <c r="J58" s="128"/>
+      <c r="K58" s="128"/>
+      <c r="L58" s="128"/>
     </row>
     <row r="59" spans="2:13">
       <c r="B59" s="29"/>
@@ -3244,597 +3272,645 @@
       <c r="L59" s="29"/>
     </row>
     <row r="60" spans="2:13" ht="9" customHeight="1">
-      <c r="B60" s="125"/>
-      <c r="C60" s="125"/>
-      <c r="E60" s="125"/>
-      <c r="F60" s="125"/>
-      <c r="G60" s="125"/>
-      <c r="H60" s="125"/>
-      <c r="I60" s="125"/>
-      <c r="J60" s="125"/>
-      <c r="K60" s="125"/>
-      <c r="L60" s="125"/>
-      <c r="M60" s="125"/>
+      <c r="B60" s="126"/>
+      <c r="C60" s="126"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="126"/>
+      <c r="I60" s="126"/>
+      <c r="J60" s="126"/>
+      <c r="K60" s="126"/>
+      <c r="L60" s="126"/>
+      <c r="M60" s="126"/>
     </row>
     <row r="61" spans="2:13" ht="31.9" customHeight="1">
-      <c r="B61" s="125"/>
-      <c r="C61" s="125"/>
-      <c r="D61" s="159" t="s">
+      <c r="B61" s="126"/>
+      <c r="C61" s="126"/>
+      <c r="D61" s="136" t="s">
         <v>119</v>
       </c>
-      <c r="E61" s="159"/>
-      <c r="F61" s="159"/>
-      <c r="G61" s="159"/>
-      <c r="H61" s="159"/>
-      <c r="I61" s="159"/>
-      <c r="J61" s="159"/>
-      <c r="K61" s="159"/>
-      <c r="L61" s="159"/>
-      <c r="M61" s="159"/>
+      <c r="E61" s="136"/>
+      <c r="F61" s="136"/>
+      <c r="G61" s="136"/>
+      <c r="H61" s="136"/>
+      <c r="I61" s="136"/>
+      <c r="J61" s="136"/>
+      <c r="K61" s="136"/>
+      <c r="L61" s="136"/>
+      <c r="M61" s="136"/>
     </row>
     <row r="62" spans="2:13" ht="21" customHeight="1">
-      <c r="B62" s="125"/>
-      <c r="C62" s="125"/>
-      <c r="D62" s="133" t="s">
+      <c r="B62" s="126"/>
+      <c r="C62" s="126"/>
+      <c r="D62" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="E62" s="133"/>
-      <c r="F62" s="133"/>
-      <c r="G62" s="133"/>
-      <c r="H62" s="133"/>
-      <c r="I62" s="133"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="149"/>
+      <c r="H62" s="149"/>
+      <c r="I62" s="149"/>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="125"/>
-      <c r="C63" s="125"/>
+      <c r="B63" s="126"/>
+      <c r="C63" s="126"/>
     </row>
     <row r="64" spans="2:13">
-      <c r="B64" s="125"/>
-      <c r="C64" s="125"/>
+      <c r="B64" s="126"/>
+      <c r="C64" s="126"/>
     </row>
     <row r="65" spans="2:12" ht="21">
-      <c r="B65" s="169" t="s">
+      <c r="B65" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="169"/>
-      <c r="D65" s="169"/>
-      <c r="E65" s="169"/>
-      <c r="F65" s="169"/>
-      <c r="G65" s="169"/>
-      <c r="H65" s="169"/>
-      <c r="I65" s="169"/>
-      <c r="J65" s="169"/>
-      <c r="K65" s="169"/>
-      <c r="L65" s="169"/>
+      <c r="C65" s="129"/>
+      <c r="D65" s="129"/>
+      <c r="E65" s="129"/>
+      <c r="F65" s="129"/>
+      <c r="G65" s="129"/>
+      <c r="H65" s="129"/>
+      <c r="I65" s="129"/>
+      <c r="J65" s="129"/>
+      <c r="K65" s="129"/>
+      <c r="L65" s="129"/>
     </row>
     <row r="67" spans="2:12">
-      <c r="B67" s="154" t="s">
+      <c r="B67" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="154"/>
-      <c r="D67" s="154"/>
-      <c r="E67" s="154"/>
-      <c r="F67" s="154"/>
-      <c r="G67" s="154"/>
-      <c r="H67" s="154"/>
-      <c r="I67" s="154"/>
-      <c r="J67" s="154"/>
-      <c r="K67" s="154"/>
-      <c r="L67" s="154"/>
+      <c r="C67" s="125"/>
+      <c r="D67" s="125"/>
+      <c r="E67" s="125"/>
+      <c r="F67" s="125"/>
+      <c r="G67" s="125"/>
+      <c r="H67" s="125"/>
+      <c r="I67" s="125"/>
+      <c r="J67" s="125"/>
+      <c r="K67" s="125"/>
+      <c r="L67" s="125"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="154" t="s">
+      <c r="B68" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="154"/>
-      <c r="D68" s="154"/>
-      <c r="E68" s="154"/>
-      <c r="F68" s="154"/>
-      <c r="G68" s="154"/>
-      <c r="H68" s="154"/>
-      <c r="I68" s="154"/>
-      <c r="J68" s="154"/>
-      <c r="K68" s="154"/>
-      <c r="L68" s="154"/>
+      <c r="C68" s="125"/>
+      <c r="D68" s="125"/>
+      <c r="E68" s="125"/>
+      <c r="F68" s="125"/>
+      <c r="G68" s="125"/>
+      <c r="H68" s="125"/>
+      <c r="I68" s="125"/>
+      <c r="J68" s="125"/>
+      <c r="K68" s="125"/>
+      <c r="L68" s="125"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="153" t="s">
+      <c r="B69" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="153"/>
-      <c r="D69" s="153"/>
-      <c r="E69" s="153"/>
-      <c r="F69" s="153"/>
-      <c r="G69" s="153"/>
-      <c r="H69" s="153"/>
-      <c r="I69" s="153"/>
-      <c r="J69" s="153"/>
-      <c r="K69" s="153"/>
-      <c r="L69" s="153"/>
+      <c r="C69" s="127"/>
+      <c r="D69" s="127"/>
+      <c r="E69" s="127"/>
+      <c r="F69" s="127"/>
+      <c r="G69" s="127"/>
+      <c r="H69" s="127"/>
+      <c r="I69" s="127"/>
+      <c r="J69" s="127"/>
+      <c r="K69" s="127"/>
+      <c r="L69" s="127"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="154" t="s">
+      <c r="B70" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="154"/>
-      <c r="D70" s="154"/>
-      <c r="E70" s="154"/>
-      <c r="F70" s="154"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="154"/>
-      <c r="I70" s="154"/>
-      <c r="J70" s="154"/>
-      <c r="K70" s="154"/>
-      <c r="L70" s="154"/>
+      <c r="C70" s="125"/>
+      <c r="D70" s="125"/>
+      <c r="E70" s="125"/>
+      <c r="F70" s="125"/>
+      <c r="G70" s="125"/>
+      <c r="H70" s="125"/>
+      <c r="I70" s="125"/>
+      <c r="J70" s="125"/>
+      <c r="K70" s="125"/>
+      <c r="L70" s="125"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="154" t="s">
+      <c r="B71" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="C71" s="154"/>
-      <c r="D71" s="154"/>
-      <c r="E71" s="154"/>
-      <c r="F71" s="154"/>
-      <c r="G71" s="154"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="154"/>
-      <c r="J71" s="154"/>
-      <c r="K71" s="154"/>
-      <c r="L71" s="154"/>
+      <c r="C71" s="125"/>
+      <c r="D71" s="125"/>
+      <c r="E71" s="125"/>
+      <c r="F71" s="125"/>
+      <c r="G71" s="125"/>
+      <c r="H71" s="125"/>
+      <c r="I71" s="125"/>
+      <c r="J71" s="125"/>
+      <c r="K71" s="125"/>
+      <c r="L71" s="125"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="153" t="s">
+      <c r="B72" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="153"/>
-      <c r="D72" s="153"/>
-      <c r="E72" s="153"/>
-      <c r="F72" s="153"/>
-      <c r="G72" s="153"/>
-      <c r="H72" s="153"/>
-      <c r="I72" s="153"/>
-      <c r="J72" s="153"/>
-      <c r="K72" s="153"/>
-      <c r="L72" s="153"/>
+      <c r="C72" s="127"/>
+      <c r="D72" s="127"/>
+      <c r="E72" s="127"/>
+      <c r="F72" s="127"/>
+      <c r="G72" s="127"/>
+      <c r="H72" s="127"/>
+      <c r="I72" s="127"/>
+      <c r="J72" s="127"/>
+      <c r="K72" s="127"/>
+      <c r="L72" s="127"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="154" t="s">
+      <c r="B73" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="154"/>
-      <c r="D73" s="154"/>
-      <c r="E73" s="154"/>
-      <c r="F73" s="154"/>
-      <c r="G73" s="154"/>
-      <c r="H73" s="154"/>
-      <c r="I73" s="154"/>
-      <c r="J73" s="154"/>
-      <c r="K73" s="154"/>
-      <c r="L73" s="154"/>
+      <c r="C73" s="125"/>
+      <c r="D73" s="125"/>
+      <c r="E73" s="125"/>
+      <c r="F73" s="125"/>
+      <c r="G73" s="125"/>
+      <c r="H73" s="125"/>
+      <c r="I73" s="125"/>
+      <c r="J73" s="125"/>
+      <c r="K73" s="125"/>
+      <c r="L73" s="125"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="154" t="s">
+      <c r="B74" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="154"/>
-      <c r="D74" s="154"/>
-      <c r="E74" s="154"/>
-      <c r="F74" s="154"/>
-      <c r="G74" s="154"/>
-      <c r="H74" s="154"/>
-      <c r="I74" s="154"/>
-      <c r="J74" s="154"/>
-      <c r="K74" s="154"/>
-      <c r="L74" s="154"/>
+      <c r="C74" s="125"/>
+      <c r="D74" s="125"/>
+      <c r="E74" s="125"/>
+      <c r="F74" s="125"/>
+      <c r="G74" s="125"/>
+      <c r="H74" s="125"/>
+      <c r="I74" s="125"/>
+      <c r="J74" s="125"/>
+      <c r="K74" s="125"/>
+      <c r="L74" s="125"/>
     </row>
     <row r="75" spans="2:12">
-      <c r="B75" s="154" t="s">
+      <c r="B75" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="154"/>
-      <c r="D75" s="154"/>
-      <c r="E75" s="154"/>
-      <c r="F75" s="154"/>
-      <c r="G75" s="154"/>
-      <c r="H75" s="154"/>
-      <c r="I75" s="154"/>
-      <c r="J75" s="154"/>
-      <c r="K75" s="154"/>
-      <c r="L75" s="154"/>
+      <c r="C75" s="125"/>
+      <c r="D75" s="125"/>
+      <c r="E75" s="125"/>
+      <c r="F75" s="125"/>
+      <c r="G75" s="125"/>
+      <c r="H75" s="125"/>
+      <c r="I75" s="125"/>
+      <c r="J75" s="125"/>
+      <c r="K75" s="125"/>
+      <c r="L75" s="125"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="154" t="s">
+      <c r="B76" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="154"/>
-      <c r="D76" s="154"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="154"/>
-      <c r="H76" s="154"/>
-      <c r="I76" s="154"/>
-      <c r="J76" s="154"/>
-      <c r="K76" s="154"/>
-      <c r="L76" s="154"/>
+      <c r="C76" s="125"/>
+      <c r="D76" s="125"/>
+      <c r="E76" s="125"/>
+      <c r="F76" s="125"/>
+      <c r="G76" s="125"/>
+      <c r="H76" s="125"/>
+      <c r="I76" s="125"/>
+      <c r="J76" s="125"/>
+      <c r="K76" s="125"/>
+      <c r="L76" s="125"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="154" t="s">
+      <c r="B77" s="125" t="s">
         <v>62</v>
       </c>
-      <c r="C77" s="154"/>
-      <c r="D77" s="154"/>
-      <c r="E77" s="154"/>
-      <c r="F77" s="154"/>
-      <c r="G77" s="154"/>
-      <c r="H77" s="154"/>
-      <c r="I77" s="154"/>
-      <c r="J77" s="154"/>
-      <c r="K77" s="154"/>
-      <c r="L77" s="154"/>
+      <c r="C77" s="125"/>
+      <c r="D77" s="125"/>
+      <c r="E77" s="125"/>
+      <c r="F77" s="125"/>
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
+      <c r="I77" s="125"/>
+      <c r="J77" s="125"/>
+      <c r="K77" s="125"/>
+      <c r="L77" s="125"/>
     </row>
     <row r="78" spans="2:12">
-      <c r="B78" s="154" t="s">
+      <c r="B78" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="154"/>
-      <c r="D78" s="154"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="154"/>
-      <c r="G78" s="154"/>
-      <c r="H78" s="154"/>
-      <c r="I78" s="154"/>
-      <c r="J78" s="154"/>
-      <c r="K78" s="154"/>
-      <c r="L78" s="154"/>
+      <c r="C78" s="125"/>
+      <c r="D78" s="125"/>
+      <c r="E78" s="125"/>
+      <c r="F78" s="125"/>
+      <c r="G78" s="125"/>
+      <c r="H78" s="125"/>
+      <c r="I78" s="125"/>
+      <c r="J78" s="125"/>
+      <c r="K78" s="125"/>
+      <c r="L78" s="125"/>
     </row>
     <row r="79" spans="2:12">
-      <c r="B79" s="154" t="s">
+      <c r="B79" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="C79" s="154"/>
-      <c r="D79" s="154"/>
-      <c r="E79" s="154"/>
-      <c r="F79" s="154"/>
-      <c r="G79" s="154"/>
-      <c r="H79" s="154"/>
-      <c r="I79" s="154"/>
-      <c r="J79" s="154"/>
-      <c r="K79" s="154"/>
-      <c r="L79" s="154"/>
+      <c r="C79" s="125"/>
+      <c r="D79" s="125"/>
+      <c r="E79" s="125"/>
+      <c r="F79" s="125"/>
+      <c r="G79" s="125"/>
+      <c r="H79" s="125"/>
+      <c r="I79" s="125"/>
+      <c r="J79" s="125"/>
+      <c r="K79" s="125"/>
+      <c r="L79" s="125"/>
     </row>
     <row r="80" spans="2:12">
-      <c r="B80" s="154" t="s">
+      <c r="B80" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="154"/>
-      <c r="D80" s="154"/>
-      <c r="E80" s="154"/>
-      <c r="F80" s="154"/>
-      <c r="G80" s="154"/>
-      <c r="H80" s="154"/>
-      <c r="I80" s="154"/>
-      <c r="J80" s="154"/>
-      <c r="K80" s="154"/>
-      <c r="L80" s="154"/>
+      <c r="C80" s="125"/>
+      <c r="D80" s="125"/>
+      <c r="E80" s="125"/>
+      <c r="F80" s="125"/>
+      <c r="G80" s="125"/>
+      <c r="H80" s="125"/>
+      <c r="I80" s="125"/>
+      <c r="J80" s="125"/>
+      <c r="K80" s="125"/>
+      <c r="L80" s="125"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="B81" s="154" t="s">
+      <c r="B81" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="154"/>
-      <c r="D81" s="154"/>
-      <c r="E81" s="154"/>
-      <c r="F81" s="154"/>
-      <c r="G81" s="154"/>
-      <c r="H81" s="154"/>
-      <c r="I81" s="154"/>
-      <c r="J81" s="154"/>
-      <c r="K81" s="154"/>
-      <c r="L81" s="154"/>
+      <c r="C81" s="125"/>
+      <c r="D81" s="125"/>
+      <c r="E81" s="125"/>
+      <c r="F81" s="125"/>
+      <c r="G81" s="125"/>
+      <c r="H81" s="125"/>
+      <c r="I81" s="125"/>
+      <c r="J81" s="125"/>
+      <c r="K81" s="125"/>
+      <c r="L81" s="125"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="B82" s="154" t="s">
+      <c r="B82" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="154"/>
-      <c r="D82" s="154"/>
-      <c r="E82" s="154"/>
-      <c r="F82" s="154"/>
-      <c r="G82" s="154"/>
-      <c r="H82" s="154"/>
-      <c r="I82" s="154"/>
-      <c r="J82" s="154"/>
-      <c r="K82" s="154"/>
-      <c r="L82" s="154"/>
+      <c r="C82" s="125"/>
+      <c r="D82" s="125"/>
+      <c r="E82" s="125"/>
+      <c r="F82" s="125"/>
+      <c r="G82" s="125"/>
+      <c r="H82" s="125"/>
+      <c r="I82" s="125"/>
+      <c r="J82" s="125"/>
+      <c r="K82" s="125"/>
+      <c r="L82" s="125"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="B83" s="154" t="s">
+      <c r="B83" s="125" t="s">
         <v>66</v>
       </c>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
-      <c r="E83" s="154"/>
-      <c r="F83" s="154"/>
-      <c r="G83" s="154"/>
-      <c r="H83" s="154"/>
-      <c r="I83" s="154"/>
-      <c r="J83" s="154"/>
-      <c r="K83" s="154"/>
-      <c r="L83" s="154"/>
+      <c r="C83" s="125"/>
+      <c r="D83" s="125"/>
+      <c r="E83" s="125"/>
+      <c r="F83" s="125"/>
+      <c r="G83" s="125"/>
+      <c r="H83" s="125"/>
+      <c r="I83" s="125"/>
+      <c r="J83" s="125"/>
+      <c r="K83" s="125"/>
+      <c r="L83" s="125"/>
     </row>
     <row r="84" spans="1:12">
-      <c r="B84" s="150" t="s">
+      <c r="B84" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="C84" s="150"/>
-      <c r="D84" s="150"/>
-      <c r="E84" s="150"/>
-      <c r="F84" s="150"/>
-      <c r="G84" s="150"/>
-      <c r="H84" s="150"/>
-      <c r="I84" s="150"/>
-      <c r="J84" s="150"/>
-      <c r="K84" s="150"/>
-      <c r="L84" s="150"/>
+      <c r="C84" s="124"/>
+      <c r="D84" s="124"/>
+      <c r="E84" s="124"/>
+      <c r="F84" s="124"/>
+      <c r="G84" s="124"/>
+      <c r="H84" s="124"/>
+      <c r="I84" s="124"/>
+      <c r="J84" s="124"/>
+      <c r="K84" s="124"/>
+      <c r="L84" s="124"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="B85" s="154" t="s">
+      <c r="B85" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
-      <c r="E85" s="154"/>
-      <c r="F85" s="154"/>
-      <c r="G85" s="154"/>
-      <c r="H85" s="154"/>
-      <c r="I85" s="154"/>
-      <c r="J85" s="154"/>
-      <c r="K85" s="154"/>
-      <c r="L85" s="154"/>
+      <c r="C85" s="125"/>
+      <c r="D85" s="125"/>
+      <c r="E85" s="125"/>
+      <c r="F85" s="125"/>
+      <c r="G85" s="125"/>
+      <c r="H85" s="125"/>
+      <c r="I85" s="125"/>
+      <c r="J85" s="125"/>
+      <c r="K85" s="125"/>
+      <c r="L85" s="125"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="B86" s="150" t="s">
+      <c r="B86" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="C86" s="150"/>
-      <c r="D86" s="150"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="150"/>
-      <c r="G86" s="150"/>
-      <c r="H86" s="150"/>
-      <c r="I86" s="150"/>
-      <c r="J86" s="150"/>
-      <c r="K86" s="150"/>
-      <c r="L86" s="150"/>
+      <c r="C86" s="124"/>
+      <c r="D86" s="124"/>
+      <c r="E86" s="124"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="124"/>
+      <c r="H86" s="124"/>
+      <c r="I86" s="124"/>
+      <c r="J86" s="124"/>
+      <c r="K86" s="124"/>
+      <c r="L86" s="124"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="B87" s="154" t="s">
+      <c r="B87" s="125" t="s">
         <v>68</v>
       </c>
-      <c r="C87" s="154"/>
-      <c r="D87" s="154"/>
-      <c r="E87" s="154"/>
-      <c r="F87" s="154"/>
-      <c r="G87" s="154"/>
-      <c r="H87" s="154"/>
-      <c r="I87" s="154"/>
-      <c r="J87" s="154"/>
-      <c r="K87" s="154"/>
-      <c r="L87" s="154"/>
+      <c r="C87" s="125"/>
+      <c r="D87" s="125"/>
+      <c r="E87" s="125"/>
+      <c r="F87" s="125"/>
+      <c r="G87" s="125"/>
+      <c r="H87" s="125"/>
+      <c r="I87" s="125"/>
+      <c r="J87" s="125"/>
+      <c r="K87" s="125"/>
+      <c r="L87" s="125"/>
     </row>
     <row r="88" spans="1:12">
-      <c r="B88" s="154" t="s">
+      <c r="B88" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="154"/>
-      <c r="D88" s="154"/>
-      <c r="E88" s="154"/>
-      <c r="F88" s="154"/>
-      <c r="G88" s="154"/>
-      <c r="H88" s="154"/>
-      <c r="I88" s="154"/>
-      <c r="J88" s="154"/>
-      <c r="K88" s="154"/>
-      <c r="L88" s="154"/>
+      <c r="C88" s="125"/>
+      <c r="D88" s="125"/>
+      <c r="E88" s="125"/>
+      <c r="F88" s="125"/>
+      <c r="G88" s="125"/>
+      <c r="H88" s="125"/>
+      <c r="I88" s="125"/>
+      <c r="J88" s="125"/>
+      <c r="K88" s="125"/>
+      <c r="L88" s="125"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="B89" s="154" t="s">
+      <c r="B89" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="C89" s="154"/>
-      <c r="D89" s="154"/>
-      <c r="E89" s="154"/>
-      <c r="F89" s="154"/>
-      <c r="G89" s="154"/>
-      <c r="H89" s="154"/>
-      <c r="I89" s="154"/>
-      <c r="J89" s="154"/>
-      <c r="K89" s="154"/>
-      <c r="L89" s="154"/>
+      <c r="C89" s="125"/>
+      <c r="D89" s="125"/>
+      <c r="E89" s="125"/>
+      <c r="F89" s="125"/>
+      <c r="G89" s="125"/>
+      <c r="H89" s="125"/>
+      <c r="I89" s="125"/>
+      <c r="J89" s="125"/>
+      <c r="K89" s="125"/>
+      <c r="L89" s="125"/>
     </row>
     <row r="90" spans="1:12">
-      <c r="B90" s="154" t="s">
+      <c r="B90" s="125" t="s">
         <v>71</v>
       </c>
-      <c r="C90" s="154"/>
-      <c r="D90" s="154"/>
-      <c r="E90" s="154"/>
-      <c r="F90" s="154"/>
-      <c r="G90" s="154"/>
-      <c r="H90" s="154"/>
-      <c r="I90" s="154"/>
-      <c r="J90" s="154"/>
-      <c r="K90" s="154"/>
-      <c r="L90" s="154"/>
+      <c r="C90" s="125"/>
+      <c r="D90" s="125"/>
+      <c r="E90" s="125"/>
+      <c r="F90" s="125"/>
+      <c r="G90" s="125"/>
+      <c r="H90" s="125"/>
+      <c r="I90" s="125"/>
+      <c r="J90" s="125"/>
+      <c r="K90" s="125"/>
+      <c r="L90" s="125"/>
     </row>
     <row r="91" spans="1:12">
-      <c r="B91" s="154" t="s">
+      <c r="B91" s="125" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="154"/>
-      <c r="D91" s="154"/>
-      <c r="E91" s="154"/>
-      <c r="F91" s="154"/>
-      <c r="G91" s="154"/>
-      <c r="H91" s="154"/>
-      <c r="I91" s="154"/>
-      <c r="J91" s="154"/>
-      <c r="K91" s="154"/>
-      <c r="L91" s="154"/>
+      <c r="C91" s="125"/>
+      <c r="D91" s="125"/>
+      <c r="E91" s="125"/>
+      <c r="F91" s="125"/>
+      <c r="G91" s="125"/>
+      <c r="H91" s="125"/>
+      <c r="I91" s="125"/>
+      <c r="J91" s="125"/>
+      <c r="K91" s="125"/>
+      <c r="L91" s="125"/>
     </row>
     <row r="92" spans="1:12">
-      <c r="A92" s="85"/>
-      <c r="B92" s="155" t="s">
+      <c r="A92" s="83"/>
+      <c r="B92" s="145" t="s">
         <v>84</v>
       </c>
-      <c r="C92" s="155"/>
-      <c r="D92" s="155"/>
-      <c r="E92" s="155"/>
-      <c r="F92" s="155"/>
-      <c r="G92" s="155"/>
-      <c r="H92" s="155"/>
-      <c r="I92" s="155"/>
-      <c r="J92" s="155"/>
-      <c r="K92" s="155"/>
-      <c r="L92" s="155"/>
+      <c r="C92" s="145"/>
+      <c r="D92" s="145"/>
+      <c r="E92" s="145"/>
+      <c r="F92" s="145"/>
+      <c r="G92" s="145"/>
+      <c r="H92" s="145"/>
+      <c r="I92" s="145"/>
+      <c r="J92" s="145"/>
+      <c r="K92" s="145"/>
+      <c r="L92" s="145"/>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="85"/>
-      <c r="B93" s="154" t="s">
+      <c r="A93" s="83"/>
+      <c r="B93" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="C93" s="154"/>
-      <c r="D93" s="154"/>
-      <c r="E93" s="154"/>
-      <c r="F93" s="154"/>
-      <c r="G93" s="154"/>
-      <c r="H93" s="154"/>
-      <c r="I93" s="154"/>
-      <c r="J93" s="154"/>
-      <c r="K93" s="154"/>
-      <c r="L93" s="154"/>
+      <c r="C93" s="125"/>
+      <c r="D93" s="125"/>
+      <c r="E93" s="125"/>
+      <c r="F93" s="125"/>
+      <c r="G93" s="125"/>
+      <c r="H93" s="125"/>
+      <c r="I93" s="125"/>
+      <c r="J93" s="125"/>
+      <c r="K93" s="125"/>
+      <c r="L93" s="125"/>
     </row>
     <row r="94" spans="1:12">
-      <c r="A94" s="85"/>
-      <c r="B94" s="155" t="s">
+      <c r="A94" s="83"/>
+      <c r="B94" s="145" t="s">
         <v>86</v>
       </c>
-      <c r="C94" s="155"/>
-      <c r="D94" s="155"/>
-      <c r="E94" s="155"/>
-      <c r="F94" s="155"/>
-      <c r="G94" s="155"/>
-      <c r="H94" s="155"/>
-      <c r="I94" s="155"/>
-      <c r="J94" s="155"/>
-      <c r="K94" s="155"/>
-      <c r="L94" s="155"/>
+      <c r="C94" s="145"/>
+      <c r="D94" s="145"/>
+      <c r="E94" s="145"/>
+      <c r="F94" s="145"/>
+      <c r="G94" s="145"/>
+      <c r="H94" s="145"/>
+      <c r="I94" s="145"/>
+      <c r="J94" s="145"/>
+      <c r="K94" s="145"/>
+      <c r="L94" s="145"/>
     </row>
     <row r="96" spans="1:12">
-      <c r="C96" s="125"/>
-      <c r="D96" s="125"/>
-      <c r="E96" s="125"/>
-      <c r="F96" s="125"/>
-      <c r="G96" s="125"/>
-      <c r="H96" s="125"/>
-      <c r="I96" s="125"/>
+      <c r="C96" s="126"/>
+      <c r="D96" s="126"/>
+      <c r="E96" s="126"/>
+      <c r="F96" s="126"/>
+      <c r="G96" s="126"/>
+      <c r="H96" s="126"/>
+      <c r="I96" s="126"/>
     </row>
     <row r="97" spans="3:9">
-      <c r="C97" s="125"/>
-      <c r="D97" s="125"/>
-      <c r="E97" s="125"/>
-      <c r="F97" s="125"/>
-      <c r="G97" s="125"/>
-      <c r="H97" s="125"/>
-      <c r="I97" s="125"/>
+      <c r="C97" s="126"/>
+      <c r="D97" s="126"/>
+      <c r="E97" s="126"/>
+      <c r="F97" s="126"/>
+      <c r="G97" s="126"/>
+      <c r="H97" s="126"/>
+      <c r="I97" s="126"/>
     </row>
     <row r="98" spans="3:9">
-      <c r="C98" s="125"/>
-      <c r="D98" s="125"/>
-      <c r="E98" s="125"/>
-      <c r="F98" s="125"/>
-      <c r="G98" s="125"/>
-      <c r="H98" s="125"/>
-      <c r="I98" s="125"/>
+      <c r="C98" s="126"/>
+      <c r="D98" s="126"/>
+      <c r="E98" s="126"/>
+      <c r="F98" s="126"/>
+      <c r="G98" s="126"/>
+      <c r="H98" s="126"/>
+      <c r="I98" s="126"/>
     </row>
     <row r="99" spans="3:9">
-      <c r="C99" s="125"/>
-      <c r="D99" s="125"/>
-      <c r="E99" s="125"/>
-      <c r="F99" s="125"/>
-      <c r="G99" s="125"/>
-      <c r="H99" s="125"/>
-      <c r="I99" s="125"/>
+      <c r="C99" s="126"/>
+      <c r="D99" s="126"/>
+      <c r="E99" s="126"/>
+      <c r="F99" s="126"/>
+      <c r="G99" s="126"/>
+      <c r="H99" s="126"/>
+      <c r="I99" s="126"/>
     </row>
     <row r="100" spans="3:9">
-      <c r="C100" s="125"/>
-      <c r="D100" s="125"/>
-      <c r="E100" s="125"/>
-      <c r="F100" s="125"/>
-      <c r="G100" s="125"/>
-      <c r="H100" s="125"/>
-      <c r="I100" s="125"/>
+      <c r="C100" s="126"/>
+      <c r="D100" s="126"/>
+      <c r="E100" s="126"/>
+      <c r="F100" s="126"/>
+      <c r="G100" s="126"/>
+      <c r="H100" s="126"/>
+      <c r="I100" s="126"/>
     </row>
     <row r="101" spans="3:9">
-      <c r="C101" s="125"/>
-      <c r="D101" s="125"/>
-      <c r="E101" s="125"/>
-      <c r="F101" s="125"/>
-      <c r="G101" s="125"/>
-      <c r="H101" s="125"/>
-      <c r="I101" s="125"/>
+      <c r="C101" s="126"/>
+      <c r="D101" s="126"/>
+      <c r="E101" s="126"/>
+      <c r="F101" s="126"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="126"/>
+      <c r="I101" s="126"/>
     </row>
     <row r="102" spans="3:9">
-      <c r="C102" s="125"/>
-      <c r="D102" s="125"/>
-      <c r="E102" s="125"/>
-      <c r="F102" s="125"/>
-      <c r="G102" s="125"/>
-      <c r="H102" s="125"/>
-      <c r="I102" s="125"/>
+      <c r="C102" s="126"/>
+      <c r="D102" s="126"/>
+      <c r="E102" s="126"/>
+      <c r="F102" s="126"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="126"/>
+      <c r="I102" s="126"/>
     </row>
     <row r="103" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C103" s="125"/>
-      <c r="D103" s="125"/>
-      <c r="E103" s="125"/>
-      <c r="F103" s="125"/>
-      <c r="G103" s="125"/>
-      <c r="H103" s="125"/>
-      <c r="I103" s="125"/>
+      <c r="C103" s="126"/>
+      <c r="D103" s="126"/>
+      <c r="E103" s="126"/>
+      <c r="F103" s="126"/>
+      <c r="G103" s="126"/>
+      <c r="H103" s="126"/>
+      <c r="I103" s="126"/>
     </row>
     <row r="104" spans="3:9" ht="15.6" customHeight="1">
-      <c r="C104" s="125"/>
-      <c r="D104" s="125"/>
-      <c r="E104" s="125"/>
-      <c r="F104" s="125"/>
-      <c r="G104" s="125"/>
-      <c r="H104" s="125"/>
-      <c r="I104" s="125"/>
+      <c r="C104" s="126"/>
+      <c r="D104" s="126"/>
+      <c r="E104" s="126"/>
+      <c r="F104" s="126"/>
+      <c r="G104" s="126"/>
+      <c r="H104" s="126"/>
+      <c r="I104" s="126"/>
     </row>
     <row r="105" spans="3:9">
-      <c r="C105" s="125"/>
-      <c r="D105" s="125"/>
-      <c r="E105" s="125"/>
-      <c r="F105" s="125"/>
-      <c r="G105" s="125"/>
-      <c r="H105" s="125"/>
-      <c r="I105" s="125"/>
+      <c r="C105" s="126"/>
+      <c r="D105" s="126"/>
+      <c r="E105" s="126"/>
+      <c r="F105" s="126"/>
+      <c r="G105" s="126"/>
+      <c r="H105" s="126"/>
+      <c r="I105" s="126"/>
     </row>
     <row r="111" spans="3:9" ht="15.6" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="86">
-    <mergeCell ref="B84:L84"/>
-    <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="E60:M60"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B65:L65"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B2:C6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="C96:I105"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="D62:I62"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B91:L91"/>
+    <mergeCell ref="B86:L86"/>
+    <mergeCell ref="B87:L87"/>
+    <mergeCell ref="B88:L88"/>
+    <mergeCell ref="B89:L89"/>
+    <mergeCell ref="B90:L90"/>
+    <mergeCell ref="B94:L94"/>
+    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B93:L93"/>
+    <mergeCell ref="B92:L92"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="B60:C64"/>
     <mergeCell ref="B19:F19"/>
@@ -3851,65 +3927,17 @@
     <mergeCell ref="B39:J39"/>
     <mergeCell ref="B40:J40"/>
     <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B94:L94"/>
-    <mergeCell ref="B77:L77"/>
-    <mergeCell ref="B78:L78"/>
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B74:L74"/>
-    <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B76:L76"/>
-    <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B82:L82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="B93:L93"/>
-    <mergeCell ref="B92:L92"/>
-    <mergeCell ref="B91:L91"/>
-    <mergeCell ref="B86:L86"/>
-    <mergeCell ref="B87:L87"/>
-    <mergeCell ref="B88:L88"/>
-    <mergeCell ref="B89:L89"/>
-    <mergeCell ref="B90:L90"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="C96:I105"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D62:I62"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="B47:L47"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B2:C6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="B84:L84"/>
+    <mergeCell ref="B85:L85"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="E60:M60"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B65:L65"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="VERIFICAR NÚMERO DE TELEFONO" error="Verifica que tenga 9 digitos sin espacio" sqref="J8:L8" xr:uid="{CC0405B2-A74A-4E8F-BF03-C34BEE695B67}">
@@ -3956,29 +3984,29 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="68" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="68" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3993,7 +4021,7 @@
       <c r="E7" s="7">
         <v>1</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="66">
         <f>SUM(C7:E7)</f>
         <v>8</v>
       </c>
@@ -4002,38 +4030,38 @@
       <c r="B8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="64">
         <v>110</v>
       </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66">
+      <c r="D8" s="64"/>
+      <c r="E8" s="64">
         <v>6</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="67">
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="170" t="s">
+      <c r="J8" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="170"/>
-      <c r="M8" s="170" t="s">
+      <c r="K8" s="164"/>
+      <c r="M8" s="164" t="s">
         <v>107</v>
       </c>
-      <c r="N8" s="170"/>
+      <c r="N8" s="164"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="65">
+      <c r="C9" s="63">
         <v>1.1539999999999999</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65">
+      <c r="D9" s="63"/>
+      <c r="E9" s="63">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="65">
         <f>SUM(C9:E9)</f>
         <v>1.1879999999999999</v>
       </c>
@@ -4060,31 +4088,31 @@
       <c r="AF9"/>
     </row>
     <row r="10" spans="2:32" ht="15" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="62">
         <v>6.36</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="62">
         <v>8.0299999999999994</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="62">
         <v>6</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="J10" s="58" t="s">
+      <c r="J10" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="K10" s="72">
+      <c r="K10" s="70">
         <v>250</v>
       </c>
-      <c r="M10" s="58" t="s">
+      <c r="M10" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="70">
         <v>250</v>
       </c>
       <c r="Y10"/>
@@ -4097,23 +4125,23 @@
       <c r="AF10"/>
     </row>
     <row r="11" spans="2:32" ht="15" hidden="1" customHeight="1">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="1"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="J11" s="58">
+      <c r="J11" s="56">
         <v>0.1</v>
       </c>
-      <c r="K11" s="72"/>
-      <c r="M11" s="58">
+      <c r="K11" s="70"/>
+      <c r="M11" s="56">
         <v>0.1</v>
       </c>
-      <c r="N11" s="72"/>
+      <c r="N11" s="70"/>
       <c r="Y11"/>
       <c r="Z11"/>
       <c r="AA11"/>
@@ -4136,21 +4164,21 @@
       <c r="E12" s="7">
         <v>50</v>
       </c>
-      <c r="F12" s="68">
+      <c r="F12" s="66">
         <f>SUM(C12:E12)</f>
         <v>151</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="J12" s="58" t="s">
+      <c r="J12" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="72">
+      <c r="K12" s="70">
         <v>350</v>
       </c>
-      <c r="M12" s="58" t="s">
+      <c r="M12" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="70">
         <v>325</v>
       </c>
       <c r="Y12"/>
@@ -4183,16 +4211,16 @@
         <v>944.03</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="70">
         <v>350</v>
       </c>
-      <c r="M13" s="58" t="s">
+      <c r="M13" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="N13" s="72">
+      <c r="N13" s="70">
         <v>325</v>
       </c>
       <c r="Y13"/>
@@ -4205,34 +4233,34 @@
       <c r="AF13"/>
     </row>
     <row r="14" spans="2:32" ht="16.5" hidden="1" customHeight="1">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="43">
         <f>(MAX(C10:C11))*C12</f>
         <v>636</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="43">
         <f t="shared" ref="D14:E14" si="1">(MAX(D10:D11))*D12</f>
         <v>8.0299999999999994</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="43">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="43">
         <f>SUM(C14:E14)</f>
         <v>944.03</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="J14" s="58">
+      <c r="J14" s="56">
         <v>0.1</v>
       </c>
-      <c r="K14" s="72"/>
-      <c r="M14" s="58">
+      <c r="K14" s="70"/>
+      <c r="M14" s="56">
         <v>0.1</v>
       </c>
-      <c r="N14" s="72"/>
+      <c r="N14" s="70"/>
       <c r="Y14"/>
       <c r="Z14"/>
       <c r="AA14"/>
@@ -4262,16 +4290,16 @@
         <v>8</v>
       </c>
       <c r="G15" s="28"/>
-      <c r="J15" s="58" t="s">
+      <c r="J15" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="K15" s="72">
+      <c r="K15" s="70">
         <v>325</v>
       </c>
-      <c r="M15" s="58" t="s">
+      <c r="M15" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="N15" s="72">
+      <c r="N15" s="70">
         <v>300</v>
       </c>
       <c r="Y15"/>
@@ -4303,17 +4331,17 @@
         <f>+J25</f>
         <v>249.47999999999996</v>
       </c>
-      <c r="G16" s="59"/>
-      <c r="J16" s="58" t="s">
+      <c r="G16" s="57"/>
+      <c r="J16" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="K16" s="72">
+      <c r="K16" s="70">
         <v>300</v>
       </c>
-      <c r="M16" s="58" t="s">
+      <c r="M16" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="N16" s="72">
+      <c r="N16" s="70">
         <v>275</v>
       </c>
       <c r="Y16"/>
@@ -4346,16 +4374,16 @@
         <v>1193.51</v>
       </c>
       <c r="G17" s="1"/>
-      <c r="J17" s="58" t="s">
+      <c r="J17" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="K17" s="72">
+      <c r="K17" s="70">
         <v>280</v>
       </c>
-      <c r="M17" s="58" t="s">
+      <c r="M17" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="N17" s="72">
+      <c r="N17" s="70">
         <v>250</v>
       </c>
       <c r="W17"/>
@@ -4370,22 +4398,22 @@
       <c r="AF17"/>
     </row>
     <row r="18" spans="1:33" ht="14.25" hidden="1" customHeight="1">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="43">
         <f t="shared" ref="C18:E18" si="3">C14+C16</f>
         <v>804.07652299185406</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="43">
         <f t="shared" si="3"/>
         <v>10.15209823840344</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="43">
         <f t="shared" si="3"/>
         <v>379.28137876974245</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="43">
         <f>SUM(C18:E18)</f>
         <v>1193.51</v>
       </c>
@@ -4466,16 +4494,16 @@
       <c r="AF20"/>
     </row>
     <row r="21" spans="1:33" ht="18.75" hidden="1" customHeight="1">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="43">
         <f>C18+C19</f>
         <v>837.76189316017496</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44">
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43">
         <f>SUM(C21:E21)</f>
         <v>837.76189316017496</v>
       </c>
@@ -4483,24 +4511,24 @@
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:33">
-      <c r="J22" s="73">
+      <c r="J22" s="71">
         <f>+F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K22" s="74">
+      <c r="K22" s="72">
         <f>J22*K13</f>
         <v>415.79999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="171" t="s">
+      <c r="B23" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="171"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
@@ -4511,11 +4539,11 @@
       </c>
     </row>
     <row r="25" spans="1:33">
-      <c r="J25" s="74">
+      <c r="J25" s="72">
         <f>K22*60%</f>
         <v>249.47999999999996</v>
       </c>
-      <c r="K25" s="74">
+      <c r="K25" s="72">
         <f>K22*40%</f>
         <v>166.32</v>
       </c>
@@ -4560,13 +4588,13 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:33">
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="117">
+      <c r="C28" s="115">
         <v>0</v>
       </c>
-      <c r="D28" s="118">
+      <c r="D28" s="116">
         <f>ROUND((MAX(D17:D18)+D26)*D27,10)</f>
         <v>0</v>
       </c>
@@ -4766,14 +4794,14 @@
       <c r="AF35"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="B36" s="173" t="s">
+      <c r="B36" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="173"/>
-      <c r="D36" s="173"/>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="173"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="167"/>
+      <c r="E36" s="167"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="167"/>
     </row>
     <row r="38" spans="1:32">
       <c r="C38" s="21">
@@ -4813,7 +4841,7 @@
         <f>+K25</f>
         <v>166.32</v>
       </c>
-      <c r="G39" s="59"/>
+      <c r="G39" s="57"/>
     </row>
     <row r="40" spans="1:32">
       <c r="C40" s="4"/>
@@ -4841,14 +4869,14 @@
       <c r="AF41"/>
     </row>
     <row r="42" spans="1:32" s="1" customFormat="1">
-      <c r="B42" s="71" t="s">
+      <c r="B42" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
     </row>
     <row r="44" spans="1:32">
       <c r="B44" s="25" t="s">
@@ -4942,42 +4970,42 @@
       <c r="AE47"/>
       <c r="AF47"/>
     </row>
-    <row r="48" spans="1:32" s="84" customFormat="1">
-      <c r="A48" s="80"/>
-      <c r="B48" s="82" t="s">
+    <row r="48" spans="1:32" s="82" customFormat="1">
+      <c r="A48" s="78"/>
+      <c r="B48" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="81">
+      <c r="C48" s="79">
         <f>C47*$K$32</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="D48" s="81">
+      <c r="D48" s="79">
         <f t="shared" ref="D48:E48" si="8">D47*$K$32</f>
         <v>51.458155426726904</v>
       </c>
-      <c r="E48" s="81">
+      <c r="E48" s="79">
         <f t="shared" si="8"/>
         <v>38.449431203033804</v>
       </c>
-      <c r="F48" s="83"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="80"/>
-      <c r="M48" s="80"/>
-      <c r="N48" s="80"/>
-      <c r="O48" s="80"/>
-      <c r="P48" s="80"/>
-      <c r="Q48" s="80"/>
-      <c r="R48" s="80"/>
-      <c r="S48" s="80"/>
-      <c r="T48" s="80"/>
-      <c r="U48" s="80"/>
-      <c r="V48" s="80"/>
-      <c r="W48" s="80"/>
-      <c r="X48" s="80"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="78"/>
+      <c r="K48" s="78"/>
+      <c r="L48" s="78"/>
+      <c r="M48" s="78"/>
+      <c r="N48" s="78"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="78"/>
+      <c r="Q48" s="78"/>
+      <c r="R48" s="78"/>
+      <c r="S48" s="78"/>
+      <c r="T48" s="78"/>
+      <c r="U48" s="78"/>
+      <c r="V48" s="78"/>
+      <c r="W48" s="78"/>
+      <c r="X48" s="78"/>
     </row>
     <row r="49" spans="25:32">
       <c r="Y49"/>

--- a/public/assets/templates/Boleta_Template.xlsx
+++ b/public/assets/templates/Boleta_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRO17\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Proyectos\Probusiness\intranet_back\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C427EF-525D-4329-9861-01649CA78B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259B0165-3802-4A77-BCA9-2B2EBCEB6A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-840" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$114</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -282,9 +282,6 @@
     <t>coordinador  logístico la tarifa.</t>
   </si>
   <si>
-    <t>8. Las cargas mayores a 200 kg x bulto tendrán un costo adicional por manipuleo, consultar con el</t>
-  </si>
-  <si>
     <t>10. Si aduana realiza un ajuste de valor a su importación, el cliente tendrá que pagar la diferencia.</t>
   </si>
   <si>
@@ -625,6 +622,9 @@
   </si>
   <si>
     <t>QTY PROVEEDORES</t>
+  </si>
+  <si>
+    <t>8. Las cargas mayores a 100 kg x bulto tendrán un costo adicional por manipuleo, consultar con el</t>
   </si>
 </sst>
 </file>
@@ -1493,19 +1493,87 @@
     <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="39" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1515,15 +1583,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1536,55 +1595,18 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="29" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="29" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1596,28 +1618,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="171" fontId="29" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="29" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="39" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2057,72 +2057,72 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AC111"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="0.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="0.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="37.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.7109375" style="1"/>
+    <col min="1" max="1" width="7.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="0.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="0.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="A1" s="146"/>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
       <c r="B2" s="126"/>
       <c r="C2" s="126"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-    </row>
-    <row r="3" spans="1:12" ht="26.25">
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+    </row>
+    <row r="3" spans="1:12" ht="25.8">
       <c r="B3" s="126"/>
       <c r="C3" s="126"/>
-      <c r="E3" s="150" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-    </row>
-    <row r="4" spans="1:12" ht="26.25">
+      <c r="E3" s="135" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.8">
       <c r="B4" s="126"/>
       <c r="C4" s="126"/>
-      <c r="E4" s="151" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="151"/>
+      <c r="E4" s="136" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
       <c r="K4" s="34"/>
     </row>
     <row r="5" spans="1:12">
@@ -2142,11 +2142,11 @@
       <c r="A7" s="126"/>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
-      <c r="E7" s="158" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="158"/>
-      <c r="G7" s="158"/>
+      <c r="E7" s="127" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
       <c r="I7" s="126"/>
       <c r="J7" s="126"/>
       <c r="K7" s="126"/>
@@ -2154,56 +2154,56 @@
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="85"/>
       <c r="E8" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="162" t="s">
+      <c r="F8" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="163"/>
+      <c r="G8" s="133"/>
       <c r="H8" s="84"/>
       <c r="I8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="154">
+      <c r="J8" s="146">
         <f>+'2'!F7</f>
         <v>8</v>
       </c>
-      <c r="K8" s="154"/>
-      <c r="L8" s="154"/>
+      <c r="K8" s="146"/>
+      <c r="L8" s="146"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" s="85"/>
       <c r="E9" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="159">
+        <v>100</v>
+      </c>
+      <c r="F9" s="128">
         <f ca="1">+TODAY()</f>
-        <v>46142</v>
-      </c>
-      <c r="G9" s="160"/>
+        <v>46184</v>
+      </c>
+      <c r="G9" s="129"/>
       <c r="H9" s="84"/>
       <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="157">
+      <c r="J9" s="125">
         <f>+'2'!F8</f>
         <v>116</v>
       </c>
-      <c r="K9" s="157"/>
-      <c r="L9" s="157"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="30" t="s">
@@ -2216,19 +2216,19 @@
       <c r="E10" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="146" t="s">
+      <c r="F10" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="161"/>
+      <c r="G10" s="131"/>
       <c r="H10" s="84"/>
       <c r="I10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J10" s="155">
+        <v>134</v>
+      </c>
+      <c r="J10" s="147">
         <v>0</v>
       </c>
-      <c r="K10" s="155"/>
-      <c r="L10" s="155"/>
+      <c r="K10" s="147"/>
+      <c r="L10" s="147"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="30" t="s">
@@ -2241,63 +2241,63 @@
       <c r="E11" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="147"/>
-      <c r="G11" s="156"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="150"/>
       <c r="H11" s="84"/>
       <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="158">
         <f>+'2'!F9</f>
         <v>1.1879999999999999</v>
       </c>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="158"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="170" t="s">
+      <c r="B13" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="170"/>
-      <c r="D13" s="170"/>
-      <c r="E13" s="170"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="170"/>
-      <c r="H13" s="170"/>
-      <c r="I13" s="170"/>
-      <c r="J13" s="170"/>
-      <c r="K13" s="171" t="s">
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="124" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="171" t="s">
+      <c r="L13" s="124" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="124" t="s">
+      <c r="B14" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="152"/>
+      <c r="J14" s="152"/>
       <c r="K14" s="36">
         <f>'2'!F13</f>
         <v>944.03</v>
@@ -2308,34 +2308,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="90"/>
-      <c r="B15" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
+      <c r="B15" s="160" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="160"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="160"/>
       <c r="K15" s="88"/>
       <c r="L15" s="89" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="148" t="s">
+      <c r="B16" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="154"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="154"/>
       <c r="K16" s="37">
         <f>'2'!F16+'2'!F19</f>
         <v>299.47999999999996</v>
@@ -2345,17 +2345,17 @@
       </c>
     </row>
     <row r="17" spans="1:29">
-      <c r="B17" s="143" t="s">
+      <c r="B17" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="143"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
       <c r="K17" s="36">
         <f>SUM(K14:K16)</f>
         <v>1243.51</v>
@@ -2378,13 +2378,13 @@
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="B19" s="131" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
+      <c r="B19" s="159" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
       <c r="G19" s="122"/>
       <c r="H19" s="122"/>
       <c r="I19" s="122"/>
@@ -2399,16 +2399,16 @@
       </c>
     </row>
     <row r="20" spans="1:29">
-      <c r="B20" s="127" t="s">
+      <c r="B20" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="155"/>
+      <c r="G20" s="155"/>
+      <c r="H20" s="155"/>
+      <c r="I20" s="155"/>
       <c r="J20" s="45">
         <f>MAX('2'!C26:E26)</f>
         <v>0.04</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="21" spans="1:29">
       <c r="B21" s="29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
@@ -2443,16 +2443,16 @@
       </c>
     </row>
     <row r="22" spans="1:29">
-      <c r="B22" s="127" t="s">
+      <c r="B22" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="155"/>
       <c r="J22" s="45">
         <v>0.16</v>
       </c>
@@ -2465,16 +2465,16 @@
       </c>
     </row>
     <row r="23" spans="1:29">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="147"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="147"/>
-      <c r="I23" s="147"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="149"/>
       <c r="J23" s="45">
         <v>0.02</v>
       </c>
@@ -2487,16 +2487,16 @@
       </c>
     </row>
     <row r="24" spans="1:29">
-      <c r="B24" s="143" t="s">
+      <c r="B24" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="143"/>
-      <c r="D24" s="143"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="143"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="153"/>
       <c r="J24" s="73"/>
       <c r="K24" s="74">
         <f>SUM(K20:K23)</f>
@@ -2507,31 +2507,31 @@
       </c>
     </row>
     <row r="25" spans="1:29">
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
+      <c r="B25" s="155"/>
+      <c r="C25" s="155"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="155"/>
+      <c r="I25" s="155"/>
       <c r="J25" s="2"/>
       <c r="K25" s="32"/>
       <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="147"/>
-      <c r="G26" s="147"/>
-      <c r="H26" s="147"/>
-      <c r="I26" s="147"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="149"/>
       <c r="J26" s="46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K26" s="37">
         <f>'2'!F31</f>
@@ -2542,16 +2542,16 @@
       </c>
     </row>
     <row r="27" spans="1:29">
-      <c r="B27" s="143" t="s">
+      <c r="B27" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="143"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="143"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="143"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
       <c r="K27" s="36">
         <f>K24+K26</f>
         <v>316.1151070046609</v>
@@ -2578,14 +2578,14 @@
       <c r="AC27"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B28" s="146"/>
-      <c r="C28" s="146"/>
-      <c r="D28" s="146"/>
-      <c r="E28" s="146"/>
-      <c r="F28" s="146"/>
-      <c r="G28" s="146"/>
-      <c r="H28" s="146"/>
-      <c r="I28" s="146"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
@@ -2606,13 +2606,13 @@
     </row>
     <row r="29" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="91"/>
-      <c r="B29" s="137" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
+      <c r="B29" s="162" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="163"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="163"/>
       <c r="G29" s="92"/>
       <c r="H29" s="93"/>
       <c r="I29" s="93"/>
@@ -2638,7 +2638,7 @@
     <row r="30" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="91"/>
       <c r="B30" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" s="95"/>
       <c r="D30" s="95"/>
@@ -2648,7 +2648,7 @@
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="96" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K30" s="97"/>
       <c r="L30" s="96" t="s">
@@ -2667,7 +2667,7 @@
     <row r="31" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A31" s="91"/>
       <c r="B31" s="98" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" s="95"/>
       <c r="D31" s="95"/>
@@ -2677,7 +2677,7 @@
       <c r="H31" s="95"/>
       <c r="I31" s="95"/>
       <c r="J31" s="96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K31" s="97"/>
       <c r="L31" s="96" t="s">
@@ -2701,7 +2701,7 @@
     <row r="32" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="91"/>
       <c r="B32" s="99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" s="100"/>
       <c r="D32" s="100"/>
@@ -2711,7 +2711,7 @@
       <c r="H32" s="100"/>
       <c r="I32" s="100"/>
       <c r="J32" s="101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K32" s="102"/>
       <c r="L32" s="103" t="s">
@@ -2782,7 +2782,7 @@
     <row r="35" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="91"/>
       <c r="B35" s="98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C35" s="95"/>
       <c r="D35" s="95"/>
@@ -2811,7 +2811,7 @@
     <row r="36" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="91"/>
       <c r="B36" s="99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C36" s="100"/>
       <c r="D36" s="100"/>
@@ -2839,16 +2839,16 @@
     </row>
     <row r="37" spans="1:29" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="91"/>
-      <c r="B37" s="139" t="s">
+      <c r="B37" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
+      <c r="C37" s="165"/>
+      <c r="D37" s="165"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="165"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="165"/>
+      <c r="I37" s="165"/>
       <c r="J37" s="108"/>
       <c r="K37" s="118">
         <f>SUM(K33+K35)-K36</f>
@@ -2874,18 +2874,18 @@
       <c r="L38" s="119"/>
       <c r="M38" s="108"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75">
-      <c r="B39" s="144" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="144"/>
-      <c r="D39" s="144"/>
-      <c r="E39" s="144"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="144"/>
-      <c r="J39" s="144"/>
+    <row r="39" spans="1:29" ht="15.6">
+      <c r="B39" s="168" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="168"/>
+      <c r="D39" s="168"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="168"/>
+      <c r="G39" s="168"/>
+      <c r="H39" s="168"/>
+      <c r="I39" s="168"/>
+      <c r="J39" s="168"/>
       <c r="K39" s="58" t="s">
         <v>34</v>
       </c>
@@ -2911,17 +2911,17 @@
       <c r="AC39"/>
     </row>
     <row r="40" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B40" s="127" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="127"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="127"/>
+      <c r="B40" s="155" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="155"/>
+      <c r="D40" s="155"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="155"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
       <c r="K40" s="36">
         <f>K37</f>
         <v>0</v>
@@ -2948,17 +2948,17 @@
       <c r="AC40"/>
     </row>
     <row r="41" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B41" s="127" t="s">
+      <c r="B41" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="127"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
+      <c r="C41" s="155"/>
+      <c r="D41" s="155"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
       <c r="K41" s="36">
         <f>K27</f>
         <v>316.1151070046609</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="42" spans="1:29">
       <c r="B42" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K42" s="36">
         <v>0</v>
@@ -2979,17 +2979,17 @@
       </c>
     </row>
     <row r="43" spans="1:29">
-      <c r="B43" s="141" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="141"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="141"/>
-      <c r="I43" s="141"/>
-      <c r="J43" s="141"/>
+      <c r="B43" s="166" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="166"/>
+      <c r="D43" s="166"/>
+      <c r="E43" s="166"/>
+      <c r="F43" s="166"/>
+      <c r="G43" s="166"/>
+      <c r="H43" s="166"/>
+      <c r="I43" s="166"/>
+      <c r="J43" s="166"/>
       <c r="K43" s="36">
         <v>0</v>
       </c>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="44" spans="1:29">
       <c r="B44" s="121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" s="121"/>
       <c r="D44" s="121"/>
@@ -3017,17 +3017,17 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B45" s="143" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="143"/>
-      <c r="D45" s="143"/>
-      <c r="E45" s="143"/>
-      <c r="F45" s="143"/>
-      <c r="G45" s="143"/>
-      <c r="H45" s="143"/>
-      <c r="I45" s="143"/>
-      <c r="J45" s="143"/>
+      <c r="B45" s="153" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="153"/>
+      <c r="D45" s="153"/>
+      <c r="E45" s="153"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="153"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="153"/>
+      <c r="J45" s="153"/>
       <c r="K45" s="74">
         <f>SUM(K40:K44)</f>
         <v>316.1151070046609</v>
@@ -3037,79 +3037,79 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B46" s="142"/>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="142"/>
-      <c r="I46" s="142"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
+      <c r="B46" s="167"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
+      <c r="E46" s="167"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
     </row>
     <row r="47" spans="1:29" ht="15.75" customHeight="1">
-      <c r="B47" s="172" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="173"/>
-      <c r="D47" s="173"/>
-      <c r="E47" s="173"/>
-      <c r="F47" s="173"/>
-      <c r="G47" s="173"/>
-      <c r="H47" s="173"/>
-      <c r="I47" s="173"/>
-      <c r="J47" s="173"/>
-      <c r="K47" s="173"/>
-      <c r="L47" s="174"/>
+      <c r="B47" s="143" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="144"/>
+      <c r="D47" s="144"/>
+      <c r="E47" s="144"/>
+      <c r="F47" s="144"/>
+      <c r="G47" s="144"/>
+      <c r="H47" s="144"/>
+      <c r="I47" s="144"/>
+      <c r="J47" s="144"/>
+      <c r="K47" s="144"/>
+      <c r="L47" s="145"/>
     </row>
     <row r="48" spans="1:29" ht="15.75" customHeight="1">
       <c r="B48" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="133" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="134"/>
-      <c r="E48" s="135"/>
+      <c r="C48" s="138" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="139"/>
+      <c r="E48" s="140"/>
       <c r="F48" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G48" s="133" t="s">
-        <v>80</v>
-      </c>
-      <c r="H48" s="135"/>
+      <c r="G48" s="138" t="s">
+        <v>79</v>
+      </c>
+      <c r="H48" s="140"/>
       <c r="I48" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J48" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="168" t="s">
-        <v>78</v>
-      </c>
-      <c r="L48" s="169"/>
+      <c r="K48" s="169" t="s">
+        <v>77</v>
+      </c>
+      <c r="L48" s="170"/>
     </row>
     <row r="49" spans="2:13">
       <c r="B49" s="44">
         <v>1</v>
       </c>
-      <c r="C49" s="133" t="str">
+      <c r="C49" s="138" t="str">
         <f>+'2'!$C$6</f>
         <v xml:space="preserve">Kids Car Seat Belt Pillow </v>
       </c>
-      <c r="D49" s="134"/>
-      <c r="E49" s="135"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="140"/>
       <c r="F49" s="7">
         <f>+'2'!$C$46</f>
         <v>100</v>
       </c>
-      <c r="G49" s="152">
+      <c r="G49" s="141">
         <f>+'2'!$C$10</f>
         <v>6.36</v>
       </c>
-      <c r="H49" s="153"/>
+      <c r="H49" s="142"/>
       <c r="I49" s="53">
         <f>+'2'!$C$47</f>
         <v>11.424505892807643</v>
@@ -3118,13 +3118,13 @@
         <f t="shared" ref="J49" si="0">+F49*I49</f>
         <v>1142.4505892807642</v>
       </c>
-      <c r="K49" s="175">
+      <c r="K49" s="137">
         <f t="shared" ref="K49" si="1">I49*3.7</f>
         <v>42.270671803388282</v>
       </c>
-      <c r="L49" s="175"/>
-    </row>
-    <row r="50" spans="2:13" ht="15.75">
+      <c r="L49" s="137"/>
+    </row>
+    <row r="50" spans="2:13" ht="15.6">
       <c r="B50" s="47" t="s">
         <v>8</v>
       </c>
@@ -3144,7 +3144,7 @@
       <c r="K50" s="75"/>
       <c r="L50" s="76"/>
     </row>
-    <row r="51" spans="2:13" ht="15.75">
+    <row r="51" spans="2:13" ht="15.6">
       <c r="B51" s="47"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -3169,7 +3169,7 @@
       <c r="K52" s="77"/>
       <c r="L52" s="78"/>
     </row>
-    <row r="53" spans="2:13" ht="18.75">
+    <row r="53" spans="2:13" ht="18">
       <c r="B53" s="59" t="s">
         <v>53</v>
       </c>
@@ -3183,80 +3183,80 @@
       <c r="J53" s="29"/>
       <c r="K53" s="29"/>
     </row>
-    <row r="54" spans="2:13" ht="18.75">
-      <c r="B54" s="128" t="s">
+    <row r="54" spans="2:13" ht="18">
+      <c r="B54" s="148" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="148"/>
+      <c r="D54" s="148"/>
+      <c r="E54" s="148"/>
+      <c r="F54" s="148"/>
+      <c r="G54" s="148"/>
+      <c r="H54" s="148"/>
+      <c r="I54" s="148"/>
+      <c r="J54" s="148"/>
+      <c r="K54" s="148"/>
+      <c r="L54" s="148"/>
+    </row>
+    <row r="55" spans="2:13" ht="18">
+      <c r="B55" s="148" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="128"/>
-      <c r="D54" s="128"/>
-      <c r="E54" s="128"/>
-      <c r="F54" s="128"/>
-      <c r="G54" s="128"/>
-      <c r="H54" s="128"/>
-      <c r="I54" s="128"/>
-      <c r="J54" s="128"/>
-      <c r="K54" s="128"/>
-      <c r="L54" s="128"/>
-    </row>
-    <row r="55" spans="2:13" ht="18.75">
-      <c r="B55" s="128" t="s">
+      <c r="C55" s="148"/>
+      <c r="D55" s="148"/>
+      <c r="E55" s="148"/>
+      <c r="F55" s="148"/>
+      <c r="G55" s="148"/>
+      <c r="H55" s="148"/>
+      <c r="I55" s="148"/>
+      <c r="J55" s="148"/>
+      <c r="K55" s="148"/>
+      <c r="L55" s="148"/>
+    </row>
+    <row r="56" spans="2:13" ht="18">
+      <c r="B56" s="148" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="128"/>
-      <c r="D55" s="128"/>
-      <c r="E55" s="128"/>
-      <c r="F55" s="128"/>
-      <c r="G55" s="128"/>
-      <c r="H55" s="128"/>
-      <c r="I55" s="128"/>
-      <c r="J55" s="128"/>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
-    </row>
-    <row r="56" spans="2:13" ht="18.75">
-      <c r="B56" s="128" t="s">
+      <c r="C56" s="148"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="148"/>
+      <c r="F56" s="148"/>
+      <c r="G56" s="148"/>
+      <c r="H56" s="148"/>
+      <c r="I56" s="148"/>
+      <c r="J56" s="148"/>
+      <c r="K56" s="148"/>
+      <c r="L56" s="148"/>
+    </row>
+    <row r="57" spans="2:13" ht="18">
+      <c r="B57" s="148" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="128"/>
-      <c r="D56" s="128"/>
-      <c r="E56" s="128"/>
-      <c r="F56" s="128"/>
-      <c r="G56" s="128"/>
-      <c r="H56" s="128"/>
-      <c r="I56" s="128"/>
-      <c r="J56" s="128"/>
-      <c r="K56" s="128"/>
-      <c r="L56" s="128"/>
-    </row>
-    <row r="57" spans="2:13" ht="18.75">
-      <c r="B57" s="128" t="s">
+      <c r="C57" s="148"/>
+      <c r="D57" s="148"/>
+      <c r="E57" s="148"/>
+      <c r="F57" s="148"/>
+      <c r="G57" s="148"/>
+      <c r="H57" s="148"/>
+      <c r="I57" s="148"/>
+      <c r="J57" s="148"/>
+      <c r="K57" s="148"/>
+      <c r="L57" s="148"/>
+    </row>
+    <row r="58" spans="2:13" ht="18">
+      <c r="B58" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="128"/>
-      <c r="D57" s="128"/>
-      <c r="E57" s="128"/>
-      <c r="F57" s="128"/>
-      <c r="G57" s="128"/>
-      <c r="H57" s="128"/>
-      <c r="I57" s="128"/>
-      <c r="J57" s="128"/>
-      <c r="K57" s="128"/>
-      <c r="L57" s="128"/>
-    </row>
-    <row r="58" spans="2:13" ht="18.75">
-      <c r="B58" s="128" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="128"/>
-      <c r="D58" s="128"/>
-      <c r="E58" s="128"/>
-      <c r="F58" s="128"/>
-      <c r="G58" s="128"/>
-      <c r="H58" s="128"/>
-      <c r="I58" s="128"/>
-      <c r="J58" s="128"/>
-      <c r="K58" s="128"/>
-      <c r="L58" s="128"/>
+      <c r="C58" s="148"/>
+      <c r="D58" s="148"/>
+      <c r="E58" s="148"/>
+      <c r="F58" s="148"/>
+      <c r="G58" s="148"/>
+      <c r="H58" s="148"/>
+      <c r="I58" s="148"/>
+      <c r="J58" s="148"/>
+      <c r="K58" s="148"/>
+      <c r="L58" s="148"/>
     </row>
     <row r="59" spans="2:13">
       <c r="B59" s="29"/>
@@ -3284,33 +3284,33 @@
       <c r="L60" s="126"/>
       <c r="M60" s="126"/>
     </row>
-    <row r="61" spans="2:13" ht="31.9" customHeight="1">
+    <row r="61" spans="2:13" ht="31.95" customHeight="1">
       <c r="B61" s="126"/>
       <c r="C61" s="126"/>
-      <c r="D61" s="136" t="s">
-        <v>119</v>
-      </c>
-      <c r="E61" s="136"/>
-      <c r="F61" s="136"/>
-      <c r="G61" s="136"/>
-      <c r="H61" s="136"/>
-      <c r="I61" s="136"/>
-      <c r="J61" s="136"/>
-      <c r="K61" s="136"/>
-      <c r="L61" s="136"/>
-      <c r="M61" s="136"/>
+      <c r="D61" s="161" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="161"/>
+      <c r="F61" s="161"/>
+      <c r="G61" s="161"/>
+      <c r="H61" s="161"/>
+      <c r="I61" s="161"/>
+      <c r="J61" s="161"/>
+      <c r="K61" s="161"/>
+      <c r="L61" s="161"/>
+      <c r="M61" s="161"/>
     </row>
     <row r="62" spans="2:13" ht="21" customHeight="1">
       <c r="B62" s="126"/>
       <c r="C62" s="126"/>
-      <c r="D62" s="149" t="s">
-        <v>120</v>
-      </c>
-      <c r="E62" s="149"/>
-      <c r="F62" s="149"/>
-      <c r="G62" s="149"/>
-      <c r="H62" s="149"/>
-      <c r="I62" s="149"/>
+      <c r="D62" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="134"/>
+      <c r="F62" s="134"/>
+      <c r="G62" s="134"/>
+      <c r="H62" s="134"/>
+      <c r="I62" s="134"/>
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="126"/>
@@ -3321,442 +3321,442 @@
       <c r="C64" s="126"/>
     </row>
     <row r="65" spans="2:12" ht="21">
-      <c r="B65" s="129" t="s">
+      <c r="B65" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="129"/>
-      <c r="D65" s="129"/>
-      <c r="E65" s="129"/>
-      <c r="F65" s="129"/>
-      <c r="G65" s="129"/>
-      <c r="H65" s="129"/>
-      <c r="I65" s="129"/>
-      <c r="J65" s="129"/>
-      <c r="K65" s="129"/>
-      <c r="L65" s="129"/>
+      <c r="C65" s="171"/>
+      <c r="D65" s="171"/>
+      <c r="E65" s="171"/>
+      <c r="F65" s="171"/>
+      <c r="G65" s="171"/>
+      <c r="H65" s="171"/>
+      <c r="I65" s="171"/>
+      <c r="J65" s="171"/>
+      <c r="K65" s="171"/>
+      <c r="L65" s="171"/>
     </row>
     <row r="67" spans="2:12">
-      <c r="B67" s="125" t="s">
+      <c r="B67" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="125"/>
-      <c r="D67" s="125"/>
-      <c r="E67" s="125"/>
-      <c r="F67" s="125"/>
-      <c r="G67" s="125"/>
-      <c r="H67" s="125"/>
-      <c r="I67" s="125"/>
-      <c r="J67" s="125"/>
-      <c r="K67" s="125"/>
-      <c r="L67" s="125"/>
+      <c r="C67" s="156"/>
+      <c r="D67" s="156"/>
+      <c r="E67" s="156"/>
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="156"/>
+      <c r="K67" s="156"/>
+      <c r="L67" s="156"/>
     </row>
     <row r="68" spans="2:12">
-      <c r="B68" s="125" t="s">
+      <c r="B68" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="125"/>
-      <c r="D68" s="125"/>
-      <c r="E68" s="125"/>
-      <c r="F68" s="125"/>
-      <c r="G68" s="125"/>
-      <c r="H68" s="125"/>
-      <c r="I68" s="125"/>
-      <c r="J68" s="125"/>
-      <c r="K68" s="125"/>
-      <c r="L68" s="125"/>
+      <c r="C68" s="156"/>
+      <c r="D68" s="156"/>
+      <c r="E68" s="156"/>
+      <c r="F68" s="156"/>
+      <c r="G68" s="156"/>
+      <c r="H68" s="156"/>
+      <c r="I68" s="156"/>
+      <c r="J68" s="156"/>
+      <c r="K68" s="156"/>
+      <c r="L68" s="156"/>
     </row>
     <row r="69" spans="2:12">
-      <c r="B69" s="127" t="s">
+      <c r="B69" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="127"/>
-      <c r="D69" s="127"/>
-      <c r="E69" s="127"/>
-      <c r="F69" s="127"/>
-      <c r="G69" s="127"/>
-      <c r="H69" s="127"/>
-      <c r="I69" s="127"/>
-      <c r="J69" s="127"/>
-      <c r="K69" s="127"/>
-      <c r="L69" s="127"/>
+      <c r="C69" s="155"/>
+      <c r="D69" s="155"/>
+      <c r="E69" s="155"/>
+      <c r="F69" s="155"/>
+      <c r="G69" s="155"/>
+      <c r="H69" s="155"/>
+      <c r="I69" s="155"/>
+      <c r="J69" s="155"/>
+      <c r="K69" s="155"/>
+      <c r="L69" s="155"/>
     </row>
     <row r="70" spans="2:12">
-      <c r="B70" s="125" t="s">
+      <c r="B70" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="125"/>
-      <c r="D70" s="125"/>
-      <c r="E70" s="125"/>
-      <c r="F70" s="125"/>
-      <c r="G70" s="125"/>
-      <c r="H70" s="125"/>
-      <c r="I70" s="125"/>
-      <c r="J70" s="125"/>
-      <c r="K70" s="125"/>
-      <c r="L70" s="125"/>
+      <c r="C70" s="156"/>
+      <c r="D70" s="156"/>
+      <c r="E70" s="156"/>
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="156"/>
+      <c r="I70" s="156"/>
+      <c r="J70" s="156"/>
+      <c r="K70" s="156"/>
+      <c r="L70" s="156"/>
     </row>
     <row r="71" spans="2:12">
-      <c r="B71" s="125" t="s">
+      <c r="B71" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="C71" s="125"/>
-      <c r="D71" s="125"/>
-      <c r="E71" s="125"/>
-      <c r="F71" s="125"/>
-      <c r="G71" s="125"/>
-      <c r="H71" s="125"/>
-      <c r="I71" s="125"/>
-      <c r="J71" s="125"/>
-      <c r="K71" s="125"/>
-      <c r="L71" s="125"/>
+      <c r="C71" s="156"/>
+      <c r="D71" s="156"/>
+      <c r="E71" s="156"/>
+      <c r="F71" s="156"/>
+      <c r="G71" s="156"/>
+      <c r="H71" s="156"/>
+      <c r="I71" s="156"/>
+      <c r="J71" s="156"/>
+      <c r="K71" s="156"/>
+      <c r="L71" s="156"/>
     </row>
     <row r="72" spans="2:12">
-      <c r="B72" s="127" t="s">
+      <c r="B72" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="127"/>
-      <c r="D72" s="127"/>
-      <c r="E72" s="127"/>
-      <c r="F72" s="127"/>
-      <c r="G72" s="127"/>
-      <c r="H72" s="127"/>
-      <c r="I72" s="127"/>
-      <c r="J72" s="127"/>
-      <c r="K72" s="127"/>
-      <c r="L72" s="127"/>
+      <c r="C72" s="155"/>
+      <c r="D72" s="155"/>
+      <c r="E72" s="155"/>
+      <c r="F72" s="155"/>
+      <c r="G72" s="155"/>
+      <c r="H72" s="155"/>
+      <c r="I72" s="155"/>
+      <c r="J72" s="155"/>
+      <c r="K72" s="155"/>
+      <c r="L72" s="155"/>
     </row>
     <row r="73" spans="2:12">
-      <c r="B73" s="125" t="s">
+      <c r="B73" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="125"/>
-      <c r="D73" s="125"/>
-      <c r="E73" s="125"/>
-      <c r="F73" s="125"/>
-      <c r="G73" s="125"/>
-      <c r="H73" s="125"/>
-      <c r="I73" s="125"/>
-      <c r="J73" s="125"/>
-      <c r="K73" s="125"/>
-      <c r="L73" s="125"/>
+      <c r="C73" s="156"/>
+      <c r="D73" s="156"/>
+      <c r="E73" s="156"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="156"/>
+      <c r="H73" s="156"/>
+      <c r="I73" s="156"/>
+      <c r="J73" s="156"/>
+      <c r="K73" s="156"/>
+      <c r="L73" s="156"/>
     </row>
     <row r="74" spans="2:12">
-      <c r="B74" s="125" t="s">
+      <c r="B74" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="125"/>
-      <c r="D74" s="125"/>
-      <c r="E74" s="125"/>
-      <c r="F74" s="125"/>
-      <c r="G74" s="125"/>
-      <c r="H74" s="125"/>
-      <c r="I74" s="125"/>
-      <c r="J74" s="125"/>
-      <c r="K74" s="125"/>
-      <c r="L74" s="125"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="156"/>
+      <c r="G74" s="156"/>
+      <c r="H74" s="156"/>
+      <c r="I74" s="156"/>
+      <c r="J74" s="156"/>
+      <c r="K74" s="156"/>
+      <c r="L74" s="156"/>
     </row>
     <row r="75" spans="2:12">
-      <c r="B75" s="125" t="s">
+      <c r="B75" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="C75" s="125"/>
-      <c r="D75" s="125"/>
-      <c r="E75" s="125"/>
-      <c r="F75" s="125"/>
-      <c r="G75" s="125"/>
-      <c r="H75" s="125"/>
-      <c r="I75" s="125"/>
-      <c r="J75" s="125"/>
-      <c r="K75" s="125"/>
-      <c r="L75" s="125"/>
+      <c r="C75" s="156"/>
+      <c r="D75" s="156"/>
+      <c r="E75" s="156"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
+      <c r="H75" s="156"/>
+      <c r="I75" s="156"/>
+      <c r="J75" s="156"/>
+      <c r="K75" s="156"/>
+      <c r="L75" s="156"/>
     </row>
     <row r="76" spans="2:12">
-      <c r="B76" s="125" t="s">
+      <c r="B76" s="156" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="125"/>
-      <c r="D76" s="125"/>
-      <c r="E76" s="125"/>
-      <c r="F76" s="125"/>
-      <c r="G76" s="125"/>
-      <c r="H76" s="125"/>
-      <c r="I76" s="125"/>
-      <c r="J76" s="125"/>
-      <c r="K76" s="125"/>
-      <c r="L76" s="125"/>
+      <c r="C76" s="156"/>
+      <c r="D76" s="156"/>
+      <c r="E76" s="156"/>
+      <c r="F76" s="156"/>
+      <c r="G76" s="156"/>
+      <c r="H76" s="156"/>
+      <c r="I76" s="156"/>
+      <c r="J76" s="156"/>
+      <c r="K76" s="156"/>
+      <c r="L76" s="156"/>
     </row>
     <row r="77" spans="2:12">
-      <c r="B77" s="125" t="s">
+      <c r="B77" s="156" t="s">
+        <v>135</v>
+      </c>
+      <c r="C77" s="156"/>
+      <c r="D77" s="156"/>
+      <c r="E77" s="156"/>
+      <c r="F77" s="156"/>
+      <c r="G77" s="156"/>
+      <c r="H77" s="156"/>
+      <c r="I77" s="156"/>
+      <c r="J77" s="156"/>
+      <c r="K77" s="156"/>
+      <c r="L77" s="156"/>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78" s="156" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" s="156"/>
+      <c r="D78" s="156"/>
+      <c r="E78" s="156"/>
+      <c r="F78" s="156"/>
+      <c r="G78" s="156"/>
+      <c r="H78" s="156"/>
+      <c r="I78" s="156"/>
+      <c r="J78" s="156"/>
+      <c r="K78" s="156"/>
+      <c r="L78" s="156"/>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79" s="156" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="156"/>
+      <c r="D79" s="156"/>
+      <c r="E79" s="156"/>
+      <c r="F79" s="156"/>
+      <c r="G79" s="156"/>
+      <c r="H79" s="156"/>
+      <c r="I79" s="156"/>
+      <c r="J79" s="156"/>
+      <c r="K79" s="156"/>
+      <c r="L79" s="156"/>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="B80" s="156" t="s">
         <v>62</v>
       </c>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="125"/>
-      <c r="F77" s="125"/>
-      <c r="G77" s="125"/>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="125"/>
-      <c r="K77" s="125"/>
-      <c r="L77" s="125"/>
-    </row>
-    <row r="78" spans="2:12">
-      <c r="B78" s="125" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" s="125"/>
-      <c r="D78" s="125"/>
-      <c r="E78" s="125"/>
-      <c r="F78" s="125"/>
-      <c r="G78" s="125"/>
-      <c r="H78" s="125"/>
-      <c r="I78" s="125"/>
-      <c r="J78" s="125"/>
-      <c r="K78" s="125"/>
-      <c r="L78" s="125"/>
-    </row>
-    <row r="79" spans="2:12">
-      <c r="B79" s="125" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="125"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="125"/>
-      <c r="F79" s="125"/>
-      <c r="G79" s="125"/>
-      <c r="H79" s="125"/>
-      <c r="I79" s="125"/>
-      <c r="J79" s="125"/>
-      <c r="K79" s="125"/>
-      <c r="L79" s="125"/>
-    </row>
-    <row r="80" spans="2:12">
-      <c r="B80" s="125" t="s">
+      <c r="C80" s="156"/>
+      <c r="D80" s="156"/>
+      <c r="E80" s="156"/>
+      <c r="F80" s="156"/>
+      <c r="G80" s="156"/>
+      <c r="H80" s="156"/>
+      <c r="I80" s="156"/>
+      <c r="J80" s="156"/>
+      <c r="K80" s="156"/>
+      <c r="L80" s="156"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="B81" s="156" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="125"/>
-      <c r="D80" s="125"/>
-      <c r="E80" s="125"/>
-      <c r="F80" s="125"/>
-      <c r="G80" s="125"/>
-      <c r="H80" s="125"/>
-      <c r="I80" s="125"/>
-      <c r="J80" s="125"/>
-      <c r="K80" s="125"/>
-      <c r="L80" s="125"/>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="B81" s="125" t="s">
+      <c r="C81" s="156"/>
+      <c r="D81" s="156"/>
+      <c r="E81" s="156"/>
+      <c r="F81" s="156"/>
+      <c r="G81" s="156"/>
+      <c r="H81" s="156"/>
+      <c r="I81" s="156"/>
+      <c r="J81" s="156"/>
+      <c r="K81" s="156"/>
+      <c r="L81" s="156"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="B82" s="156" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="125"/>
-      <c r="D81" s="125"/>
-      <c r="E81" s="125"/>
-      <c r="F81" s="125"/>
-      <c r="G81" s="125"/>
-      <c r="H81" s="125"/>
-      <c r="I81" s="125"/>
-      <c r="J81" s="125"/>
-      <c r="K81" s="125"/>
-      <c r="L81" s="125"/>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="B82" s="125" t="s">
+      <c r="C82" s="156"/>
+      <c r="D82" s="156"/>
+      <c r="E82" s="156"/>
+      <c r="F82" s="156"/>
+      <c r="G82" s="156"/>
+      <c r="H82" s="156"/>
+      <c r="I82" s="156"/>
+      <c r="J82" s="156"/>
+      <c r="K82" s="156"/>
+      <c r="L82" s="156"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="B83" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="C82" s="125"/>
-      <c r="D82" s="125"/>
-      <c r="E82" s="125"/>
-      <c r="F82" s="125"/>
-      <c r="G82" s="125"/>
-      <c r="H82" s="125"/>
-      <c r="I82" s="125"/>
-      <c r="J82" s="125"/>
-      <c r="K82" s="125"/>
-      <c r="L82" s="125"/>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="B83" s="125" t="s">
+      <c r="C83" s="156"/>
+      <c r="D83" s="156"/>
+      <c r="E83" s="156"/>
+      <c r="F83" s="156"/>
+      <c r="G83" s="156"/>
+      <c r="H83" s="156"/>
+      <c r="I83" s="156"/>
+      <c r="J83" s="156"/>
+      <c r="K83" s="156"/>
+      <c r="L83" s="156"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="B84" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="152"/>
+      <c r="D84" s="152"/>
+      <c r="E84" s="152"/>
+      <c r="F84" s="152"/>
+      <c r="G84" s="152"/>
+      <c r="H84" s="152"/>
+      <c r="I84" s="152"/>
+      <c r="J84" s="152"/>
+      <c r="K84" s="152"/>
+      <c r="L84" s="152"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="B85" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="C83" s="125"/>
-      <c r="D83" s="125"/>
-      <c r="E83" s="125"/>
-      <c r="F83" s="125"/>
-      <c r="G83" s="125"/>
-      <c r="H83" s="125"/>
-      <c r="I83" s="125"/>
-      <c r="J83" s="125"/>
-      <c r="K83" s="125"/>
-      <c r="L83" s="125"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="B84" s="124" t="s">
-        <v>52</v>
-      </c>
-      <c r="C84" s="124"/>
-      <c r="D84" s="124"/>
-      <c r="E84" s="124"/>
-      <c r="F84" s="124"/>
-      <c r="G84" s="124"/>
-      <c r="H84" s="124"/>
-      <c r="I84" s="124"/>
-      <c r="J84" s="124"/>
-      <c r="K84" s="124"/>
-      <c r="L84" s="124"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="B85" s="125" t="s">
+      <c r="C85" s="156"/>
+      <c r="D85" s="156"/>
+      <c r="E85" s="156"/>
+      <c r="F85" s="156"/>
+      <c r="G85" s="156"/>
+      <c r="H85" s="156"/>
+      <c r="I85" s="156"/>
+      <c r="J85" s="156"/>
+      <c r="K85" s="156"/>
+      <c r="L85" s="156"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="B86" s="152" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" s="152"/>
+      <c r="D86" s="152"/>
+      <c r="E86" s="152"/>
+      <c r="F86" s="152"/>
+      <c r="G86" s="152"/>
+      <c r="H86" s="152"/>
+      <c r="I86" s="152"/>
+      <c r="J86" s="152"/>
+      <c r="K86" s="152"/>
+      <c r="L86" s="152"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="B87" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="C85" s="125"/>
-      <c r="D85" s="125"/>
-      <c r="E85" s="125"/>
-      <c r="F85" s="125"/>
-      <c r="G85" s="125"/>
-      <c r="H85" s="125"/>
-      <c r="I85" s="125"/>
-      <c r="J85" s="125"/>
-      <c r="K85" s="125"/>
-      <c r="L85" s="125"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="B86" s="124" t="s">
-        <v>51</v>
-      </c>
-      <c r="C86" s="124"/>
-      <c r="D86" s="124"/>
-      <c r="E86" s="124"/>
-      <c r="F86" s="124"/>
-      <c r="G86" s="124"/>
-      <c r="H86" s="124"/>
-      <c r="I86" s="124"/>
-      <c r="J86" s="124"/>
-      <c r="K86" s="124"/>
-      <c r="L86" s="124"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="B87" s="125" t="s">
+      <c r="C87" s="156"/>
+      <c r="D87" s="156"/>
+      <c r="E87" s="156"/>
+      <c r="F87" s="156"/>
+      <c r="G87" s="156"/>
+      <c r="H87" s="156"/>
+      <c r="I87" s="156"/>
+      <c r="J87" s="156"/>
+      <c r="K87" s="156"/>
+      <c r="L87" s="156"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="B88" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C87" s="125"/>
-      <c r="D87" s="125"/>
-      <c r="E87" s="125"/>
-      <c r="F87" s="125"/>
-      <c r="G87" s="125"/>
-      <c r="H87" s="125"/>
-      <c r="I87" s="125"/>
-      <c r="J87" s="125"/>
-      <c r="K87" s="125"/>
-      <c r="L87" s="125"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="B88" s="125" t="s">
+      <c r="C88" s="156"/>
+      <c r="D88" s="156"/>
+      <c r="E88" s="156"/>
+      <c r="F88" s="156"/>
+      <c r="G88" s="156"/>
+      <c r="H88" s="156"/>
+      <c r="I88" s="156"/>
+      <c r="J88" s="156"/>
+      <c r="K88" s="156"/>
+      <c r="L88" s="156"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="B89" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="125"/>
-      <c r="D88" s="125"/>
-      <c r="E88" s="125"/>
-      <c r="F88" s="125"/>
-      <c r="G88" s="125"/>
-      <c r="H88" s="125"/>
-      <c r="I88" s="125"/>
-      <c r="J88" s="125"/>
-      <c r="K88" s="125"/>
-      <c r="L88" s="125"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="B89" s="125" t="s">
+      <c r="C89" s="156"/>
+      <c r="D89" s="156"/>
+      <c r="E89" s="156"/>
+      <c r="F89" s="156"/>
+      <c r="G89" s="156"/>
+      <c r="H89" s="156"/>
+      <c r="I89" s="156"/>
+      <c r="J89" s="156"/>
+      <c r="K89" s="156"/>
+      <c r="L89" s="156"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="156" t="s">
         <v>70</v>
       </c>
-      <c r="C89" s="125"/>
-      <c r="D89" s="125"/>
-      <c r="E89" s="125"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="125"/>
-      <c r="H89" s="125"/>
-      <c r="I89" s="125"/>
-      <c r="J89" s="125"/>
-      <c r="K89" s="125"/>
-      <c r="L89" s="125"/>
-    </row>
-    <row r="90" spans="1:12">
-      <c r="B90" s="125" t="s">
+      <c r="C90" s="156"/>
+      <c r="D90" s="156"/>
+      <c r="E90" s="156"/>
+      <c r="F90" s="156"/>
+      <c r="G90" s="156"/>
+      <c r="H90" s="156"/>
+      <c r="I90" s="156"/>
+      <c r="J90" s="156"/>
+      <c r="K90" s="156"/>
+      <c r="L90" s="156"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" s="156" t="s">
         <v>71</v>
       </c>
-      <c r="C90" s="125"/>
-      <c r="D90" s="125"/>
-      <c r="E90" s="125"/>
-      <c r="F90" s="125"/>
-      <c r="G90" s="125"/>
-      <c r="H90" s="125"/>
-      <c r="I90" s="125"/>
-      <c r="J90" s="125"/>
-      <c r="K90" s="125"/>
-      <c r="L90" s="125"/>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="B91" s="125" t="s">
-        <v>72</v>
-      </c>
-      <c r="C91" s="125"/>
-      <c r="D91" s="125"/>
-      <c r="E91" s="125"/>
-      <c r="F91" s="125"/>
-      <c r="G91" s="125"/>
-      <c r="H91" s="125"/>
-      <c r="I91" s="125"/>
-      <c r="J91" s="125"/>
-      <c r="K91" s="125"/>
-      <c r="L91" s="125"/>
+      <c r="C91" s="156"/>
+      <c r="D91" s="156"/>
+      <c r="E91" s="156"/>
+      <c r="F91" s="156"/>
+      <c r="G91" s="156"/>
+      <c r="H91" s="156"/>
+      <c r="I91" s="156"/>
+      <c r="J91" s="156"/>
+      <c r="K91" s="156"/>
+      <c r="L91" s="156"/>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="83"/>
-      <c r="B92" s="145" t="s">
-        <v>84</v>
-      </c>
-      <c r="C92" s="145"/>
-      <c r="D92" s="145"/>
-      <c r="E92" s="145"/>
-      <c r="F92" s="145"/>
-      <c r="G92" s="145"/>
-      <c r="H92" s="145"/>
-      <c r="I92" s="145"/>
-      <c r="J92" s="145"/>
-      <c r="K92" s="145"/>
-      <c r="L92" s="145"/>
+      <c r="B92" s="157" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="157"/>
+      <c r="D92" s="157"/>
+      <c r="E92" s="157"/>
+      <c r="F92" s="157"/>
+      <c r="G92" s="157"/>
+      <c r="H92" s="157"/>
+      <c r="I92" s="157"/>
+      <c r="J92" s="157"/>
+      <c r="K92" s="157"/>
+      <c r="L92" s="157"/>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="83"/>
-      <c r="B93" s="125" t="s">
-        <v>85</v>
-      </c>
-      <c r="C93" s="125"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="125"/>
-      <c r="F93" s="125"/>
-      <c r="G93" s="125"/>
-      <c r="H93" s="125"/>
-      <c r="I93" s="125"/>
-      <c r="J93" s="125"/>
-      <c r="K93" s="125"/>
-      <c r="L93" s="125"/>
+      <c r="B93" s="156" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" s="156"/>
+      <c r="D93" s="156"/>
+      <c r="E93" s="156"/>
+      <c r="F93" s="156"/>
+      <c r="G93" s="156"/>
+      <c r="H93" s="156"/>
+      <c r="I93" s="156"/>
+      <c r="J93" s="156"/>
+      <c r="K93" s="156"/>
+      <c r="L93" s="156"/>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="83"/>
-      <c r="B94" s="145" t="s">
-        <v>86</v>
-      </c>
-      <c r="C94" s="145"/>
-      <c r="D94" s="145"/>
-      <c r="E94" s="145"/>
-      <c r="F94" s="145"/>
-      <c r="G94" s="145"/>
-      <c r="H94" s="145"/>
-      <c r="I94" s="145"/>
-      <c r="J94" s="145"/>
-      <c r="K94" s="145"/>
-      <c r="L94" s="145"/>
+      <c r="B94" s="157" t="s">
+        <v>85</v>
+      </c>
+      <c r="C94" s="157"/>
+      <c r="D94" s="157"/>
+      <c r="E94" s="157"/>
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="157"/>
+      <c r="K94" s="157"/>
+      <c r="L94" s="157"/>
     </row>
     <row r="96" spans="1:12">
       <c r="C96" s="126"/>
@@ -3852,14 +3852,68 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="86">
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B2:C6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="B84:L84"/>
+    <mergeCell ref="B85:L85"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="E60:M60"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="B69:L69"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B67:L67"/>
+    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B65:L65"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="B60:C64"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B56:L56"/>
+    <mergeCell ref="D61:J61"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B94:L94"/>
+    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B93:L93"/>
+    <mergeCell ref="B92:L92"/>
+    <mergeCell ref="B91:L91"/>
+    <mergeCell ref="B86:L86"/>
+    <mergeCell ref="B87:L87"/>
+    <mergeCell ref="B88:L88"/>
+    <mergeCell ref="B89:L89"/>
+    <mergeCell ref="B90:L90"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B16:J16"/>
     <mergeCell ref="C96:I105"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="E2:L2"/>
@@ -3876,68 +3930,14 @@
     <mergeCell ref="B57:L57"/>
     <mergeCell ref="B55:L55"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B91:L91"/>
-    <mergeCell ref="B86:L86"/>
-    <mergeCell ref="B87:L87"/>
-    <mergeCell ref="B88:L88"/>
-    <mergeCell ref="B89:L89"/>
-    <mergeCell ref="B90:L90"/>
-    <mergeCell ref="B94:L94"/>
-    <mergeCell ref="B77:L77"/>
-    <mergeCell ref="B78:L78"/>
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B74:L74"/>
-    <mergeCell ref="B75:L75"/>
-    <mergeCell ref="B76:L76"/>
-    <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B82:L82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="B93:L93"/>
-    <mergeCell ref="B92:L92"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="B60:C64"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="D61:J61"/>
-    <mergeCell ref="K61:M61"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="B40:J40"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B84:L84"/>
-    <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="E60:M60"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B65:L65"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B2:C6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:L7"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="VERIFICAR NÚMERO DE TELEFONO" error="Verifica que tenga 9 digitos sin espacio" sqref="J8:L8" xr:uid="{CC0405B2-A74A-4E8F-BF03-C34BEE695B67}">
@@ -3970,41 +3970,41 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A3:AG50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="11.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="2"/>
-    <col min="8" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" style="1" customWidth="1"/>
-    <col min="12" max="32" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="11.44140625" style="2"/>
+    <col min="8" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="32" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:32">
-      <c r="B3" s="166" t="s">
+      <c r="B3" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
     </row>
     <row r="6" spans="2:32" ht="15" customHeight="1">
       <c r="B6" s="68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="E6" s="68" t="s">
         <v>103</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>104</v>
       </c>
       <c r="F6" s="68" t="s">
         <v>8</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="7" spans="2:32" ht="15" customHeight="1">
       <c r="B7" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="7">
         <v>7</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="8" spans="2:32" ht="15" customHeight="1">
       <c r="B8" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="64">
         <v>110</v>
@@ -4041,18 +4041,18 @@
         <f>SUM(C8:E8)</f>
         <v>116</v>
       </c>
-      <c r="J8" s="164" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="164"/>
-      <c r="M8" s="164" t="s">
-        <v>107</v>
-      </c>
-      <c r="N8" s="164"/>
+      <c r="J8" s="172" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="172"/>
+      <c r="M8" s="172" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8" s="172"/>
     </row>
     <row r="9" spans="2:32" ht="15" customHeight="1">
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="63">
         <v>1.1539999999999999</v>
@@ -4067,13 +4067,13 @@
       </c>
       <c r="G9" s="1"/>
       <c r="J9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>54</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>54</v>
@@ -4104,13 +4104,13 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K10" s="70">
         <v>250</v>
       </c>
       <c r="M10" s="56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N10" s="70">
         <v>250</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="11" spans="2:32" ht="15" hidden="1" customHeight="1">
       <c r="B11" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="41"/>
@@ -4170,13 +4170,13 @@
       </c>
       <c r="G12" s="1"/>
       <c r="J12" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K12" s="70">
         <v>350</v>
       </c>
       <c r="M12" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N12" s="70">
         <v>325</v>
@@ -4212,13 +4212,13 @@
       </c>
       <c r="G13" s="1"/>
       <c r="J13" s="56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K13" s="70">
         <v>350</v>
       </c>
       <c r="M13" s="56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N13" s="70">
         <v>325</v>
@@ -4291,13 +4291,13 @@
       </c>
       <c r="G15" s="28"/>
       <c r="J15" s="56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K15" s="70">
         <v>325</v>
       </c>
       <c r="M15" s="56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N15" s="70">
         <v>300</v>
@@ -4333,13 +4333,13 @@
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K16" s="70">
         <v>300</v>
       </c>
       <c r="M16" s="56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N16" s="70">
         <v>275</v>
@@ -4375,13 +4375,13 @@
       </c>
       <c r="G17" s="1"/>
       <c r="J17" s="56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K17" s="70">
         <v>280</v>
       </c>
       <c r="M17" s="56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N17" s="70">
         <v>250</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="18" spans="1:33" ht="14.25" hidden="1" customHeight="1">
       <c r="B18" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="43">
         <f t="shared" ref="C18:E18" si="3">C14+C16</f>
@@ -4479,10 +4479,10 @@
       </c>
       <c r="G20" s="1"/>
       <c r="J20" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y20"/>
       <c r="Z20"/>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="21" spans="1:33" ht="18.75" hidden="1" customHeight="1">
       <c r="B21" s="42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="43">
         <f>C18+C19</f>
@@ -4521,21 +4521,21 @@
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="B23" s="165" t="s">
+      <c r="B23" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="165"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165"/>
-      <c r="F23" s="165"/>
-      <c r="G23" s="165"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="173"/>
     </row>
     <row r="24" spans="1:33">
       <c r="J24" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -4589,7 +4589,7 @@
     </row>
     <row r="28" spans="1:33">
       <c r="B28" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="115">
         <v>0</v>
@@ -4733,7 +4733,7 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K32" s="5">
         <v>3.7</v>
@@ -4794,14 +4794,14 @@
       <c r="AF35"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="B36" s="167" t="s">
+      <c r="B36" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="167"/>
-      <c r="D36" s="167"/>
-      <c r="E36" s="167"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="167"/>
+      <c r="C36" s="175"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="175"/>
+      <c r="F36" s="175"/>
+      <c r="G36" s="175"/>
     </row>
     <row r="38" spans="1:32">
       <c r="C38" s="21">
